--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור כהן - שתי אצבעות מצידון קאבר</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-21</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410111&amp;sid=d9fde2e1eab8b08b2faa365bbd09a1de</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור כהן - שתי אצבעות מצידון קאבר</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-22</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H3" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-22</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H4" t="str">
-        <v>Nick Carter</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-22</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:38</v>
+        <v>4:11</v>
       </c>
       <c r="H5" t="str">
-        <v>Carly Pearce</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-22</v>
@@ -606,10 +606,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:11</v>
+        <v>2:57</v>
       </c>
       <c r="H6" t="str">
-        <v>OneRepublic</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-22</v>
@@ -644,10 +644,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:57</v>
+        <v>3:47</v>
       </c>
       <c r="H7" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-22</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:47</v>
+        <v>7:10</v>
       </c>
       <c r="H8" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-22</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:10</v>
+        <v>3:06</v>
       </c>
       <c r="H9" t="str">
-        <v>David Gilmour</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-22</v>
@@ -758,10 +758,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:06</v>
+        <v>3:05</v>
       </c>
       <c r="H10" t="str">
-        <v>Grace Enger</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-22</v>
@@ -796,10 +796,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H11" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-22</v>
@@ -834,10 +834,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:12</v>
+        <v>9:11</v>
       </c>
       <c r="H12" t="str">
-        <v>Freya Ridings</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-22</v>
@@ -872,10 +872,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>9:11</v>
+        <v>3:49</v>
       </c>
       <c r="H13" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-22</v>
@@ -910,10 +910,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:49</v>
+        <v>3:28</v>
       </c>
       <c r="H14" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-22</v>
@@ -948,10 +948,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H15" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-22</v>
@@ -986,10 +986,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:31</v>
+        <v>3:11</v>
       </c>
       <c r="H16" t="str">
-        <v>Martin Garrix</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-22</v>
@@ -1024,10 +1024,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:11</v>
+        <v>2:27</v>
       </c>
       <c r="H17" t="str">
-        <v>Baby Queen</v>
+        <v>HAUSER</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-22</v>
@@ -1062,10 +1062,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-22</v>
@@ -1100,10 +1100,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:34</v>
+        <v>2:50</v>
       </c>
       <c r="H19" t="str">
-        <v>Holly Humberstone</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-22</v>
@@ -1138,10 +1138,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H20" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-22</v>
@@ -1176,10 +1176,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:51</v>
+        <v>2:39</v>
       </c>
       <c r="H21" t="str">
-        <v>Rick Astley</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-22</v>
@@ -1214,10 +1214,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:39</v>
+        <v>5:08</v>
       </c>
       <c r="H22" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Jessie J</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-22</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:08</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Jessie J</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-22</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H24" t="str">
-        <v>Bishop Briggs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-22</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:42</v>
+        <v>2:31</v>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-22</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:31</v>
+        <v>3:14</v>
       </c>
       <c r="H26" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-22</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H27" t="str">
-        <v>Luke Combs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-22</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H28" t="str">
-        <v>Allison Russell</v>
+        <v>We Three</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-22</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:43</v>
+        <v>2:54</v>
       </c>
       <c r="H29" t="str">
-        <v>We Three</v>
+        <v>paris jackson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-22</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H30" t="str">
-        <v>paris jackson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-22</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:46</v>
+        <v>3:37</v>
       </c>
       <c r="H31" t="str">
-        <v>Kane Brown</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-22</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Lainey Wilson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-22</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H33" t="str">
-        <v>Malcolm Todd</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-22</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:38</v>
+        <v>4:29</v>
       </c>
       <c r="H34" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Kungs</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-22</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:29</v>
+        <v>4:28</v>
       </c>
       <c r="H35" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-22</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:28</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>Sunday (1994)</v>
+        <v>aron!</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-22</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H37" t="str">
-        <v>aron!</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-22</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:51</v>
+        <v>2:49</v>
       </c>
       <c r="H38" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-22</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H39" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-22</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:16</v>
       </c>
       <c r="H40" t="str">
-        <v>Owen Riegling</v>
+        <v>LANY</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-22</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H41" t="str">
-        <v>LANY</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-22</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H42" t="str">
-        <v>Maverick Sabre</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-22</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:50</v>
+        <v>3:57</v>
       </c>
       <c r="H43" t="str">
-        <v>Amanda Jordan</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-22</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:57</v>
+        <v>3:58</v>
       </c>
       <c r="H44" t="str">
-        <v>Beabadoobee</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-22</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:58</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>Spacey Jane</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H46" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-22</v>
@@ -2164,10 +2164,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H47" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H48" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-22</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H49" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-22</v>
@@ -2278,10 +2278,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H50" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-22</v>
@@ -2316,10 +2316,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H51" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-22</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H52" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-22</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H53" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-22</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-22</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-22</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H56" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-22</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:01</v>
+        <v>4:56</v>
       </c>
       <c r="H57" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-22</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:56</v>
+        <v>2:54</v>
       </c>
       <c r="H58" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-22</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H59" t="str">
-        <v>Bebe Rexha</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-22</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>NathanEvanss</v>
+        <v>R3HAB</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-22</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H61" t="str">
-        <v>R3HAB</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-22</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H62" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-22</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H63" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-22</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:41</v>
+        <v>2:29</v>
       </c>
       <c r="H64" t="str">
-        <v>Johnny Orlando</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-22</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Russell Dickerson</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-22</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H66" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-22</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H67" t="str">
-        <v>Matt Hansen</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-22</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H68" t="str">
-        <v>Mike Posner</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-22</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Katelyn Tarver</v>
+        <v>almost monday</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-22</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-22</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H71" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-22</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H72" t="str">
-        <v>vaultboy</v>
+        <v>The Warning</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-22</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H73" t="str">
-        <v>The Warning</v>
+        <v>aron!</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-22</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H74" t="str">
-        <v>aron!</v>
+        <v>Bazzi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-22</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Bazzi</v>
+        <v>Sting</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-22</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:43</v>
+        <v>2:44</v>
       </c>
       <c r="H76" t="str">
-        <v>Sting</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-22</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:44</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-22</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:37</v>
+        <v>4:52</v>
       </c>
       <c r="H78" t="str">
-        <v>Jessie Ware</v>
+        <v>Cannons</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-22</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:52</v>
+        <v>2:13</v>
       </c>
       <c r="H79" t="str">
-        <v>Cannons</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-22</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H80" t="str">
-        <v>Kim Petras</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-22</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:19</v>
+        <v>2:31</v>
       </c>
       <c r="H81" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-22</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:31</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-22</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Ringo Starr</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-22</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:10</v>
+        <v>3:55</v>
       </c>
       <c r="H84" t="str">
-        <v>Maya Hawke</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-22</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:55</v>
+        <v>3:52</v>
       </c>
       <c r="H85" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-22</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:52</v>
+        <v>2:53</v>
       </c>
       <c r="H86" t="str">
-        <v>Demi Lovato</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-22</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:53</v>
+        <v>4:30</v>
       </c>
       <c r="H87" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie J</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-22</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:30</v>
+        <v>5:18</v>
       </c>
       <c r="H88" t="str">
-        <v>Jessie J</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-22</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-22</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-22</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H91" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-22</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H92" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-22</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H93" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-22</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-22</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H95" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-22</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H96" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-22</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H97" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-22</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-22</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H99" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-22</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H100" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-22</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H101" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>SWIM</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G102" t="str">
-        <v>3:40</v>
+        <v>2:39</v>
       </c>
       <c r="H102" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>BTS</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L102" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SWIM</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ARIRANG</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G103" t="str">
-        <v>2:39</v>
+        <v>5:01</v>
       </c>
       <c r="H103" t="str">
-        <v>BTS</v>
+        <v>RAYE</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L103" t="str">
-        <v>SWIM - BTS</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>5:01</v>
+        <v>3:46</v>
       </c>
       <c r="H104" t="str">
-        <v>RAYE</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Loving Life Again</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dandelion</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G105" t="str">
-        <v>3:46</v>
+        <v>2:45</v>
       </c>
       <c r="H105" t="str">
-        <v>Ella Langley</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L105" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Rethink Some Things</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Way I Am</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G106" t="str">
-        <v>2:45</v>
+        <v>2:42</v>
       </c>
       <c r="H106" t="str">
-        <v>Luke Combs</v>
+        <v>Feid</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L106" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>TRANKAITO</v>
+        <v>Leak It</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:42</v>
+        <v>3:03</v>
       </c>
       <c r="H107" t="str">
-        <v>Feid</v>
+        <v>FLO</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L107" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Leak It</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Leak It - Single</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:03</v>
+        <v>2:40</v>
       </c>
       <c r="H108" t="str">
-        <v>FLO</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L108" t="str">
-        <v>Leak It - FLO</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>LUVAGIRL</v>
+        <v>D33P3R</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>R3SET</v>
       </c>
       <c r="G109" t="str">
-        <v>2:40</v>
+        <v>3:25</v>
       </c>
       <c r="H109" t="str">
-        <v>Coco Jones</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L109" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>D33P3R</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>R3SET</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:25</v>
+        <v>3:01</v>
       </c>
       <c r="H110" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Yeat</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L110" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:01</v>
+        <v>3:09</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L111" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Don't Hate Me</v>
+        <v>Pongo</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G112" t="str">
         <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Miles Caton</v>
+        <v>Rvssian</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L112" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Pongo</v>
+        <v>BOTERO</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Pongo - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:09</v>
+        <v>4:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Rvssian</v>
+        <v>Maluma</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L113" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>BOTERO</v>
+        <v>Distance</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>BOTERO - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:14</v>
+        <v>3:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L114" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Distance</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Distance - Single</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:14</v>
+        <v>3:44</v>
       </c>
       <c r="H115" t="str">
-        <v>Finn Askew</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L115" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Riptides</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G116" t="str">
-        <v>3:44</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>Dionne Warwick</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L116" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Riptides</v>
+        <v>2.0</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>I Built You a Tower</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>2:49</v>
       </c>
       <c r="H117" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>BTS</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L117" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2.0</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ARIRANG</v>
+        <v>6WA</v>
       </c>
       <c r="G118" t="str">
-        <v>2:49</v>
+        <v>3:08</v>
       </c>
       <c r="H118" t="str">
-        <v>BTS</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L118" t="str">
-        <v>2.0 - BTS</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>6IXER PARTY</v>
+        <v>Highest</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>6WA</v>
+        <v>Detour</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H119" t="str">
-        <v>BigXthaPlug</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L119" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Highest</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Detour</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:56</v>
+        <v>2:40</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L120" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>So What</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G121" t="str">
-        <v>2:40</v>
+        <v>4:31</v>
       </c>
       <c r="H121" t="str">
-        <v>Coi Leray</v>
+        <v>MUNA</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>So What</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G122" t="str">
-        <v>4:31</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>MUNA</v>
+        <v>Eli</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L122" t="str">
-        <v>So What - MUNA</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G123" t="str">
-        <v>3:12</v>
+        <v>4:06</v>
       </c>
       <c r="H123" t="str">
-        <v>Eli</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L123" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Running To Pain</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>So Help Me God</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:06</v>
+        <v>2:14</v>
       </c>
       <c r="H124" t="str">
-        <v>Kelsey Lu</v>
+        <v>Anitta</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L124" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>4:20</v>
       </c>
       <c r="H125" t="str">
-        <v>Anitta</v>
+        <v>Latto</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L125" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-22</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Big Mama</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G126" t="str">
-        <v>4:20</v>
+        <v>2:58</v>
       </c>
       <c r="H126" t="str">
-        <v>Latto</v>
+        <v>6LACK</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L126" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Bird Flu</v>
+        <v>Lighter</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:59</v>
       </c>
       <c r="H127" t="str">
-        <v>6LACK</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L127" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Lighter</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>4:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Jelly Roll</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L128" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Wide Awake</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>Chris Stussy</v>
+        <v>Lizzo</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L129" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G130" t="str">
-        <v>3:25</v>
+        <v>2:34</v>
       </c>
       <c r="H130" t="str">
-        <v>Lizzo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L130" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Dinner Party</v>
+        <v>NORMAL</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Dinner Party</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G131" t="str">
-        <v>2:34</v>
+        <v>3:01</v>
       </c>
       <c r="H131" t="str">
-        <v>Niall Horan</v>
+        <v>BTS</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L131" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>NORMAL</v>
+        <v>Die Living</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ARIRANG</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>BTS</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L132" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Die Living</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Die Living - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:50</v>
+        <v>2:59</v>
       </c>
       <c r="H133" t="str">
-        <v>ILLENIUM</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L133" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Heaven On Earth</v>
+        <v>an apple a day</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:59</v>
+        <v>5:16</v>
       </c>
       <c r="H134" t="str">
-        <v>Pentatonix</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L134" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>an apple a day</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>an apple a day - Single</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>5:16</v>
+        <v>2:09</v>
       </c>
       <c r="H135" t="str">
-        <v>horsegiirL</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L135" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>OUT LATE.</v>
+        <v>Be With You</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G136" t="str">
-        <v>2:09</v>
+        <v>3:35</v>
       </c>
       <c r="H136" t="str">
-        <v>Loud Luxury</v>
+        <v>Muse</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L136" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Be With You</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Wow! Signal</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G137" t="str">
-        <v>3:35</v>
+        <v>8:27</v>
       </c>
       <c r="H137" t="str">
-        <v>Muse</v>
+        <v>Neurosis</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L137" t="str">
-        <v>Be With You - Muse</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>First Red Rays</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G138" t="str">
-        <v>8:27</v>
+        <v>4:02</v>
       </c>
       <c r="H138" t="str">
-        <v>Neurosis</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L138" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Caught In The Echo</v>
+        <v>Little by Little</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>4:02</v>
+        <v>2:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Foo Fighters</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L139" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Little by Little</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Little by Little - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:34</v>
+        <v>3:28</v>
       </c>
       <c r="H140" t="str">
-        <v>Mon Rovîa</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L140" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Montgomery County</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:28</v>
+        <v>2:46</v>
       </c>
       <c r="H141" t="str">
-        <v>Parker McCollum</v>
+        <v>Alok</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L141" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Dive Into Me</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G142" t="str">
-        <v>2:46</v>
+        <v>2:40</v>
       </c>
       <c r="H142" t="str">
-        <v>Alok</v>
+        <v>Artemas</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L142" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>more than just a little bit</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>getting up to no good</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:40</v>
+        <v>2:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Artemas</v>
+        <v>Asake</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L143" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>WORSHIP</v>
+        <v>Honest</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>WORSHIP - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:43</v>
+        <v>3:22</v>
       </c>
       <c r="H144" t="str">
-        <v>Asake</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L144" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Honest</v>
+        <v>6ft Under</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Honest - Single</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:22</v>
+        <v>3:30</v>
       </c>
       <c r="H145" t="str">
-        <v>Ebony Riley</v>
+        <v>KELS</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L145" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>6ft Under</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>6ft Under - Single</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G146" t="str">
-        <v>3:30</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>KELS</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L146" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Maybe Again</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>When The City Sleeps</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G147" t="str">
-        <v>3:29</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>Alex Isley</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L147" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Trigger Happy</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Attachment Theory</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G148" t="str">
         <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L148" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G149" t="str">
-        <v>3:01</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Kid Cudi</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L149" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:30</v>
+        <v>2:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Swae Lee</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L150" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Runnin' On E</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>LINAJE</v>
       </c>
       <c r="G151" t="str">
-        <v>2:27</v>
+        <v>5:36</v>
       </c>
       <c r="H151" t="str">
-        <v>Wyatt Flores</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L151" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>FREESTYLE</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>LINAJE</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G152" t="str">
-        <v>5:36</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>marquitos</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L152" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Orcasitas</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Alma De Cántaro</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G153" t="str">
-        <v>3:23</v>
+        <v>2:35</v>
       </c>
       <c r="H153" t="str">
-        <v>marquitos</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L153" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Vida Loca</v>
+        <v>Honest</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>FREE SPIRITS</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G154" t="str">
-        <v>2:35</v>
+        <v>3:39</v>
       </c>
       <c r="H154" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L154" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Honest</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>The Weight of the Woods</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:39</v>
+        <v>3:01</v>
       </c>
       <c r="H155" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L155" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Peaches!</v>
       </c>
       <c r="G156" t="str">
-        <v>3:01</v>
+        <v>5:00</v>
       </c>
       <c r="H156" t="str">
-        <v>Kenia Os</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L156" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Peaches!</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G157" t="str">
-        <v>5:00</v>
+        <v>3:36</v>
       </c>
       <c r="H157" t="str">
-        <v>The Black Keys</v>
+        <v>Cannons</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L157" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Light as a Feather</v>
+        <v>Loving One</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Everything Glows</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Cannons</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L158" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Loving One</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Loving One - Single</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:39</v>
+        <v>3:05</v>
       </c>
       <c r="H159" t="str">
-        <v>People I’ve Met</v>
+        <v>Trousdale</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L159" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Both Can Be True</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G160" t="str">
-        <v>3:05</v>
+        <v>4:27</v>
       </c>
       <c r="H160" t="str">
-        <v>Trousdale</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L160" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Buffalo 66</v>
+        <v>brb</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>brb - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:27</v>
+        <v>2:36</v>
       </c>
       <c r="H161" t="str">
-        <v>Nessa Barrett</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L161" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>brb</v>
+        <v>Euphoria</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>brb - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:36</v>
+        <v>3:32</v>
       </c>
       <c r="H162" t="str">
-        <v>The Two Lips</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L162" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Euphoria</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Euphoria - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>3:32</v>
+        <v>2:57</v>
       </c>
       <c r="H163" t="str">
-        <v>Talia Rae</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L163" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>if i'm lucky</v>
+        <v>Gracie</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>better late than not at all - EP</v>
+        <v>F.I.G</v>
       </c>
       <c r="G164" t="str">
-        <v>2:57</v>
+        <v>2:54</v>
       </c>
       <c r="H164" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L164" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Gracie</v>
+        <v>down under</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>F.I.G</v>
+        <v>down under - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:54</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>Naomi Scott</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L165" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>down under</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>down under - Single</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L166" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Send Me A Sign</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>3:02</v>
       </c>
       <c r="H167" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L167" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G168" t="str">
-        <v>3:02</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>OneRepublic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L168" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Dream Chaser</v>
+        <v>Trouble</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dream Chaser</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G169" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Willie Nelson</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L169" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Trouble</v>
+        <v>judas</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Girlfriend</v>
+        <v>judas - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Grace Ives</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L170" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>judas</v>
+        <v>JINX</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>judas - Single</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:31</v>
+        <v>2:54</v>
       </c>
       <c r="H171" t="str">
-        <v>Josiah Queen</v>
+        <v>Zacari</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L171" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>JINX</v>
+        <v>se fue</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>JINX - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G172" t="str">
-        <v>2:54</v>
+        <v>2:51</v>
       </c>
       <c r="H172" t="str">
-        <v>Zacari</v>
+        <v>Eddy</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L172" t="str">
-        <v>JINX - Zacari</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>se fue</v>
+        <v>The Blade</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Náufrago</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:51</v>
+        <v>3:15</v>
       </c>
       <c r="H173" t="str">
-        <v>Eddy</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L173" t="str">
-        <v>se fue - Eddy</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Blade</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Blade - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:15</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>Kingfishr</v>
+        <v>SPINALL</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L174" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Metric Rules</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:13</v>
+        <v>2:15</v>
       </c>
       <c r="H175" t="str">
-        <v>SPINALL</v>
+        <v>ZEP</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L175" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:15</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>ZEP</v>
+        <v>Hutch</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L176" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:23</v>
+        <v>5:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Hutch</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L177" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Cyclone</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G178" t="str">
-        <v>5:15</v>
+        <v>5:33</v>
       </c>
       <c r="H178" t="str">
-        <v>MJ Cole</v>
+        <v>Gaerea</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L178" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Cyclone</v>
+        <v>Checkmate</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Loss</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>5:33</v>
+        <v>4:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Gaerea</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L179" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checkmate</v>
+        <v>DAVE</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Checkmate - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:23</v>
+        <v>2:01</v>
       </c>
       <c r="H180" t="str">
-        <v>Blue Medusa</v>
+        <v>Hulvey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L180" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>DAVE</v>
+        <v>Change</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>DAVE - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:01</v>
+        <v>2:38</v>
       </c>
       <c r="H181" t="str">
-        <v>Hulvey</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L181" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Change</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Change - Single</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:38</v>
+        <v>3:05</v>
       </c>
       <c r="H182" t="str">
-        <v>Stephen Stanley</v>
+        <v>Maisak</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L182" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Te Entiendo</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>V</v>
       </c>
       <c r="G183" t="str">
-        <v>3:05</v>
+        <v>2:01</v>
       </c>
       <c r="H183" t="str">
-        <v>Maisak</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L183" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>V</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G184" t="str">
-        <v>2:01</v>
+        <v>3:53</v>
       </c>
       <c r="H184" t="str">
-        <v>Rey Quinto</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L184" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Tirabalas</v>
+        <v>punchbowl</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:53</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>Hans el Oso</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L185" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>punchbowl</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>punchbowl - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:34</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>Julio Caesar</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L186" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Wild Ride</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Wild Ride - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>2:03</v>
       </c>
       <c r="H187" t="str">
-        <v>Durand Bernarr</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L187" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Lamb Chop</v>
+        <v>Free Nick</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:03</v>
+        <v>2:05</v>
       </c>
       <c r="H188" t="str">
-        <v>Chuckyy</v>
+        <v>Raq baby</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L188" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Free Nick</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Free Nick - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:05</v>
+        <v>3:06</v>
       </c>
       <c r="H189" t="str">
-        <v>Raq baby</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L189" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make Me Brand New</v>
+        <v>Define You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:06</v>
+        <v>3:34</v>
       </c>
       <c r="H190" t="str">
-        <v>Dante’ Pride</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L190" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Define You</v>
+        <v>If You Change</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Define You - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G191" t="str">
-        <v>3:34</v>
+        <v>4:41</v>
       </c>
       <c r="H191" t="str">
-        <v>Luca Fogale</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L191" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>If You Change</v>
+        <v>What I See</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Roses</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:41</v>
+        <v>2:32</v>
       </c>
       <c r="H192" t="str">
-        <v>Widowspeak</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L192" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>What I See</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G193" t="str">
-        <v>2:32</v>
+        <v>3:47</v>
       </c>
       <c r="H193" t="str">
-        <v>See You Next Year</v>
+        <v>Witch Post</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L193" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Witching Hour</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Butterfly</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:47</v>
+        <v>3:07</v>
       </c>
       <c r="H194" t="str">
-        <v>Witch Post</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L194" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Actin' Tough</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:07</v>
+        <v>2:52</v>
       </c>
       <c r="H195" t="str">
-        <v>Dean Turnley</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L195" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Rewind It</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-22</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:52</v>
+        <v>1:34</v>
       </c>
       <c r="H196" t="str">
-        <v>Anais Cardot</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L196" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Rewind It</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-22</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Rewind It - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>1:34</v>
+        <v>2:33</v>
       </c>
       <c r="H197" t="str">
-        <v>Nino Paid</v>
+        <v>slayr</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L197" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Turn It Up</v>
+        <v>Down</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-22</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:33</v>
+        <v>2:08</v>
       </c>
       <c r="H198" t="str">
-        <v>slayr</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L198" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Down</v>
+        <v>Make It Out</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-22</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Down - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:08</v>
+        <v>2:17</v>
       </c>
       <c r="H199" t="str">
-        <v>MexikoDro</v>
+        <v>Trueblood</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L199" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Make It Out</v>
+        <v>better than boston</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-22</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Make It Out - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:17</v>
+        <v>3:02</v>
       </c>
       <c r="H200" t="str">
-        <v>Trueblood</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L200" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>better than boston</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-22</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>better than boston - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:02</v>
+        <v>2:34</v>
       </c>
       <c r="H201" t="str">
-        <v>Tom Siletto</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L201" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>All I Need</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-22</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:34</v>
+        <v>3:06</v>
       </c>
       <c r="H202" t="str">
-        <v>Lost Frequencies</v>
+        <v>GRiZ</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L202" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>All I Need</v>
+        <v>Weeping Tones</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-22</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>All I Need - Single</v>
+        <v>Peace In Place</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>2:59</v>
       </c>
       <c r="H203" t="str">
-        <v>GRiZ</v>
+        <v>Poison the Well</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
       </c>
       <c r="L203" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>Weeping Tones - Poison the Well</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Weeping Tones</v>
+        <v>Promise You This</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-22</v>
@@ -8127,68 +8127,30 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Peace In Place</v>
+        <v>Goliath</v>
       </c>
       <c r="G204" t="str">
-        <v>2:59</v>
+        <v>5:19</v>
       </c>
       <c r="H204" t="str">
-        <v>Poison the Well</v>
+        <v>Exodus</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
       <c r="L204" t="str">
-        <v>Weeping Tones - Poison the Well</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Promise You This</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Goliath</v>
-      </c>
-      <c r="G205" t="str">
-        <v>5:19</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Exodus</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
-      </c>
-      <c r="L205" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>אושר כהן – כולם גנבים</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a9%d7%a8-%d7%9b%d7%94%d7%9f-%d7%9b%d7%95%d7%9c%d7%9d-%d7%92%d7%a0%d7%91%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v>אושר כהן שר דינמיקה זוגית לא בריאה, כמעט ממכרת בשיר פופ ים־תיכוני  שמשלב בין רגש גולמי, דרמה קולית והפקה עכשווית בשיר המתאר מערכת יחסים רעילה בגיל צעיר ליבת השיר היא מערכת יחסים סוערת שמבוססת על משיכה–דחייה: מצד אחד: "אני אוהב</v>
       </c>
       <c r="G2" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>אושר כהן – כולם גנבים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-22</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H3" t="str">
-        <v>Nick Carter</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B4" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-22</v>
@@ -530,10 +530,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H4" t="str">
-        <v>Carly Pearce</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-22</v>
@@ -568,10 +568,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:11</v>
+        <v>3:38</v>
       </c>
       <c r="H5" t="str">
-        <v>OneRepublic</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-22</v>
@@ -606,10 +606,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:57</v>
+        <v>4:11</v>
       </c>
       <c r="H6" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B7" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-22</v>
@@ -644,10 +644,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:47</v>
+        <v>2:57</v>
       </c>
       <c r="H7" t="str">
-        <v>Armin van Buuren</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-22</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>7:10</v>
+        <v>3:47</v>
       </c>
       <c r="H8" t="str">
-        <v>David Gilmour</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-22</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:06</v>
+        <v>7:10</v>
       </c>
       <c r="H9" t="str">
-        <v>Grace Enger</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B10" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-22</v>
@@ -758,10 +758,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:05</v>
+        <v>3:06</v>
       </c>
       <c r="H10" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-22</v>
@@ -796,10 +796,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:12</v>
+        <v>3:05</v>
       </c>
       <c r="H11" t="str">
-        <v>Freya Ridings</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B12" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-22</v>
@@ -834,10 +834,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>9:11</v>
+        <v>3:12</v>
       </c>
       <c r="H12" t="str">
-        <v>David Gilmour</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B13" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-22</v>
@@ -872,10 +872,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:49</v>
+        <v>9:11</v>
       </c>
       <c r="H13" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B14" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-22</v>
@@ -910,10 +910,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:28</v>
+        <v>3:49</v>
       </c>
       <c r="H14" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B15" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-22</v>
@@ -948,10 +948,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:31</v>
+        <v>3:28</v>
       </c>
       <c r="H15" t="str">
-        <v>Martin Garrix</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-22</v>
@@ -986,10 +986,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:11</v>
+        <v>3:31</v>
       </c>
       <c r="H16" t="str">
-        <v>Baby Queen</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-22</v>
@@ -1024,10 +1024,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:27</v>
+        <v>3:11</v>
       </c>
       <c r="H17" t="str">
-        <v>HAUSER</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B18" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-22</v>
@@ -1062,10 +1062,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H18" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B19" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-22</v>
@@ -1100,10 +1100,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:50</v>
+        <v>3:34</v>
       </c>
       <c r="H19" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-22</v>
@@ -1138,10 +1138,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:51</v>
+        <v>2:50</v>
       </c>
       <c r="H20" t="str">
-        <v>Rick Astley</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-22</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:39</v>
+        <v>3:51</v>
       </c>
       <c r="H21" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-22</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:08</v>
+        <v>2:39</v>
       </c>
       <c r="H22" t="str">
-        <v>Jessie J</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-22</v>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:46</v>
+        <v>5:08</v>
       </c>
       <c r="H23" t="str">
-        <v>Bishop Briggs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-22</v>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:42</v>
+        <v>3:46</v>
       </c>
       <c r="H24" t="str">
-        <v>Dean Lewis</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-22</v>
@@ -1328,10 +1328,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:31</v>
+        <v>2:42</v>
       </c>
       <c r="H25" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-22</v>
@@ -1366,10 +1366,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:14</v>
+        <v>2:31</v>
       </c>
       <c r="H26" t="str">
-        <v>Luke Combs</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B27" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-22</v>
@@ -1404,10 +1404,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H27" t="str">
-        <v>Allison Russell</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-22</v>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:43</v>
+        <v>3:22</v>
       </c>
       <c r="H28" t="str">
-        <v>We Three</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-22</v>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:54</v>
+        <v>3:43</v>
       </c>
       <c r="H29" t="str">
-        <v>paris jackson</v>
+        <v>We Three</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B30" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-22</v>
@@ -1518,10 +1518,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H30" t="str">
-        <v>Kane Brown</v>
+        <v>paris jackson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-22</v>
@@ -1556,10 +1556,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:37</v>
+        <v>2:46</v>
       </c>
       <c r="H31" t="str">
-        <v>Lainey Wilson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-22</v>
@@ -1594,10 +1594,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:57</v>
+        <v>3:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Malcolm Todd</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-22</v>
@@ -1632,10 +1632,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:38</v>
+        <v>2:57</v>
       </c>
       <c r="H33" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-22</v>
@@ -1670,10 +1670,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:29</v>
+        <v>3:38</v>
       </c>
       <c r="H34" t="str">
-        <v>Kungs</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B35" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-22</v>
@@ -1708,10 +1708,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:28</v>
+        <v>4:29</v>
       </c>
       <c r="H35" t="str">
-        <v>Sunday (1994)</v>
+        <v>Kungs</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B36" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-22</v>
@@ -1746,10 +1746,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:26</v>
+        <v>4:28</v>
       </c>
       <c r="H36" t="str">
-        <v>aron!</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B37" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-22</v>
@@ -1784,10 +1784,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:51</v>
+        <v>3:26</v>
       </c>
       <c r="H37" t="str">
-        <v>Colinstoughmusic</v>
+        <v>aron!</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B38" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-22</v>
@@ -1822,10 +1822,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:49</v>
+        <v>3:51</v>
       </c>
       <c r="H38" t="str">
-        <v>Sunday (1994)</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B39" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-22</v>
@@ -1860,10 +1860,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:16</v>
+        <v>2:49</v>
       </c>
       <c r="H39" t="str">
-        <v>Owen Riegling</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-22</v>
@@ -1901,7 +1901,7 @@
         <v>4:16</v>
       </c>
       <c r="H40" t="str">
-        <v>LANY</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-22</v>
@@ -1936,10 +1936,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H41" t="str">
-        <v>Maverick Sabre</v>
+        <v>LANY</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-22</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:50</v>
+        <v>3:25</v>
       </c>
       <c r="H42" t="str">
-        <v>Amanda Jordan</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-22</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:57</v>
+        <v>2:50</v>
       </c>
       <c r="H43" t="str">
-        <v>Beabadoobee</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-22</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:58</v>
+        <v>3:57</v>
       </c>
       <c r="H44" t="str">
-        <v>Spacey Jane</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-22</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:25</v>
+        <v>3:58</v>
       </c>
       <c r="H45" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:09</v>
+        <v>3:25</v>
       </c>
       <c r="H46" t="str">
-        <v>Mei Semones</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B47" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-22</v>
@@ -2164,10 +2164,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:08</v>
+        <v>4:09</v>
       </c>
       <c r="H47" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:57</v>
+        <v>2:08</v>
       </c>
       <c r="H48" t="str">
-        <v>Natalie Jane</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-22</v>
@@ -2240,10 +2240,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:13</v>
+        <v>2:57</v>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B50" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-22</v>
@@ -2278,10 +2278,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H50" t="str">
-        <v>David Gilmour</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B51" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-22</v>
@@ -2316,10 +2316,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:57</v>
+        <v>4:12</v>
       </c>
       <c r="H51" t="str">
-        <v>Far Caspian</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-22</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:34</v>
+        <v>3:57</v>
       </c>
       <c r="H52" t="str">
-        <v>Celine Dion</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-22</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:48</v>
+        <v>3:34</v>
       </c>
       <c r="H53" t="str">
-        <v>Harry Styles</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-22</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:58</v>
+        <v>3:48</v>
       </c>
       <c r="H54" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-22</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:33</v>
+        <v>4:58</v>
       </c>
       <c r="H55" t="str">
-        <v>Ellise</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-22</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:01</v>
+        <v>2:33</v>
       </c>
       <c r="H56" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Ellise</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-22</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:56</v>
+        <v>5:01</v>
       </c>
       <c r="H57" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-22</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:54</v>
+        <v>4:56</v>
       </c>
       <c r="H58" t="str">
-        <v>Bebe Rexha</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-22</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H59" t="str">
-        <v>NathanEvanss</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-22</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H60" t="str">
-        <v>R3HAB</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-22</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>R3HAB</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-22</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:16</v>
+        <v>3:21</v>
       </c>
       <c r="H62" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-22</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H63" t="str">
-        <v>Johnny Orlando</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-22</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:29</v>
+        <v>2:41</v>
       </c>
       <c r="H64" t="str">
-        <v>Russell Dickerson</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-22</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H65" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-22</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:46</v>
+        <v>2:43</v>
       </c>
       <c r="H66" t="str">
-        <v>Matt Hansen</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-22</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:01</v>
+        <v>3:46</v>
       </c>
       <c r="H67" t="str">
-        <v>Mike Posner</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-22</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H68" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-22</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H69" t="str">
-        <v>almost monday</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-22</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H70" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>almost monday</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-22</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H71" t="str">
-        <v>vaultboy</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-22</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H72" t="str">
-        <v>The Warning</v>
+        <v>vaultboy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-22</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="H73" t="str">
-        <v>aron!</v>
+        <v>The Warning</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-22</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:43</v>
+        <v>2:14</v>
       </c>
       <c r="H74" t="str">
-        <v>Bazzi</v>
+        <v>aron!</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-22</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Sting</v>
+        <v>Bazzi</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-22</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:44</v>
+        <v>4:43</v>
       </c>
       <c r="H76" t="str">
-        <v>Dean Lewis</v>
+        <v>Sting</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-22</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>2:44</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-22</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:52</v>
+        <v>4:37</v>
       </c>
       <c r="H78" t="str">
-        <v>Cannons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-22</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:13</v>
+        <v>4:52</v>
       </c>
       <c r="H79" t="str">
-        <v>Kim Petras</v>
+        <v>Cannons</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-22</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:19</v>
+        <v>2:13</v>
       </c>
       <c r="H80" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-22</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:31</v>
+        <v>3:19</v>
       </c>
       <c r="H81" t="str">
-        <v>Kiana Ledé</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-22</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>2:31</v>
       </c>
       <c r="H82" t="str">
-        <v>Ringo Starr</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-22</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>2:43</v>
       </c>
       <c r="H83" t="str">
-        <v>Maya Hawke</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-22</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:55</v>
+        <v>3:10</v>
       </c>
       <c r="H84" t="str">
-        <v>Armin van Buuren</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-22</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:52</v>
+        <v>3:55</v>
       </c>
       <c r="H85" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-22</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:53</v>
+        <v>3:52</v>
       </c>
       <c r="H86" t="str">
-        <v>Peter Gabriel</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-22</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:30</v>
+        <v>2:53</v>
       </c>
       <c r="H87" t="str">
-        <v>Jessie J</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-22</v>
@@ -3722,10 +3722,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:18</v>
+        <v>4:30</v>
       </c>
       <c r="H88" t="str">
-        <v>Harry Styles</v>
+        <v>Jessie J</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-22</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H89" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-22</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H90" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-22</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H91" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-22</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H92" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-22</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H93" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-22</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H94" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-22</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H95" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-22</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H96" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-22</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H97" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-22</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H98" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-22</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H99" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-22</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H100" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-22</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H101" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SWIM</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>ARIRANG</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:39</v>
+        <v>3:40</v>
       </c>
       <c r="H102" t="str">
-        <v>BTS</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>SWIM - BTS</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>SWIM</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G103" t="str">
-        <v>5:01</v>
+        <v>2:39</v>
       </c>
       <c r="H103" t="str">
-        <v>RAYE</v>
+        <v>BTS</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L103" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Loving Life Again</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G104" t="str">
-        <v>3:46</v>
+        <v>5:01</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>RAYE</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L104" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Rethink Some Things</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>Dandelion</v>
       </c>
       <c r="G105" t="str">
-        <v>2:45</v>
+        <v>3:46</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L105" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TRANKAITO</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G106" t="str">
-        <v>2:42</v>
+        <v>2:45</v>
       </c>
       <c r="H106" t="str">
-        <v>Feid</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L106" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Leak It</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Leak It - Single</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G107" t="str">
-        <v>3:03</v>
+        <v>2:42</v>
       </c>
       <c r="H107" t="str">
-        <v>FLO</v>
+        <v>Feid</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L107" t="str">
-        <v>Leak It - FLO</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>LUVAGIRL</v>
+        <v>Leak It</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:40</v>
+        <v>3:03</v>
       </c>
       <c r="H108" t="str">
-        <v>Coco Jones</v>
+        <v>FLO</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L108" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>D33P3R</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>R3SET</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:25</v>
+        <v>2:40</v>
       </c>
       <c r="H109" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L109" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>D33P3R</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>R3SET</v>
       </c>
       <c r="G110" t="str">
-        <v>3:01</v>
+        <v>3:25</v>
       </c>
       <c r="H110" t="str">
-        <v>Yeat</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L110" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Don't Hate Me</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:09</v>
+        <v>3:01</v>
       </c>
       <c r="H111" t="str">
-        <v>Miles Caton</v>
+        <v>Yeat</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L111" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Pongo</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Pongo - Single</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G112" t="str">
         <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Rvssian</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L112" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>BOTERO</v>
+        <v>Pongo</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>BOTERO - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:14</v>
+        <v>3:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Maluma</v>
+        <v>Rvssian</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L113" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Distance</v>
+        <v>BOTERO</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Distance - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Finn Askew</v>
+        <v>Maluma</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L114" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Distance</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H115" t="str">
-        <v>Dionne Warwick</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L115" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H116" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L116" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2.0</v>
+        <v>Riptides</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>ARIRANG</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G117" t="str">
-        <v>2:49</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>BTS</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L117" t="str">
-        <v>2.0 - BTS</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>6IXER PARTY</v>
+        <v>2.0</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>6WA</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G118" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H118" t="str">
-        <v>BigXthaPlug</v>
+        <v>BTS</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L118" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Highest</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Detour</v>
+        <v>6WA</v>
       </c>
       <c r="G119" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H119" t="str">
-        <v>Samara Cyn</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L119" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>Highest</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Detour</v>
       </c>
       <c r="G120" t="str">
-        <v>2:40</v>
+        <v>2:56</v>
       </c>
       <c r="H120" t="str">
-        <v>Coi Leray</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>So What</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:31</v>
+        <v>2:40</v>
       </c>
       <c r="H121" t="str">
-        <v>MUNA</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L121" t="str">
-        <v>So What - MUNA</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>So What</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G122" t="str">
-        <v>3:12</v>
+        <v>4:31</v>
       </c>
       <c r="H122" t="str">
-        <v>Eli</v>
+        <v>MUNA</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L122" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Running To Pain</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>So Help Me God</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G123" t="str">
-        <v>4:06</v>
+        <v>3:12</v>
       </c>
       <c r="H123" t="str">
-        <v>Kelsey Lu</v>
+        <v>Eli</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L123" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G124" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H124" t="str">
-        <v>Anitta</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L124" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Big Mama</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:20</v>
+        <v>2:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Latto</v>
+        <v>Anitta</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L125" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Bird Flu</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-22</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Big Mama</v>
       </c>
       <c r="G126" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H126" t="str">
-        <v>6LACK</v>
+        <v>Latto</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L126" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Lighter</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G127" t="str">
-        <v>2:59</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>Jelly Roll</v>
+        <v>6LACK</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L127" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Wide Awake</v>
+        <v>Lighter</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:16</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>Chris Stussy</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L128" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Lizzo</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L129" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:34</v>
+        <v>3:25</v>
       </c>
       <c r="H130" t="str">
-        <v>Niall Horan</v>
+        <v>Lizzo</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L130" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>NORMAL</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>ARIRANG</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G131" t="str">
-        <v>3:01</v>
+        <v>2:34</v>
       </c>
       <c r="H131" t="str">
-        <v>BTS</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L131" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Die Living</v>
+        <v>NORMAL</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Die Living - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>3:01</v>
       </c>
       <c r="H132" t="str">
-        <v>ILLENIUM</v>
+        <v>BTS</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L132" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Heaven On Earth</v>
+        <v>Die Living</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:59</v>
+        <v>2:50</v>
       </c>
       <c r="H133" t="str">
-        <v>Pentatonix</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L133" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>an apple a day</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>an apple a day - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>5:16</v>
+        <v>2:59</v>
       </c>
       <c r="H134" t="str">
-        <v>horsegiirL</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L134" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>OUT LATE.</v>
+        <v>an apple a day</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:09</v>
+        <v>5:16</v>
       </c>
       <c r="H135" t="str">
-        <v>Loud Luxury</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L135" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Be With You</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>The Wow! Signal</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:35</v>
+        <v>2:09</v>
       </c>
       <c r="H136" t="str">
-        <v>Muse</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L136" t="str">
-        <v>Be With You - Muse</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>First Red Rays</v>
+        <v>Be With You</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G137" t="str">
-        <v>8:27</v>
+        <v>3:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Neurosis</v>
+        <v>Muse</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L137" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Caught In The Echo</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Your Favorite Toy</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G138" t="str">
-        <v>4:02</v>
+        <v>8:27</v>
       </c>
       <c r="H138" t="str">
-        <v>Foo Fighters</v>
+        <v>Neurosis</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L138" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Little by Little</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Little by Little - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G139" t="str">
-        <v>2:34</v>
+        <v>4:02</v>
       </c>
       <c r="H139" t="str">
-        <v>Mon Rovîa</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L139" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Montgomery County</v>
+        <v>Little by Little</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:28</v>
+        <v>2:34</v>
       </c>
       <c r="H140" t="str">
-        <v>Parker McCollum</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L140" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dive Into Me</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H141" t="str">
-        <v>Alok</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L141" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>more than just a little bit</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>getting up to no good</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H142" t="str">
-        <v>Artemas</v>
+        <v>Alok</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L142" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>WORSHIP</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>WORSHIP - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G143" t="str">
-        <v>2:43</v>
+        <v>2:40</v>
       </c>
       <c r="H143" t="str">
-        <v>Asake</v>
+        <v>Artemas</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L143" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Honest</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Honest - Single</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:22</v>
+        <v>2:43</v>
       </c>
       <c r="H144" t="str">
-        <v>Ebony Riley</v>
+        <v>Asake</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L144" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>6ft Under</v>
+        <v>Honest</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>6ft Under - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H145" t="str">
-        <v>KELS</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L145" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Maybe Again</v>
+        <v>6ft Under</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>When The City Sleeps</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H146" t="str">
-        <v>Alex Isley</v>
+        <v>KELS</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L146" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Trigger Happy</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Attachment Theory</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>3:29</v>
       </c>
       <c r="H147" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L147" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G148" t="str">
         <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Kid Cudi</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L148" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H149" t="str">
-        <v>Swae Lee</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L149" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Runnin' On E</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G150" t="str">
-        <v>2:27</v>
+        <v>3:30</v>
       </c>
       <c r="H150" t="str">
-        <v>Wyatt Flores</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L150" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>FREESTYLE</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LINAJE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:36</v>
+        <v>2:27</v>
       </c>
       <c r="H151" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L151" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Orcasitas</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Alma De Cántaro</v>
+        <v>LINAJE</v>
       </c>
       <c r="G152" t="str">
-        <v>3:23</v>
+        <v>5:36</v>
       </c>
       <c r="H152" t="str">
-        <v>marquitos</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L152" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Vida Loca</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G153" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H153" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>marquitos</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L153" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>The Weight of the Woods</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G154" t="str">
-        <v>3:39</v>
+        <v>2:35</v>
       </c>
       <c r="H154" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L154" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Honest</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G155" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H155" t="str">
-        <v>Kenia Os</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L155" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Peaches!</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G156" t="str">
-        <v>5:00</v>
+        <v>3:01</v>
       </c>
       <c r="H156" t="str">
-        <v>The Black Keys</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L156" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Light as a Feather</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Everything Glows</v>
+        <v>Peaches!</v>
       </c>
       <c r="G157" t="str">
-        <v>3:36</v>
+        <v>5:00</v>
       </c>
       <c r="H157" t="str">
-        <v>Cannons</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L157" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Loving One</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Loving One - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H158" t="str">
-        <v>People I’ve Met</v>
+        <v>Cannons</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L158" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Both Can Be True</v>
+        <v>Loving One</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H159" t="str">
-        <v>Trousdale</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L159" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Buffalo 66</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>4:27</v>
+        <v>3:05</v>
       </c>
       <c r="H160" t="str">
-        <v>Nessa Barrett</v>
+        <v>Trousdale</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L160" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>brb</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>brb - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G161" t="str">
-        <v>2:36</v>
+        <v>4:27</v>
       </c>
       <c r="H161" t="str">
-        <v>The Two Lips</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L161" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Euphoria</v>
+        <v>brb</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Euphoria - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H162" t="str">
-        <v>Talia Rae</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L162" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>if i'm lucky</v>
+        <v>Euphoria</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H163" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L163" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Gracie</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>F.I.G</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H164" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L164" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>down under</v>
+        <v>Gracie</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>down under - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>2:54</v>
       </c>
       <c r="H165" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L165" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Send Me A Sign</v>
+        <v>down under</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>down under - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H166" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L166" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:02</v>
+        <v>3:15</v>
       </c>
       <c r="H167" t="str">
-        <v>OneRepublic</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L167" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Dream Chaser</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dream Chaser</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Willie Nelson</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L168" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Trouble</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Girlfriend</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G169" t="str">
-        <v>3:17</v>
+        <v>3:14</v>
       </c>
       <c r="H169" t="str">
-        <v>Grace Ives</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L169" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>judas</v>
+        <v>Trouble</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>judas - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G170" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H170" t="str">
-        <v>Josiah Queen</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L170" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>JINX</v>
+        <v>judas</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>JINX - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:54</v>
+        <v>3:31</v>
       </c>
       <c r="H171" t="str">
-        <v>Zacari</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L171" t="str">
-        <v>JINX - Zacari</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>se fue</v>
+        <v>JINX</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Náufrago</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H172" t="str">
-        <v>Eddy</v>
+        <v>Zacari</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L172" t="str">
-        <v>se fue - Eddy</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>The Blade</v>
+        <v>se fue</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>The Blade - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G173" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H173" t="str">
-        <v>Kingfishr</v>
+        <v>Eddy</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L173" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Metric Rules</v>
+        <v>The Blade</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H174" t="str">
-        <v>SPINALL</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L174" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>2:15</v>
+        <v>3:13</v>
       </c>
       <c r="H175" t="str">
-        <v>ZEP</v>
+        <v>SPINALL</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L175" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:23</v>
+        <v>2:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Hutch</v>
+        <v>ZEP</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L176" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>5:15</v>
+        <v>3:23</v>
       </c>
       <c r="H177" t="str">
-        <v>MJ Cole</v>
+        <v>Hutch</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L177" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cyclone</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Loss</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:33</v>
+        <v>5:15</v>
       </c>
       <c r="H178" t="str">
-        <v>Gaerea</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L178" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Checkmate</v>
+        <v>Cyclone</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Checkmate - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>5:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Blue Medusa</v>
+        <v>Gaerea</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L179" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>DAVE</v>
+        <v>Checkmate</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>DAVE - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:01</v>
+        <v>4:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Hulvey</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L180" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Change</v>
+        <v>DAVE</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Change - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:38</v>
+        <v>2:01</v>
       </c>
       <c r="H181" t="str">
-        <v>Stephen Stanley</v>
+        <v>Hulvey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L181" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Te Entiendo</v>
+        <v>Change</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:05</v>
+        <v>2:38</v>
       </c>
       <c r="H182" t="str">
-        <v>Maisak</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L182" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>V</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:01</v>
+        <v>3:05</v>
       </c>
       <c r="H183" t="str">
-        <v>Rey Quinto</v>
+        <v>Maisak</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L183" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tirabalas</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>V</v>
       </c>
       <c r="G184" t="str">
-        <v>3:53</v>
+        <v>2:01</v>
       </c>
       <c r="H184" t="str">
-        <v>Hans el Oso</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L184" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>punchbowl</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>punchbowl - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G185" t="str">
-        <v>2:34</v>
+        <v>3:53</v>
       </c>
       <c r="H185" t="str">
-        <v>Julio Caesar</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L185" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Wild Ride</v>
+        <v>punchbowl</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Wild Ride - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>2:34</v>
       </c>
       <c r="H186" t="str">
-        <v>Durand Bernarr</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L186" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Lamb Chop</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:03</v>
+        <v>3:41</v>
       </c>
       <c r="H187" t="str">
-        <v>Chuckyy</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L187" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Free Nick</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Free Nick - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:05</v>
+        <v>2:03</v>
       </c>
       <c r="H188" t="str">
-        <v>Raq baby</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L188" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Make Me Brand New</v>
+        <v>Free Nick</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:06</v>
+        <v>2:05</v>
       </c>
       <c r="H189" t="str">
-        <v>Dante’ Pride</v>
+        <v>Raq baby</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L189" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Define You</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Define You - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:34</v>
+        <v>3:06</v>
       </c>
       <c r="H190" t="str">
-        <v>Luca Fogale</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L190" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>If You Change</v>
+        <v>Define You</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Roses</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:41</v>
+        <v>3:34</v>
       </c>
       <c r="H191" t="str">
-        <v>Widowspeak</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L191" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>What I See</v>
+        <v>If You Change</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G192" t="str">
-        <v>2:32</v>
+        <v>4:41</v>
       </c>
       <c r="H192" t="str">
-        <v>See You Next Year</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L192" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Witching Hour</v>
+        <v>What I See</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Butterfly</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:47</v>
+        <v>2:32</v>
       </c>
       <c r="H193" t="str">
-        <v>Witch Post</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L193" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Actin' Tough</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G194" t="str">
-        <v>3:07</v>
+        <v>3:47</v>
       </c>
       <c r="H194" t="str">
-        <v>Dean Turnley</v>
+        <v>Witch Post</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L194" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H195" t="str">
-        <v>Anais Cardot</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L195" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rewind It</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-22</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Rewind It - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>1:34</v>
+        <v>2:52</v>
       </c>
       <c r="H196" t="str">
-        <v>Nino Paid</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L196" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Turn It Up</v>
+        <v>Rewind It</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-22</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:33</v>
+        <v>1:34</v>
       </c>
       <c r="H197" t="str">
-        <v>slayr</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L197" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Down</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-22</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Down - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:08</v>
+        <v>2:33</v>
       </c>
       <c r="H198" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L198" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Make It Out</v>
+        <v>Down</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-22</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Make It Out - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:17</v>
+        <v>2:08</v>
       </c>
       <c r="H199" t="str">
-        <v>Trueblood</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L199" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>better than boston</v>
+        <v>Make It Out</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-22</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>better than boston - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:02</v>
+        <v>2:17</v>
       </c>
       <c r="H200" t="str">
-        <v>Tom Siletto</v>
+        <v>Trueblood</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L200" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>better than boston</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-22</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H201" t="str">
-        <v>Lost Frequencies</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L201" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>All I Need</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-22</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>All I Need - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>2:34</v>
       </c>
       <c r="H202" t="str">
-        <v>GRiZ</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L202" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Weeping Tones</v>
+        <v>All I Need</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-22</v>
@@ -8089,68 +8089,106 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Peace In Place</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H203" t="str">
-        <v>Poison the Well</v>
+        <v>GRiZ</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L203" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D204" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
+      <c r="D205" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G204" t="str">
+      <c r="G205" t="str">
         <v>5:19</v>
       </c>
-      <c r="H204" t="str">
+      <c r="H205" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K204" t="str">
+      <c r="K205" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L204" t="str">
+      <c r="L205" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אושר כהן – כולם גנבים</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-22</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a9%d7%a8-%d7%9b%d7%94%d7%9f-%d7%9b%d7%95%d7%9c%d7%9d-%d7%92%d7%a0%d7%91%d7%99%d7%9d/</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אושר כהן שר דינמיקה זוגית לא בריאה, כמעט ממכרת בשיר פופ ים־תיכוני  שמשלב בין רגש גולמי, דרמה קולית והפקה עכשווית בשיר המתאר מערכת יחסים רעילה בגיל צעיר ליבת השיר היא מערכת יחסים סוערת שמבוססת על משיכה–דחייה: מצד אחד: "אני אוהב</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אושר כהן – כולם גנבים</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-22</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H3" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-22</v>
@@ -530,10 +530,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H4" t="str">
-        <v>Nick Carter</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-22</v>
@@ -568,10 +568,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:38</v>
+        <v>4:11</v>
       </c>
       <c r="H5" t="str">
-        <v>Carly Pearce</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-22</v>
@@ -606,10 +606,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:11</v>
+        <v>2:57</v>
       </c>
       <c r="H6" t="str">
-        <v>OneRepublic</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-22</v>
@@ -644,10 +644,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:57</v>
+        <v>3:47</v>
       </c>
       <c r="H7" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-22</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:47</v>
+        <v>7:10</v>
       </c>
       <c r="H8" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-22</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:10</v>
+        <v>3:06</v>
       </c>
       <c r="H9" t="str">
-        <v>David Gilmour</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-22</v>
@@ -758,10 +758,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:06</v>
+        <v>3:05</v>
       </c>
       <c r="H10" t="str">
-        <v>Grace Enger</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-22</v>
@@ -796,10 +796,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H11" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-22</v>
@@ -834,10 +834,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:12</v>
+        <v>9:11</v>
       </c>
       <c r="H12" t="str">
-        <v>Freya Ridings</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-22</v>
@@ -872,10 +872,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>9:11</v>
+        <v>3:49</v>
       </c>
       <c r="H13" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-22</v>
@@ -910,10 +910,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:49</v>
+        <v>3:28</v>
       </c>
       <c r="H14" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-22</v>
@@ -948,10 +948,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H15" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-22</v>
@@ -986,10 +986,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:31</v>
+        <v>3:11</v>
       </c>
       <c r="H16" t="str">
-        <v>Martin Garrix</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-22</v>
@@ -1024,10 +1024,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:11</v>
+        <v>2:27</v>
       </c>
       <c r="H17" t="str">
-        <v>Baby Queen</v>
+        <v>HAUSER</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-22</v>
@@ -1062,10 +1062,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-22</v>
@@ -1100,10 +1100,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:34</v>
+        <v>2:50</v>
       </c>
       <c r="H19" t="str">
-        <v>Holly Humberstone</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-22</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H20" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-22</v>
@@ -1176,10 +1176,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:51</v>
+        <v>2:39</v>
       </c>
       <c r="H21" t="str">
-        <v>Rick Astley</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-22</v>
@@ -1214,10 +1214,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:39</v>
+        <v>5:08</v>
       </c>
       <c r="H22" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Jessie J</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-22</v>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:08</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Jessie J</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-22</v>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H24" t="str">
-        <v>Bishop Briggs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-22</v>
@@ -1328,10 +1328,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:42</v>
+        <v>2:31</v>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-22</v>
@@ -1366,10 +1366,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:31</v>
+        <v>3:14</v>
       </c>
       <c r="H26" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-22</v>
@@ -1404,10 +1404,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H27" t="str">
-        <v>Luke Combs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-22</v>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H28" t="str">
-        <v>Allison Russell</v>
+        <v>We Three</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-22</v>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:43</v>
+        <v>2:54</v>
       </c>
       <c r="H29" t="str">
-        <v>We Three</v>
+        <v>paris jackson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-22</v>
@@ -1518,10 +1518,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H30" t="str">
-        <v>paris jackson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-22</v>
@@ -1556,10 +1556,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:46</v>
+        <v>3:37</v>
       </c>
       <c r="H31" t="str">
-        <v>Kane Brown</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-22</v>
@@ -1594,10 +1594,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Lainey Wilson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-22</v>
@@ -1632,10 +1632,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H33" t="str">
-        <v>Malcolm Todd</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-22</v>
@@ -1670,10 +1670,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:38</v>
+        <v>4:29</v>
       </c>
       <c r="H34" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Kungs</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-22</v>
@@ -1708,10 +1708,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:29</v>
+        <v>4:28</v>
       </c>
       <c r="H35" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-22</v>
@@ -1746,10 +1746,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:28</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>Sunday (1994)</v>
+        <v>aron!</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-22</v>
@@ -1784,10 +1784,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H37" t="str">
-        <v>aron!</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-22</v>
@@ -1822,10 +1822,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:51</v>
+        <v>2:49</v>
       </c>
       <c r="H38" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-22</v>
@@ -1860,10 +1860,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H39" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-22</v>
@@ -1901,7 +1901,7 @@
         <v>4:16</v>
       </c>
       <c r="H40" t="str">
-        <v>Owen Riegling</v>
+        <v>LANY</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-22</v>
@@ -1936,10 +1936,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H41" t="str">
-        <v>LANY</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-22</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H42" t="str">
-        <v>Maverick Sabre</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-22</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:50</v>
+        <v>3:57</v>
       </c>
       <c r="H43" t="str">
-        <v>Amanda Jordan</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-22</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:57</v>
+        <v>3:58</v>
       </c>
       <c r="H44" t="str">
-        <v>Beabadoobee</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-22</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:58</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>Spacey Jane</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H46" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-22</v>
@@ -2164,10 +2164,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H47" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H48" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-22</v>
@@ -2240,10 +2240,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H49" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-22</v>
@@ -2278,10 +2278,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H50" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-22</v>
@@ -2316,10 +2316,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H51" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-22</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H52" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-22</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H53" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-22</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-22</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-22</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H56" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-22</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:01</v>
+        <v>4:56</v>
       </c>
       <c r="H57" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-22</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:56</v>
+        <v>2:54</v>
       </c>
       <c r="H58" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-22</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H59" t="str">
-        <v>Bebe Rexha</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-22</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>NathanEvanss</v>
+        <v>R3HAB</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-22</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H61" t="str">
-        <v>R3HAB</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-22</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H62" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-22</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H63" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-22</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:41</v>
+        <v>2:29</v>
       </c>
       <c r="H64" t="str">
-        <v>Johnny Orlando</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-22</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Russell Dickerson</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-22</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H66" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-22</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H67" t="str">
-        <v>Matt Hansen</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-22</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H68" t="str">
-        <v>Mike Posner</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-22</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Katelyn Tarver</v>
+        <v>almost monday</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-22</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-22</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H71" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-22</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H72" t="str">
-        <v>vaultboy</v>
+        <v>The Warning</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-22</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H73" t="str">
-        <v>The Warning</v>
+        <v>aron!</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-22</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H74" t="str">
-        <v>aron!</v>
+        <v>Bazzi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-22</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Bazzi</v>
+        <v>Sting</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-22</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:43</v>
+        <v>2:44</v>
       </c>
       <c r="H76" t="str">
-        <v>Sting</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-22</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:44</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-22</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:37</v>
+        <v>4:52</v>
       </c>
       <c r="H78" t="str">
-        <v>Jessie Ware</v>
+        <v>Cannons</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-22</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:52</v>
+        <v>2:13</v>
       </c>
       <c r="H79" t="str">
-        <v>Cannons</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-22</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H80" t="str">
-        <v>Kim Petras</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-22</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:19</v>
+        <v>2:31</v>
       </c>
       <c r="H81" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-22</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:31</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-22</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Ringo Starr</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-22</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:10</v>
+        <v>3:55</v>
       </c>
       <c r="H84" t="str">
-        <v>Maya Hawke</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-22</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:55</v>
+        <v>3:52</v>
       </c>
       <c r="H85" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-22</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:52</v>
+        <v>2:53</v>
       </c>
       <c r="H86" t="str">
-        <v>Demi Lovato</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-22</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:53</v>
+        <v>4:30</v>
       </c>
       <c r="H87" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie J</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B88" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-22</v>
@@ -3722,10 +3722,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:30</v>
+        <v>5:18</v>
       </c>
       <c r="H88" t="str">
-        <v>Jessie J</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-22</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-22</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-22</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H91" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-22</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H92" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-22</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H93" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-22</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-22</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H95" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-22</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H96" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-22</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H97" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-22</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-22</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H99" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-22</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H100" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-22</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H101" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>SWIM</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G102" t="str">
-        <v>3:40</v>
+        <v>2:39</v>
       </c>
       <c r="H102" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>BTS</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L102" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SWIM</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ARIRANG</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G103" t="str">
-        <v>2:39</v>
+        <v>5:01</v>
       </c>
       <c r="H103" t="str">
-        <v>BTS</v>
+        <v>RAYE</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L103" t="str">
-        <v>SWIM - BTS</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>5:01</v>
+        <v>3:46</v>
       </c>
       <c r="H104" t="str">
-        <v>RAYE</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Loving Life Again</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dandelion</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G105" t="str">
-        <v>3:46</v>
+        <v>2:45</v>
       </c>
       <c r="H105" t="str">
-        <v>Ella Langley</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L105" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Rethink Some Things</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Way I Am</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G106" t="str">
-        <v>2:45</v>
+        <v>2:42</v>
       </c>
       <c r="H106" t="str">
-        <v>Luke Combs</v>
+        <v>Feid</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L106" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>TRANKAITO</v>
+        <v>Leak It</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:42</v>
+        <v>3:03</v>
       </c>
       <c r="H107" t="str">
-        <v>Feid</v>
+        <v>FLO</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L107" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Leak It</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Leak It - Single</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:03</v>
+        <v>2:40</v>
       </c>
       <c r="H108" t="str">
-        <v>FLO</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L108" t="str">
-        <v>Leak It - FLO</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>LUVAGIRL</v>
+        <v>D33P3R</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>R3SET</v>
       </c>
       <c r="G109" t="str">
-        <v>2:40</v>
+        <v>3:25</v>
       </c>
       <c r="H109" t="str">
-        <v>Coco Jones</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L109" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>D33P3R</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>R3SET</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:25</v>
+        <v>3:01</v>
       </c>
       <c r="H110" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Yeat</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L110" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:01</v>
+        <v>3:09</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L111" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Don't Hate Me</v>
+        <v>Pongo</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G112" t="str">
         <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Miles Caton</v>
+        <v>Rvssian</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L112" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Pongo</v>
+        <v>BOTERO</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Pongo - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:09</v>
+        <v>4:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Rvssian</v>
+        <v>Maluma</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L113" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>BOTERO</v>
+        <v>Distance</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>BOTERO - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:14</v>
+        <v>3:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L114" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Distance</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Distance - Single</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:14</v>
+        <v>3:44</v>
       </c>
       <c r="H115" t="str">
-        <v>Finn Askew</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L115" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Riptides</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G116" t="str">
-        <v>3:44</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>Dionne Warwick</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L116" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Riptides</v>
+        <v>2.0</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>I Built You a Tower</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>2:49</v>
       </c>
       <c r="H117" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>BTS</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L117" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2.0</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ARIRANG</v>
+        <v>6WA</v>
       </c>
       <c r="G118" t="str">
-        <v>2:49</v>
+        <v>3:08</v>
       </c>
       <c r="H118" t="str">
-        <v>BTS</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L118" t="str">
-        <v>2.0 - BTS</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>6IXER PARTY</v>
+        <v>Highest</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>6WA</v>
+        <v>Detour</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H119" t="str">
-        <v>BigXthaPlug</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L119" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Highest</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Detour</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:56</v>
+        <v>2:40</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L120" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>So What</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G121" t="str">
-        <v>2:40</v>
+        <v>4:31</v>
       </c>
       <c r="H121" t="str">
-        <v>Coi Leray</v>
+        <v>MUNA</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>So What</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G122" t="str">
-        <v>4:31</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>MUNA</v>
+        <v>Eli</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L122" t="str">
-        <v>So What - MUNA</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G123" t="str">
-        <v>3:12</v>
+        <v>4:06</v>
       </c>
       <c r="H123" t="str">
-        <v>Eli</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L123" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Running To Pain</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>So Help Me God</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:06</v>
+        <v>2:14</v>
       </c>
       <c r="H124" t="str">
-        <v>Kelsey Lu</v>
+        <v>Anitta</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L124" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>4:20</v>
       </c>
       <c r="H125" t="str">
-        <v>Anitta</v>
+        <v>Latto</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L125" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-22</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Big Mama</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G126" t="str">
-        <v>4:20</v>
+        <v>2:58</v>
       </c>
       <c r="H126" t="str">
-        <v>Latto</v>
+        <v>6LACK</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L126" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Bird Flu</v>
+        <v>Lighter</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:59</v>
       </c>
       <c r="H127" t="str">
-        <v>6LACK</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L127" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Lighter</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>4:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Jelly Roll</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L128" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Wide Awake</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>Chris Stussy</v>
+        <v>Lizzo</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L129" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G130" t="str">
-        <v>3:25</v>
+        <v>2:34</v>
       </c>
       <c r="H130" t="str">
-        <v>Lizzo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L130" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Dinner Party</v>
+        <v>NORMAL</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Dinner Party</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G131" t="str">
-        <v>2:34</v>
+        <v>3:01</v>
       </c>
       <c r="H131" t="str">
-        <v>Niall Horan</v>
+        <v>BTS</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L131" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>NORMAL</v>
+        <v>Die Living</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ARIRANG</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>BTS</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L132" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Die Living</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Die Living - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:50</v>
+        <v>2:59</v>
       </c>
       <c r="H133" t="str">
-        <v>ILLENIUM</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L133" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Heaven On Earth</v>
+        <v>an apple a day</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:59</v>
+        <v>5:16</v>
       </c>
       <c r="H134" t="str">
-        <v>Pentatonix</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L134" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>an apple a day</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>an apple a day - Single</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>5:16</v>
+        <v>2:09</v>
       </c>
       <c r="H135" t="str">
-        <v>horsegiirL</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L135" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>OUT LATE.</v>
+        <v>Be With You</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G136" t="str">
-        <v>2:09</v>
+        <v>3:35</v>
       </c>
       <c r="H136" t="str">
-        <v>Loud Luxury</v>
+        <v>Muse</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L136" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Be With You</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Wow! Signal</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G137" t="str">
-        <v>3:35</v>
+        <v>8:27</v>
       </c>
       <c r="H137" t="str">
-        <v>Muse</v>
+        <v>Neurosis</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L137" t="str">
-        <v>Be With You - Muse</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>First Red Rays</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G138" t="str">
-        <v>8:27</v>
+        <v>4:02</v>
       </c>
       <c r="H138" t="str">
-        <v>Neurosis</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L138" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Caught In The Echo</v>
+        <v>Little by Little</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>4:02</v>
+        <v>2:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Foo Fighters</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L139" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Little by Little</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Little by Little - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:34</v>
+        <v>3:28</v>
       </c>
       <c r="H140" t="str">
-        <v>Mon Rovîa</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L140" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Montgomery County</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:28</v>
+        <v>2:46</v>
       </c>
       <c r="H141" t="str">
-        <v>Parker McCollum</v>
+        <v>Alok</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L141" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Dive Into Me</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G142" t="str">
-        <v>2:46</v>
+        <v>2:40</v>
       </c>
       <c r="H142" t="str">
-        <v>Alok</v>
+        <v>Artemas</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L142" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>more than just a little bit</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>getting up to no good</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:40</v>
+        <v>2:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Artemas</v>
+        <v>Asake</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L143" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>WORSHIP</v>
+        <v>Honest</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>WORSHIP - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:43</v>
+        <v>3:22</v>
       </c>
       <c r="H144" t="str">
-        <v>Asake</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L144" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Honest</v>
+        <v>6ft Under</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Honest - Single</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:22</v>
+        <v>3:30</v>
       </c>
       <c r="H145" t="str">
-        <v>Ebony Riley</v>
+        <v>KELS</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L145" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>6ft Under</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>6ft Under - Single</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G146" t="str">
-        <v>3:30</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>KELS</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L146" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Maybe Again</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>When The City Sleeps</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G147" t="str">
-        <v>3:29</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>Alex Isley</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L147" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Trigger Happy</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Attachment Theory</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G148" t="str">
         <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L148" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G149" t="str">
-        <v>3:01</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Kid Cudi</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L149" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:30</v>
+        <v>2:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Swae Lee</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L150" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Runnin' On E</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>LINAJE</v>
       </c>
       <c r="G151" t="str">
-        <v>2:27</v>
+        <v>5:36</v>
       </c>
       <c r="H151" t="str">
-        <v>Wyatt Flores</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L151" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>FREESTYLE</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>LINAJE</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G152" t="str">
-        <v>5:36</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>marquitos</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L152" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Orcasitas</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Alma De Cántaro</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G153" t="str">
-        <v>3:23</v>
+        <v>2:35</v>
       </c>
       <c r="H153" t="str">
-        <v>marquitos</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L153" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Vida Loca</v>
+        <v>Honest</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>FREE SPIRITS</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G154" t="str">
-        <v>2:35</v>
+        <v>3:39</v>
       </c>
       <c r="H154" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L154" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Honest</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>The Weight of the Woods</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:39</v>
+        <v>3:01</v>
       </c>
       <c r="H155" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L155" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Peaches!</v>
       </c>
       <c r="G156" t="str">
-        <v>3:01</v>
+        <v>5:00</v>
       </c>
       <c r="H156" t="str">
-        <v>Kenia Os</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L156" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Peaches!</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G157" t="str">
-        <v>5:00</v>
+        <v>3:36</v>
       </c>
       <c r="H157" t="str">
-        <v>The Black Keys</v>
+        <v>Cannons</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L157" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Light as a Feather</v>
+        <v>Loving One</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Everything Glows</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Cannons</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L158" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Loving One</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Loving One - Single</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:39</v>
+        <v>3:05</v>
       </c>
       <c r="H159" t="str">
-        <v>People I’ve Met</v>
+        <v>Trousdale</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L159" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Both Can Be True</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G160" t="str">
-        <v>3:05</v>
+        <v>4:27</v>
       </c>
       <c r="H160" t="str">
-        <v>Trousdale</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L160" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Buffalo 66</v>
+        <v>brb</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>brb - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:27</v>
+        <v>2:36</v>
       </c>
       <c r="H161" t="str">
-        <v>Nessa Barrett</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L161" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>brb</v>
+        <v>Euphoria</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>brb - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:36</v>
+        <v>3:32</v>
       </c>
       <c r="H162" t="str">
-        <v>The Two Lips</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L162" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Euphoria</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Euphoria - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>3:32</v>
+        <v>2:57</v>
       </c>
       <c r="H163" t="str">
-        <v>Talia Rae</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L163" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>if i'm lucky</v>
+        <v>Gracie</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>better late than not at all - EP</v>
+        <v>F.I.G</v>
       </c>
       <c r="G164" t="str">
-        <v>2:57</v>
+        <v>2:54</v>
       </c>
       <c r="H164" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L164" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Gracie</v>
+        <v>down under</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>F.I.G</v>
+        <v>down under - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:54</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>Naomi Scott</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L165" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>down under</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>down under - Single</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L166" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Send Me A Sign</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>3:02</v>
       </c>
       <c r="H167" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L167" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G168" t="str">
-        <v>3:02</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>OneRepublic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L168" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Dream Chaser</v>
+        <v>Trouble</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dream Chaser</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G169" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Willie Nelson</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L169" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Trouble</v>
+        <v>judas</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Girlfriend</v>
+        <v>judas - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Grace Ives</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L170" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>judas</v>
+        <v>JINX</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>judas - Single</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:31</v>
+        <v>2:54</v>
       </c>
       <c r="H171" t="str">
-        <v>Josiah Queen</v>
+        <v>Zacari</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L171" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>JINX</v>
+        <v>se fue</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>JINX - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G172" t="str">
-        <v>2:54</v>
+        <v>2:51</v>
       </c>
       <c r="H172" t="str">
-        <v>Zacari</v>
+        <v>Eddy</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L172" t="str">
-        <v>JINX - Zacari</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>se fue</v>
+        <v>The Blade</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Náufrago</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:51</v>
+        <v>3:15</v>
       </c>
       <c r="H173" t="str">
-        <v>Eddy</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L173" t="str">
-        <v>se fue - Eddy</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Blade</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Blade - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:15</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>Kingfishr</v>
+        <v>SPINALL</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L174" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Metric Rules</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:13</v>
+        <v>2:15</v>
       </c>
       <c r="H175" t="str">
-        <v>SPINALL</v>
+        <v>ZEP</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L175" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:15</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>ZEP</v>
+        <v>Hutch</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L176" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:23</v>
+        <v>5:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Hutch</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L177" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Cyclone</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G178" t="str">
-        <v>5:15</v>
+        <v>5:33</v>
       </c>
       <c r="H178" t="str">
-        <v>MJ Cole</v>
+        <v>Gaerea</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L178" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Cyclone</v>
+        <v>Checkmate</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Loss</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>5:33</v>
+        <v>4:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Gaerea</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L179" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checkmate</v>
+        <v>DAVE</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Checkmate - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:23</v>
+        <v>2:01</v>
       </c>
       <c r="H180" t="str">
-        <v>Blue Medusa</v>
+        <v>Hulvey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L180" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>DAVE</v>
+        <v>Change</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>DAVE - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:01</v>
+        <v>2:38</v>
       </c>
       <c r="H181" t="str">
-        <v>Hulvey</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L181" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Change</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Change - Single</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:38</v>
+        <v>3:05</v>
       </c>
       <c r="H182" t="str">
-        <v>Stephen Stanley</v>
+        <v>Maisak</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L182" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Te Entiendo</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>V</v>
       </c>
       <c r="G183" t="str">
-        <v>3:05</v>
+        <v>2:01</v>
       </c>
       <c r="H183" t="str">
-        <v>Maisak</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L183" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>V</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G184" t="str">
-        <v>2:01</v>
+        <v>3:53</v>
       </c>
       <c r="H184" t="str">
-        <v>Rey Quinto</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L184" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Tirabalas</v>
+        <v>punchbowl</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:53</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>Hans el Oso</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L185" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>punchbowl</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>punchbowl - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:34</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>Julio Caesar</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L186" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Wild Ride</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Wild Ride - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>2:03</v>
       </c>
       <c r="H187" t="str">
-        <v>Durand Bernarr</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L187" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Lamb Chop</v>
+        <v>Free Nick</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:03</v>
+        <v>2:05</v>
       </c>
       <c r="H188" t="str">
-        <v>Chuckyy</v>
+        <v>Raq baby</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L188" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Free Nick</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Free Nick - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:05</v>
+        <v>3:06</v>
       </c>
       <c r="H189" t="str">
-        <v>Raq baby</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L189" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make Me Brand New</v>
+        <v>Define You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:06</v>
+        <v>3:34</v>
       </c>
       <c r="H190" t="str">
-        <v>Dante’ Pride</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L190" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Define You</v>
+        <v>If You Change</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Define You - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G191" t="str">
-        <v>3:34</v>
+        <v>4:41</v>
       </c>
       <c r="H191" t="str">
-        <v>Luca Fogale</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L191" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>If You Change</v>
+        <v>What I See</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Roses</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:41</v>
+        <v>2:32</v>
       </c>
       <c r="H192" t="str">
-        <v>Widowspeak</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L192" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>What I See</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G193" t="str">
-        <v>2:32</v>
+        <v>3:47</v>
       </c>
       <c r="H193" t="str">
-        <v>See You Next Year</v>
+        <v>Witch Post</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L193" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Witching Hour</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Butterfly</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:47</v>
+        <v>3:07</v>
       </c>
       <c r="H194" t="str">
-        <v>Witch Post</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L194" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Actin' Tough</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:07</v>
+        <v>2:52</v>
       </c>
       <c r="H195" t="str">
-        <v>Dean Turnley</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L195" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Rewind It</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-22</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:52</v>
+        <v>1:34</v>
       </c>
       <c r="H196" t="str">
-        <v>Anais Cardot</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L196" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Rewind It</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-22</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Rewind It - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>1:34</v>
+        <v>2:33</v>
       </c>
       <c r="H197" t="str">
-        <v>Nino Paid</v>
+        <v>slayr</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L197" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Turn It Up</v>
+        <v>Down</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-22</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:33</v>
+        <v>2:08</v>
       </c>
       <c r="H198" t="str">
-        <v>slayr</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L198" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Down</v>
+        <v>Make It Out</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-22</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Down - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:08</v>
+        <v>2:17</v>
       </c>
       <c r="H199" t="str">
-        <v>MexikoDro</v>
+        <v>Trueblood</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L199" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Make It Out</v>
+        <v>better than boston</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-22</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Make It Out - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>2:17</v>
+        <v>3:02</v>
       </c>
       <c r="H200" t="str">
-        <v>Trueblood</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L200" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>better than boston</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-22</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>better than boston - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:02</v>
+        <v>2:34</v>
       </c>
       <c r="H201" t="str">
-        <v>Tom Siletto</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L201" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>All I Need</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-22</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>2:34</v>
+        <v>3:06</v>
       </c>
       <c r="H202" t="str">
-        <v>Lost Frequencies</v>
+        <v>GRiZ</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L202" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>All I Need</v>
+        <v>Weeping Tones</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-22</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>All I Need - Single</v>
+        <v>Peace In Place</v>
       </c>
       <c r="G203" t="str">
-        <v>3:06</v>
+        <v>2:59</v>
       </c>
       <c r="H203" t="str">
-        <v>GRiZ</v>
+        <v>Poison the Well</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
       </c>
       <c r="L203" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>Weeping Tones - Poison the Well</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Weeping Tones</v>
+        <v>Promise You This</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-22</v>
@@ -8127,68 +8127,30 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Peace In Place</v>
+        <v>Goliath</v>
       </c>
       <c r="G204" t="str">
-        <v>2:59</v>
+        <v>5:19</v>
       </c>
       <c r="H204" t="str">
-        <v>Poison the Well</v>
+        <v>Exodus</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
       <c r="L204" t="str">
-        <v>Weeping Tones - Poison the Well</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Promise You This</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Goliath</v>
-      </c>
-      <c r="G205" t="str">
-        <v>5:19</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Exodus</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
-      </c>
-      <c r="L205" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L216"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>רני רחמים - עכשיו זה נגמר</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410122&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>רני רחמים - עכשיו זה נגמר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>רגב הוד - תודה לאל קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410121&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-22</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>3:31</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Nick Carter</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>רגב הוד - תודה לאל קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>נתי גדמו - כל מה שבניתי</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410120&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-22</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>3:38</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Carly Pearce</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>נתי גדמו - כל מה שבניתי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>נהוראי אריאלי - זהות בדויה</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410119&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-22</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>4:11</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>OneRepublic</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>נהוראי אריאלי - זהות בדויה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>לידור - כל מה שעשיתי</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410118&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-22</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>2:57</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>לידור - כל מה שעשיתי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>יותם רכס - עסקים כרגיל</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410117&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-22</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:47</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Armin van Buuren</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>יותם רכס - עסקים כרגיל</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>בן צור - אישתי</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410116&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-22</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>7:10</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>David Gilmour</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>בן צור - אישתי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>אתל - טוקסיק</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410115&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-22</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:06</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Grace Enger</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>אתל - טוקסיק</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>ארי ברמן - דור הגאולה</v>
       </c>
       <c r="B10" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410114&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-22</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>3:05</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Tucker Wetmore</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>ארי ברמן - דור הגאולה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>אלה הודיה גוילי - סוף העולם</v>
       </c>
       <c r="B11" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410113&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-22</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>3:12</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Freya Ridings</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>אלה הודיה גוילי - סוף העולם</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>אדל חן - אושר אמיתי</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410112&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-22</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>9:11</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>David Gilmour</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>אדל חן - אושר אמיתי</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>פו פייטרס Caught In The Echo</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>2026-03-22</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-caught-in-the-echo/</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-22</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>אנחנו במרחק של בערך חודש מהוצאת האלבום החדש של פו פייטרס Foo Fighters, שנקרא  Your Favorite Toy, ודייב גרול והלהקה משתפים בסינגל השני – Caught In The Echo. לא היו לי בדיוק ציפיות בשמיים משיר חדש של פו פייטרס  עם</v>
       </c>
       <c r="G13" t="str">
-        <v>3:49</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>SIENNA SPIRO</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>פו פייטרס Caught In The Echo</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-22</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:28</v>
+        <v>3:17</v>
       </c>
       <c r="H14" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B15" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-22</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:31</v>
       </c>
       <c r="H15" t="str">
-        <v>Martin Garrix</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-22</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:11</v>
+        <v>3:38</v>
       </c>
       <c r="H16" t="str">
-        <v>Baby Queen</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-22</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:27</v>
+        <v>4:11</v>
       </c>
       <c r="H17" t="str">
-        <v>HAUSER</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B18" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-22</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:34</v>
+        <v>2:57</v>
       </c>
       <c r="H18" t="str">
-        <v>Holly Humberstone</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-22</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H19" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B20" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-22</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:51</v>
+        <v>7:10</v>
       </c>
       <c r="H20" t="str">
-        <v>Rick Astley</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B21" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-22</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:39</v>
+        <v>3:06</v>
       </c>
       <c r="H21" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-22</v>
@@ -1214,10 +1214,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:08</v>
+        <v>3:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Jessie J</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-22</v>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:46</v>
+        <v>3:12</v>
       </c>
       <c r="H23" t="str">
-        <v>Bishop Briggs</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-22</v>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:42</v>
+        <v>9:11</v>
       </c>
       <c r="H24" t="str">
-        <v>Dean Lewis</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B25" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-22</v>
@@ -1328,10 +1328,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:31</v>
+        <v>3:49</v>
       </c>
       <c r="H25" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B26" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-22</v>
@@ -1366,10 +1366,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:14</v>
+        <v>3:28</v>
       </c>
       <c r="H26" t="str">
-        <v>Luke Combs</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-22</v>
@@ -1404,10 +1404,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H27" t="str">
-        <v>Allison Russell</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-22</v>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:43</v>
+        <v>3:11</v>
       </c>
       <c r="H28" t="str">
-        <v>We Three</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-22</v>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:54</v>
+        <v>2:27</v>
       </c>
       <c r="H29" t="str">
-        <v>paris jackson</v>
+        <v>HAUSER</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B30" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-22</v>
@@ -1518,10 +1518,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:46</v>
+        <v>3:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Kane Brown</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-22</v>
@@ -1556,10 +1556,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:37</v>
+        <v>2:50</v>
       </c>
       <c r="H31" t="str">
-        <v>Lainey Wilson</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-22</v>
@@ -1594,10 +1594,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:57</v>
+        <v>3:51</v>
       </c>
       <c r="H32" t="str">
-        <v>Malcolm Todd</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-22</v>
@@ -1632,10 +1632,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:38</v>
+        <v>2:39</v>
       </c>
       <c r="H33" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B34" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-22</v>
@@ -1670,10 +1670,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:29</v>
+        <v>5:08</v>
       </c>
       <c r="H34" t="str">
-        <v>Kungs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B35" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-22</v>
@@ -1708,10 +1708,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:28</v>
+        <v>3:46</v>
       </c>
       <c r="H35" t="str">
-        <v>Sunday (1994)</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-22</v>
@@ -1746,10 +1746,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:26</v>
+        <v>2:42</v>
       </c>
       <c r="H36" t="str">
-        <v>aron!</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-22</v>
@@ -1784,10 +1784,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:51</v>
+        <v>2:31</v>
       </c>
       <c r="H37" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B38" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-22</v>
@@ -1822,10 +1822,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:49</v>
+        <v>3:14</v>
       </c>
       <c r="H38" t="str">
-        <v>Sunday (1994)</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B39" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-22</v>
@@ -1860,10 +1860,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:16</v>
+        <v>3:22</v>
       </c>
       <c r="H39" t="str">
-        <v>Owen Riegling</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B40" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-22</v>
@@ -1898,10 +1898,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:16</v>
+        <v>3:43</v>
       </c>
       <c r="H40" t="str">
-        <v>LANY</v>
+        <v>We Three</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-22</v>
@@ -1936,10 +1936,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H41" t="str">
-        <v>Maverick Sabre</v>
+        <v>paris jackson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-22</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:50</v>
+        <v>2:46</v>
       </c>
       <c r="H42" t="str">
-        <v>Amanda Jordan</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-22</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:57</v>
+        <v>3:37</v>
       </c>
       <c r="H43" t="str">
-        <v>Beabadoobee</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-22</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:58</v>
+        <v>2:57</v>
       </c>
       <c r="H44" t="str">
-        <v>Spacey Jane</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-22</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:25</v>
+        <v>3:38</v>
       </c>
       <c r="H45" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:09</v>
+        <v>4:29</v>
       </c>
       <c r="H46" t="str">
-        <v>Mei Semones</v>
+        <v>Kungs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-22</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:08</v>
+        <v>4:28</v>
       </c>
       <c r="H47" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H48" t="str">
-        <v>Natalie Jane</v>
+        <v>aron!</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-22</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:13</v>
+        <v>3:51</v>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-22</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>2:49</v>
       </c>
       <c r="H50" t="str">
-        <v>David Gilmour</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-22</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:57</v>
+        <v>4:16</v>
       </c>
       <c r="H51" t="str">
-        <v>Far Caspian</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-22</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:34</v>
+        <v>4:16</v>
       </c>
       <c r="H52" t="str">
-        <v>Celine Dion</v>
+        <v>LANY</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-22</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:48</v>
+        <v>3:25</v>
       </c>
       <c r="H53" t="str">
-        <v>Harry Styles</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-22</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:58</v>
+        <v>2:50</v>
       </c>
       <c r="H54" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-22</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:33</v>
+        <v>3:57</v>
       </c>
       <c r="H55" t="str">
-        <v>Ellise</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-22</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:01</v>
+        <v>3:58</v>
       </c>
       <c r="H56" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-22</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:56</v>
+        <v>3:25</v>
       </c>
       <c r="H57" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-22</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:54</v>
+        <v>4:09</v>
       </c>
       <c r="H58" t="str">
-        <v>Bebe Rexha</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-22</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:46</v>
+        <v>2:08</v>
       </c>
       <c r="H59" t="str">
-        <v>NathanEvanss</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-22</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H60" t="str">
-        <v>R3HAB</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-22</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:21</v>
+        <v>3:13</v>
       </c>
       <c r="H61" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-22</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:16</v>
+        <v>4:12</v>
       </c>
       <c r="H62" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-22</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:41</v>
+        <v>3:57</v>
       </c>
       <c r="H63" t="str">
-        <v>Johnny Orlando</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-22</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:29</v>
+        <v>3:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Russell Dickerson</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-22</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:43</v>
+        <v>3:48</v>
       </c>
       <c r="H65" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-22</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:46</v>
+        <v>4:58</v>
       </c>
       <c r="H66" t="str">
-        <v>Matt Hansen</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-22</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:01</v>
+        <v>2:33</v>
       </c>
       <c r="H67" t="str">
-        <v>Mike Posner</v>
+        <v>Ellise</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-22</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:23</v>
+        <v>5:01</v>
       </c>
       <c r="H68" t="str">
-        <v>Katelyn Tarver</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-22</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:39</v>
+        <v>4:56</v>
       </c>
       <c r="H69" t="str">
-        <v>almost monday</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-22</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:04</v>
+        <v>2:54</v>
       </c>
       <c r="H70" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-22</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:25</v>
+        <v>2:46</v>
       </c>
       <c r="H71" t="str">
-        <v>vaultboy</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-22</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:49</v>
+        <v>2:56</v>
       </c>
       <c r="H72" t="str">
-        <v>The Warning</v>
+        <v>R3HAB</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-22</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:14</v>
+        <v>3:21</v>
       </c>
       <c r="H73" t="str">
-        <v>aron!</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-22</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:43</v>
+        <v>3:16</v>
       </c>
       <c r="H74" t="str">
-        <v>Bazzi</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-22</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:43</v>
+        <v>2:41</v>
       </c>
       <c r="H75" t="str">
-        <v>Sting</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-22</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:44</v>
+        <v>2:29</v>
       </c>
       <c r="H76" t="str">
-        <v>Dean Lewis</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-22</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>2:43</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-22</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:52</v>
+        <v>3:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Cannons</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-22</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:13</v>
+        <v>4:01</v>
       </c>
       <c r="H79" t="str">
-        <v>Kim Petras</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-22</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:19</v>
+        <v>3:23</v>
       </c>
       <c r="H80" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-22</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:31</v>
+        <v>3:39</v>
       </c>
       <c r="H81" t="str">
-        <v>Kiana Ledé</v>
+        <v>almost monday</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-22</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>3:04</v>
       </c>
       <c r="H82" t="str">
-        <v>Ringo Starr</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-22</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>3:25</v>
       </c>
       <c r="H83" t="str">
-        <v>Maya Hawke</v>
+        <v>vaultboy</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-22</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:55</v>
+        <v>3:49</v>
       </c>
       <c r="H84" t="str">
-        <v>Armin van Buuren</v>
+        <v>The Warning</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-22</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:52</v>
+        <v>2:14</v>
       </c>
       <c r="H85" t="str">
-        <v>Demi Lovato</v>
+        <v>aron!</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-22</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:53</v>
+        <v>2:43</v>
       </c>
       <c r="H86" t="str">
-        <v>Peter Gabriel</v>
+        <v>Bazzi</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-22</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H87" t="str">
-        <v>Jessie J</v>
+        <v>Sting</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-22</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:18</v>
+        <v>2:44</v>
       </c>
       <c r="H88" t="str">
-        <v>Harry Styles</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-22</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>7:20</v>
+        <v>4:37</v>
       </c>
       <c r="H89" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-22</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:01</v>
+        <v>4:52</v>
       </c>
       <c r="H90" t="str">
-        <v>BRITs</v>
+        <v>Cannons</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-22</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:31</v>
+        <v>2:13</v>
       </c>
       <c r="H91" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-22</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:00</v>
+        <v>3:19</v>
       </c>
       <c r="H92" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-22</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:11</v>
+        <v>2:31</v>
       </c>
       <c r="H93" t="str">
-        <v>The Kiffness</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-22</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:32</v>
+        <v>2:43</v>
       </c>
       <c r="H94" t="str">
-        <v>Lauv</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-22</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:03</v>
+        <v>3:10</v>
       </c>
       <c r="H95" t="str">
-        <v>RAYE</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-22</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:50</v>
+        <v>3:55</v>
       </c>
       <c r="H96" t="str">
-        <v>Armik</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-22</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:53</v>
+        <v>3:52</v>
       </c>
       <c r="H97" t="str">
-        <v>Scorpions</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-22</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:04</v>
+        <v>2:53</v>
       </c>
       <c r="H98" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-22</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:32</v>
+        <v>4:30</v>
       </c>
       <c r="H99" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Jessie J</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-22</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:47</v>
+        <v>5:18</v>
       </c>
       <c r="H100" t="str">
-        <v>Girl Tones</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-22</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:40</v>
+        <v>7:20</v>
       </c>
       <c r="H101" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SWIM</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>ARIRANG</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:39</v>
+        <v>3:01</v>
       </c>
       <c r="H102" t="str">
-        <v>BTS</v>
+        <v>BRITs</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>SWIM - BTS</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>5:01</v>
+        <v>3:31</v>
       </c>
       <c r="H103" t="str">
-        <v>RAYE</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Loving Life Again</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:46</v>
+        <v>3:00</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Rethink Some Things</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:45</v>
+        <v>3:11</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TRANKAITO</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:42</v>
+        <v>3:32</v>
       </c>
       <c r="H106" t="str">
-        <v>Feid</v>
+        <v>Lauv</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Leak It</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Leak It - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:03</v>
+        <v>5:03</v>
       </c>
       <c r="H107" t="str">
-        <v>FLO</v>
+        <v>RAYE</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Leak It - FLO</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>LUVAGIRL</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:40</v>
+        <v>4:50</v>
       </c>
       <c r="H108" t="str">
-        <v>Coco Jones</v>
+        <v>Armik</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>D33P3R</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>R3SET</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:25</v>
+        <v>4:53</v>
       </c>
       <c r="H109" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Scorpions</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:01</v>
+        <v>3:04</v>
       </c>
       <c r="H110" t="str">
-        <v>Yeat</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Don't Hate Me</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:09</v>
+        <v>4:32</v>
       </c>
       <c r="H111" t="str">
-        <v>Miles Caton</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Pongo</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Pongo - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>3:09</v>
+        <v>3:47</v>
       </c>
       <c r="H112" t="str">
-        <v>Rvssian</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>BOTERO</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>BOTERO - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>4:14</v>
+        <v>3:40</v>
       </c>
       <c r="H113" t="str">
-        <v>Maluma</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Distance</v>
+        <v>SWIM</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Distance - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G114" t="str">
-        <v>3:14</v>
+        <v>2:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Finn Askew</v>
+        <v>BTS</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L114" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G115" t="str">
-        <v>3:44</v>
+        <v>5:01</v>
       </c>
       <c r="H115" t="str">
-        <v>Dionne Warwick</v>
+        <v>RAYE</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L115" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Riptides</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>I Built You a Tower</v>
+        <v>Dandelion</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>3:46</v>
       </c>
       <c r="H116" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L116" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2.0</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>ARIRANG</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G117" t="str">
-        <v>2:49</v>
+        <v>2:45</v>
       </c>
       <c r="H117" t="str">
-        <v>BTS</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L117" t="str">
-        <v>2.0 - BTS</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>6IXER PARTY</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>6WA</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G118" t="str">
-        <v>3:08</v>
+        <v>2:42</v>
       </c>
       <c r="H118" t="str">
-        <v>BigXthaPlug</v>
+        <v>Feid</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L118" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Highest</v>
+        <v>Leak It</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Detour</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:56</v>
+        <v>3:03</v>
       </c>
       <c r="H119" t="str">
-        <v>Samara Cyn</v>
+        <v>FLO</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L119" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G120" t="str">
         <v>2:40</v>
       </c>
       <c r="H120" t="str">
-        <v>Coi Leray</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>So What</v>
+        <v>D33P3R</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Dancing On The Wall</v>
+        <v>R3SET</v>
       </c>
       <c r="G121" t="str">
-        <v>4:31</v>
+        <v>3:25</v>
       </c>
       <c r="H121" t="str">
-        <v>MUNA</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L121" t="str">
-        <v>So What - MUNA</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:12</v>
+        <v>3:01</v>
       </c>
       <c r="H122" t="str">
-        <v>Eli</v>
+        <v>Yeat</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L122" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Running To Pain</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>So Help Me God</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H123" t="str">
-        <v>Kelsey Lu</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L123" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Pongo</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:14</v>
+        <v>3:09</v>
       </c>
       <c r="H124" t="str">
-        <v>Anitta</v>
+        <v>Rvssian</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L124" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>BOTERO</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Big Mama</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:20</v>
+        <v>4:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Latto</v>
+        <v>Maluma</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L125" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Bird Flu</v>
+        <v>Distance</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-22</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:58</v>
+        <v>3:14</v>
       </c>
       <c r="H126" t="str">
-        <v>6LACK</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L126" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Lighter</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:59</v>
+        <v>3:44</v>
       </c>
       <c r="H127" t="str">
-        <v>Jelly Roll</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L127" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Wide Awake</v>
+        <v>Riptides</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Wide Awake - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G128" t="str">
-        <v>4:16</v>
+        <v>3:17</v>
       </c>
       <c r="H128" t="str">
-        <v>Chris Stussy</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L128" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>2.0</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G129" t="str">
-        <v>3:25</v>
+        <v>2:49</v>
       </c>
       <c r="H129" t="str">
-        <v>Lizzo</v>
+        <v>BTS</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L129" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Dinner Party</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Dinner Party</v>
+        <v>6WA</v>
       </c>
       <c r="G130" t="str">
-        <v>2:34</v>
+        <v>3:08</v>
       </c>
       <c r="H130" t="str">
-        <v>Niall Horan</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L130" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>NORMAL</v>
+        <v>Highest</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>ARIRANG</v>
+        <v>Detour</v>
       </c>
       <c r="G131" t="str">
-        <v>3:01</v>
+        <v>2:56</v>
       </c>
       <c r="H131" t="str">
-        <v>BTS</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L131" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Die Living</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Die Living - Single</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>2:40</v>
       </c>
       <c r="H132" t="str">
-        <v>ILLENIUM</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L132" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Heaven On Earth</v>
+        <v>So What</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G133" t="str">
-        <v>2:59</v>
+        <v>4:31</v>
       </c>
       <c r="H133" t="str">
-        <v>Pentatonix</v>
+        <v>MUNA</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L133" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>an apple a day</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>an apple a day - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G134" t="str">
-        <v>5:16</v>
+        <v>3:12</v>
       </c>
       <c r="H134" t="str">
-        <v>horsegiirL</v>
+        <v>Eli</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L134" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>OUT LATE.</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G135" t="str">
-        <v>2:09</v>
+        <v>4:06</v>
       </c>
       <c r="H135" t="str">
-        <v>Loud Luxury</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L135" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Be With You</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>The Wow! Signal</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:35</v>
+        <v>2:14</v>
       </c>
       <c r="H136" t="str">
-        <v>Muse</v>
+        <v>Anitta</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L136" t="str">
-        <v>Be With You - Muse</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>First Red Rays</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>Big Mama</v>
       </c>
       <c r="G137" t="str">
-        <v>8:27</v>
+        <v>4:20</v>
       </c>
       <c r="H137" t="str">
-        <v>Neurosis</v>
+        <v>Latto</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L137" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Caught In The Echo</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G138" t="str">
-        <v>4:02</v>
+        <v>2:58</v>
       </c>
       <c r="H138" t="str">
-        <v>Foo Fighters</v>
+        <v>6LACK</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L138" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Little by Little</v>
+        <v>Lighter</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Little by Little - Single</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:34</v>
+        <v>2:59</v>
       </c>
       <c r="H139" t="str">
-        <v>Mon Rovîa</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L139" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Montgomery County</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:28</v>
+        <v>4:16</v>
       </c>
       <c r="H140" t="str">
-        <v>Parker McCollum</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L140" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dive Into Me</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>3:25</v>
       </c>
       <c r="H141" t="str">
-        <v>Alok</v>
+        <v>Lizzo</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L141" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>more than just a little bit</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>getting up to no good</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G142" t="str">
-        <v>2:40</v>
+        <v>2:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Artemas</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L142" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>WORSHIP</v>
+        <v>NORMAL</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>WORSHIP - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G143" t="str">
-        <v>2:43</v>
+        <v>3:01</v>
       </c>
       <c r="H143" t="str">
-        <v>Asake</v>
+        <v>BTS</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L143" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Honest</v>
+        <v>Die Living</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Honest - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:22</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Ebony Riley</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L144" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>6ft Under</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>6ft Under - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:30</v>
+        <v>2:59</v>
       </c>
       <c r="H145" t="str">
-        <v>KELS</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L145" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Maybe Again</v>
+        <v>an apple a day</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>When The City Sleeps</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:29</v>
+        <v>5:16</v>
       </c>
       <c r="H146" t="str">
-        <v>Alex Isley</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L146" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Trigger Happy</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Attachment Theory</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>2:09</v>
       </c>
       <c r="H147" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L147" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>Be With You</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G148" t="str">
-        <v>3:01</v>
+        <v>3:35</v>
       </c>
       <c r="H148" t="str">
-        <v>Kid Cudi</v>
+        <v>Muse</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L148" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G149" t="str">
-        <v>3:30</v>
+        <v>8:27</v>
       </c>
       <c r="H149" t="str">
-        <v>Swae Lee</v>
+        <v>Neurosis</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L149" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Runnin' On E</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G150" t="str">
-        <v>2:27</v>
+        <v>4:02</v>
       </c>
       <c r="H150" t="str">
-        <v>Wyatt Flores</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L150" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>FREESTYLE</v>
+        <v>Little by Little</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LINAJE</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:36</v>
+        <v>2:34</v>
       </c>
       <c r="H151" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L151" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Orcasitas</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Alma De Cántaro</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G152" t="str">
-        <v>3:23</v>
+        <v>3:28</v>
       </c>
       <c r="H152" t="str">
-        <v>marquitos</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L152" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Vida Loca</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:35</v>
+        <v>2:46</v>
       </c>
       <c r="H153" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Alok</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L153" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Honest</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>The Weight of the Woods</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G154" t="str">
-        <v>3:39</v>
+        <v>2:40</v>
       </c>
       <c r="H154" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Artemas</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L154" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ruleta Rusa</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:01</v>
+        <v>2:43</v>
       </c>
       <c r="H155" t="str">
-        <v>Kenia Os</v>
+        <v>Asake</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L155" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Honest</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Peaches!</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>5:00</v>
+        <v>3:22</v>
       </c>
       <c r="H156" t="str">
-        <v>The Black Keys</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L156" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Light as a Feather</v>
+        <v>6ft Under</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Everything Glows</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:36</v>
+        <v>3:30</v>
       </c>
       <c r="H157" t="str">
-        <v>Cannons</v>
+        <v>KELS</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L157" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Loving One</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Loving One - Single</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>3:29</v>
       </c>
       <c r="H158" t="str">
-        <v>People I’ve Met</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L158" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Both Can Be True</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G159" t="str">
-        <v>3:05</v>
+        <v>3:01</v>
       </c>
       <c r="H159" t="str">
-        <v>Trousdale</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L159" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Buffalo 66</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>4:27</v>
+        <v>3:01</v>
       </c>
       <c r="H160" t="str">
-        <v>Nessa Barrett</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L160" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>brb</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>brb - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G161" t="str">
-        <v>2:36</v>
+        <v>3:30</v>
       </c>
       <c r="H161" t="str">
-        <v>The Two Lips</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L161" t="str">
-        <v>brb - The Two Lips</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Euphoria</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Euphoria - Single</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:32</v>
+        <v>2:27</v>
       </c>
       <c r="H162" t="str">
-        <v>Talia Rae</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L162" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>if i'm lucky</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>better late than not at all - EP</v>
+        <v>LINAJE</v>
       </c>
       <c r="G163" t="str">
-        <v>2:57</v>
+        <v>5:36</v>
       </c>
       <c r="H163" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L163" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Gracie</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>F.I.G</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G164" t="str">
-        <v>2:54</v>
+        <v>3:23</v>
       </c>
       <c r="H164" t="str">
-        <v>Naomi Scott</v>
+        <v>marquitos</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L164" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>down under</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>down under - Single</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>2:35</v>
       </c>
       <c r="H165" t="str">
-        <v>Kevian Kraemer</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L165" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Send Me A Sign</v>
+        <v>Honest</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:39</v>
       </c>
       <c r="H166" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L166" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G167" t="str">
-        <v>3:02</v>
+        <v>3:01</v>
       </c>
       <c r="H167" t="str">
-        <v>OneRepublic</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L167" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Dream Chaser</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dream Chaser</v>
+        <v>Peaches!</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>5:00</v>
       </c>
       <c r="H168" t="str">
-        <v>Willie Nelson</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L168" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Trouble</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Girlfriend</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G169" t="str">
-        <v>3:17</v>
+        <v>3:36</v>
       </c>
       <c r="H169" t="str">
-        <v>Grace Ives</v>
+        <v>Cannons</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L169" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>judas</v>
+        <v>Loving One</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>judas - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:31</v>
+        <v>3:39</v>
       </c>
       <c r="H170" t="str">
-        <v>Josiah Queen</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L170" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>JINX</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>JINX - Single</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H171" t="str">
-        <v>Zacari</v>
+        <v>Trousdale</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L171" t="str">
-        <v>JINX - Zacari</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>se fue</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Náufrago</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G172" t="str">
-        <v>2:51</v>
+        <v>4:27</v>
       </c>
       <c r="H172" t="str">
-        <v>Eddy</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L172" t="str">
-        <v>se fue - Eddy</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>The Blade</v>
+        <v>brb</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>The Blade - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:15</v>
+        <v>2:36</v>
       </c>
       <c r="H173" t="str">
-        <v>Kingfishr</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L173" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Metric Rules</v>
+        <v>Euphoria</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:13</v>
+        <v>3:32</v>
       </c>
       <c r="H174" t="str">
-        <v>SPINALL</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L174" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>2:15</v>
+        <v>2:57</v>
       </c>
       <c r="H175" t="str">
-        <v>ZEP</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L175" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>Gracie</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G176" t="str">
-        <v>3:23</v>
+        <v>2:54</v>
       </c>
       <c r="H176" t="str">
-        <v>Hutch</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L176" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>down under</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>down under - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>5:15</v>
+        <v>3:24</v>
       </c>
       <c r="H177" t="str">
-        <v>MJ Cole</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L177" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cyclone</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Loss</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:33</v>
+        <v>3:15</v>
       </c>
       <c r="H178" t="str">
-        <v>Gaerea</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L178" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Checkmate</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Checkmate - Single</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>3:02</v>
       </c>
       <c r="H179" t="str">
-        <v>Blue Medusa</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L179" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>DAVE</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>DAVE - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G180" t="str">
-        <v>2:01</v>
+        <v>3:14</v>
       </c>
       <c r="H180" t="str">
-        <v>Hulvey</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L180" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Change</v>
+        <v>Trouble</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Change - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G181" t="str">
-        <v>2:38</v>
+        <v>3:17</v>
       </c>
       <c r="H181" t="str">
-        <v>Stephen Stanley</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L181" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Te Entiendo</v>
+        <v>judas</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:05</v>
+        <v>3:31</v>
       </c>
       <c r="H182" t="str">
-        <v>Maisak</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L182" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>CHEVROLET 90</v>
+        <v>JINX</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>V</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:01</v>
+        <v>2:54</v>
       </c>
       <c r="H183" t="str">
-        <v>Rey Quinto</v>
+        <v>Zacari</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L183" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tirabalas</v>
+        <v>se fue</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>Náufrago</v>
       </c>
       <c r="G184" t="str">
-        <v>3:53</v>
+        <v>2:51</v>
       </c>
       <c r="H184" t="str">
-        <v>Hans el Oso</v>
+        <v>Eddy</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L184" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>punchbowl</v>
+        <v>The Blade</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>punchbowl - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:34</v>
+        <v>3:15</v>
       </c>
       <c r="H185" t="str">
-        <v>Julio Caesar</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L185" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Wild Ride</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Wild Ride - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>3:13</v>
       </c>
       <c r="H186" t="str">
-        <v>Durand Bernarr</v>
+        <v>SPINALL</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L186" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Lamb Chop</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:03</v>
+        <v>2:15</v>
       </c>
       <c r="H187" t="str">
-        <v>Chuckyy</v>
+        <v>ZEP</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L187" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Free Nick</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Free Nick - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:05</v>
+        <v>3:23</v>
       </c>
       <c r="H188" t="str">
-        <v>Raq baby</v>
+        <v>Hutch</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L188" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Make Me Brand New</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:06</v>
+        <v>5:15</v>
       </c>
       <c r="H189" t="str">
-        <v>Dante’ Pride</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L189" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Define You</v>
+        <v>Cyclone</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Define You - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G190" t="str">
-        <v>3:34</v>
+        <v>5:33</v>
       </c>
       <c r="H190" t="str">
-        <v>Luca Fogale</v>
+        <v>Gaerea</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L190" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>If You Change</v>
+        <v>Checkmate</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Roses</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:41</v>
+        <v>4:23</v>
       </c>
       <c r="H191" t="str">
-        <v>Widowspeak</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L191" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>What I See</v>
+        <v>DAVE</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:32</v>
+        <v>2:01</v>
       </c>
       <c r="H192" t="str">
-        <v>See You Next Year</v>
+        <v>Hulvey</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L192" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Witching Hour</v>
+        <v>Change</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Butterfly</v>
+        <v>Change - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:47</v>
+        <v>2:38</v>
       </c>
       <c r="H193" t="str">
-        <v>Witch Post</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L193" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Actin' Tough</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:07</v>
+        <v>3:05</v>
       </c>
       <c r="H194" t="str">
-        <v>Dean Turnley</v>
+        <v>Maisak</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L194" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>V</v>
       </c>
       <c r="G195" t="str">
-        <v>2:52</v>
+        <v>2:01</v>
       </c>
       <c r="H195" t="str">
-        <v>Anais Cardot</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L195" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rewind It</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-22</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Rewind It - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G196" t="str">
-        <v>1:34</v>
+        <v>3:53</v>
       </c>
       <c r="H196" t="str">
-        <v>Nino Paid</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L196" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Turn It Up</v>
+        <v>punchbowl</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-22</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Turn It Up - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:33</v>
+        <v>2:34</v>
       </c>
       <c r="H197" t="str">
-        <v>slayr</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L197" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Down</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-22</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Down - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:08</v>
+        <v>3:41</v>
       </c>
       <c r="H198" t="str">
-        <v>MexikoDro</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L198" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Make It Out</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-22</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Make It Out - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:17</v>
+        <v>2:03</v>
       </c>
       <c r="H199" t="str">
-        <v>Trueblood</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L199" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>better than boston</v>
+        <v>Free Nick</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-22</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>better than boston - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:02</v>
+        <v>2:05</v>
       </c>
       <c r="H200" t="str">
-        <v>Tom Siletto</v>
+        <v>Raq baby</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L200" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-22</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:34</v>
+        <v>3:06</v>
       </c>
       <c r="H201" t="str">
-        <v>Lost Frequencies</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L201" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>All I Need</v>
+        <v>Define You</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-22</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>All I Need - Single</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>3:34</v>
       </c>
       <c r="H202" t="str">
-        <v>GRiZ</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L202" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Weeping Tones</v>
+        <v>If You Change</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-22</v>
@@ -8089,68 +8089,524 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Peace In Place</v>
+        <v>Roses</v>
       </c>
       <c r="G203" t="str">
-        <v>2:59</v>
+        <v>4:41</v>
       </c>
       <c r="H203" t="str">
-        <v>Poison the Well</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L203" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
+        <v>What I See</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>SYNY 3 Act II - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:32</v>
+      </c>
+      <c r="H204" t="str">
+        <v>See You Next Year</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+      </c>
+      <c r="L204" t="str">
+        <v>What I See - See You Next Year</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Witching Hour</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Butterfly</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:47</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Witch Post</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Witching Hour - Witch Post</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Actin' Tough</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Actin' Tough - Single</v>
+      </c>
+      <c r="G206" t="str">
+        <v>3:07</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Dean Turnley</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Actin' Tough - Dean Turnley</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Coração - A COLORS SHOW</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Coração - A COLORS SHOW - Single</v>
+      </c>
+      <c r="G207" t="str">
+        <v>2:52</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Anais Cardot</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Rewind It</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Rewind It - Single</v>
+      </c>
+      <c r="G208" t="str">
+        <v>1:34</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Nino Paid</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Rewind It - Nino Paid</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Turn It Up</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>Turn It Up - Single</v>
+      </c>
+      <c r="G209" t="str">
+        <v>2:33</v>
+      </c>
+      <c r="H209" t="str">
+        <v>slayr</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Turn It Up - slayr</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Down</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/down/1884531560</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Down - Single</v>
+      </c>
+      <c r="G210" t="str">
+        <v>2:08</v>
+      </c>
+      <c r="H210" t="str">
+        <v>MexikoDro</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/down/1884531558</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Down - MexikoDro</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Make It Out</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Make It Out - Single</v>
+      </c>
+      <c r="G211" t="str">
+        <v>2:17</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Trueblood</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Make It Out - Trueblood</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>better than boston</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>better than boston - Single</v>
+      </c>
+      <c r="G212" t="str">
+        <v>3:02</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Tom Siletto</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+      </c>
+      <c r="L212" t="str">
+        <v>better than boston - Tom Siletto</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>So Much Beauty (Around Us)</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>So Much Beauty (Around Us) - Single</v>
+      </c>
+      <c r="G213" t="str">
+        <v>2:34</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Lost Frequencies</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+      </c>
+      <c r="L213" t="str">
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>All I Need</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>All I Need - Single</v>
+      </c>
+      <c r="G214" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H214" t="str">
+        <v>GRiZ</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+      </c>
+      <c r="L214" t="str">
+        <v>All I Need - GRiZ</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G215" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H215" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D204" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
+      <c r="D216" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G204" t="str">
+      <c r="G216" t="str">
         <v>5:19</v>
       </c>
-      <c r="H204" t="str">
+      <c r="H216" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K204" t="str">
+      <c r="K216" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L204" t="str">
+      <c r="L216" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L216"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L213"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רני רחמים - עכשיו זה נגמר</v>
+        <v>קורין מלאכי - ברוקלין</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410122&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410131&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רני רחמים - עכשיו זה נגמר</v>
+        <v>קורין מלאכי - ברוקלין</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רגב הוד - תודה לאל קאבר</v>
+        <v>מנחם שוקרון - תפילות</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410121&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410130&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רגב הוד - תודה לאל קאבר</v>
+        <v>מנחם שוקרון - תפילות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתי גדמו - כל מה שבניתי</v>
+        <v>יניב יעקובי - שירת הים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410120&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410129&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתי גדמו - כל מה שבניתי</v>
+        <v>יניב יעקובי - שירת הים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נהוראי אריאלי - זהות בדויה</v>
+        <v>יוסף יצחק פרקש - אל תירא</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410119&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410128&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נהוראי אריאלי - זהות בדויה</v>
+        <v>יוסף יצחק פרקש - אל תירא</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>לידור - כל מה שעשיתי</v>
+        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410118&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410127&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>לידור - כל מה שעשיתי</v>
+        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יותם רכס - עסקים כרגיל</v>
+        <v>טל עזאני - מלכת הלבבות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410117&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410126&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יותם רכס - עסקים כרגיל</v>
+        <v>טל עזאני - מלכת הלבבות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>בן צור - אישתי</v>
+        <v>אליעד לוי - געגוע אלייך</v>
       </c>
       <c r="B8" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410116&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410125&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>בן צור - אישתי</v>
+        <v>אליעד לוי - געגוע אלייך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אתל - טוקסיק</v>
+        <v>אבי חן - לחזור לבית</v>
       </c>
       <c r="B9" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410115&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410124&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אתל - טוקסיק</v>
+        <v>אבי חן - לחזור לבית</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ארי ברמן - דור הגאולה</v>
+        <v>שר שלום מהצרי - והיא שעמדה</v>
       </c>
       <c r="B10" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410114&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410123&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ארי ברמן - דור הגאולה</v>
+        <v>שר שלום מהצרי - והיא שעמדה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אלה הודיה גוילי - סוף העולם</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-22</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410113&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,36 +811,36 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אלה הודיה גוילי - סוף העולם</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אדל חן - אושר אמיתי</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-03-22</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410112&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>3:31</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Nick Carter</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,36 +849,36 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אדל חן - אושר אמיתי</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>פו פייטרס Caught In The Echo</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-03-22</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-caught-in-the-echo/</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>אנחנו במרחק של בערך חודש מהוצאת האלבום החדש של פו פייטרס Foo Fighters, שנקרא  Your Favorite Toy, ודייב גרול והלהקה משתפים בסינגל השני – Caught In The Echo. לא היו לי בדיוק ציפיות בשמיים משיר חדש של פו פייטרס  עם</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>3:38</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Carly Pearce</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>פו פייטרס Caught In The Echo</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:17</v>
+        <v>4:11</v>
       </c>
       <c r="H14" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:31</v>
+        <v>2:57</v>
       </c>
       <c r="H15" t="str">
-        <v>Nick Carter</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:38</v>
+        <v>3:47</v>
       </c>
       <c r="H16" t="str">
-        <v>Carly Pearce</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:11</v>
+        <v>7:10</v>
       </c>
       <c r="H17" t="str">
-        <v>OneRepublic</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:57</v>
+        <v>3:06</v>
       </c>
       <c r="H18" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:47</v>
+        <v>3:05</v>
       </c>
       <c r="H19" t="str">
-        <v>Armin van Buuren</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>7:10</v>
+        <v>3:12</v>
       </c>
       <c r="H20" t="str">
-        <v>David Gilmour</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:06</v>
+        <v>9:11</v>
       </c>
       <c r="H21" t="str">
-        <v>Grace Enger</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B22" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:05</v>
+        <v>3:49</v>
       </c>
       <c r="H22" t="str">
-        <v>Tucker Wetmore</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:12</v>
+        <v>3:28</v>
       </c>
       <c r="H23" t="str">
-        <v>Freya Ridings</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>9:11</v>
+        <v>3:31</v>
       </c>
       <c r="H24" t="str">
-        <v>David Gilmour</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B25" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:49</v>
+        <v>3:11</v>
       </c>
       <c r="H25" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B26" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:28</v>
+        <v>2:27</v>
       </c>
       <c r="H26" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>HAUSER</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B27" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:31</v>
+        <v>3:34</v>
       </c>
       <c r="H27" t="str">
-        <v>Martin Garrix</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:11</v>
+        <v>2:50</v>
       </c>
       <c r="H28" t="str">
-        <v>Baby Queen</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:27</v>
+        <v>3:51</v>
       </c>
       <c r="H29" t="str">
-        <v>HAUSER</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:34</v>
+        <v>2:39</v>
       </c>
       <c r="H30" t="str">
-        <v>Holly Humberstone</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B31" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1556,10 +1556,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:50</v>
+        <v>5:08</v>
       </c>
       <c r="H31" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Jessie J</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B32" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:51</v>
+        <v>3:46</v>
       </c>
       <c r="H32" t="str">
-        <v>Rick Astley</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:39</v>
+        <v>2:42</v>
       </c>
       <c r="H33" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B34" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>5:08</v>
+        <v>2:31</v>
       </c>
       <c r="H34" t="str">
-        <v>Jessie J</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B35" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:46</v>
+        <v>3:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Bishop Briggs</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H36" t="str">
-        <v>Dean Lewis</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:31</v>
+        <v>3:43</v>
       </c>
       <c r="H37" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>We Three</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,21 +1799,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B38" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1822,10 +1822,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:14</v>
+        <v>2:54</v>
       </c>
       <c r="H38" t="str">
-        <v>Luke Combs</v>
+        <v>paris jackson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,21 +1837,21 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1860,10 +1860,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:22</v>
+        <v>2:46</v>
       </c>
       <c r="H39" t="str">
-        <v>Allison Russell</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,21 +1875,21 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1898,10 +1898,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:43</v>
+        <v>3:37</v>
       </c>
       <c r="H40" t="str">
-        <v>We Three</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,21 +1913,21 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1936,10 +1936,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H41" t="str">
-        <v>paris jackson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,21 +1951,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:46</v>
+        <v>3:38</v>
       </c>
       <c r="H42" t="str">
-        <v>Kane Brown</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:37</v>
+        <v>4:29</v>
       </c>
       <c r="H43" t="str">
-        <v>Lainey Wilson</v>
+        <v>Kungs</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:57</v>
+        <v>4:28</v>
       </c>
       <c r="H44" t="str">
-        <v>Malcolm Todd</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H45" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>aron!</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2126,10 +2126,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:29</v>
+        <v>3:51</v>
       </c>
       <c r="H46" t="str">
-        <v>Kungs</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B47" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2164,7 +2164,7 @@
         <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:28</v>
+        <v>2:49</v>
       </c>
       <c r="H47" t="str">
         <v>Sunday (1994)</v>
@@ -2179,21 +2179,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B48" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2202,10 +2202,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:26</v>
+        <v>4:16</v>
       </c>
       <c r="H48" t="str">
-        <v>aron!</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B49" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,10 +2240,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:51</v>
+        <v>4:16</v>
       </c>
       <c r="H49" t="str">
-        <v>Colinstoughmusic</v>
+        <v>LANY</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:49</v>
+        <v>3:25</v>
       </c>
       <c r="H50" t="str">
-        <v>Sunday (1994)</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:16</v>
+        <v>2:50</v>
       </c>
       <c r="H51" t="str">
-        <v>Owen Riegling</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:16</v>
+        <v>3:57</v>
       </c>
       <c r="H52" t="str">
-        <v>LANY</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:25</v>
+        <v>3:58</v>
       </c>
       <c r="H53" t="str">
-        <v>Maverick Sabre</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:50</v>
+        <v>3:25</v>
       </c>
       <c r="H54" t="str">
-        <v>Amanda Jordan</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:57</v>
+        <v>4:09</v>
       </c>
       <c r="H55" t="str">
-        <v>Beabadoobee</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:58</v>
+        <v>2:08</v>
       </c>
       <c r="H56" t="str">
-        <v>Spacey Jane</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:25</v>
+        <v>2:57</v>
       </c>
       <c r="H57" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B58" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:09</v>
+        <v>3:13</v>
       </c>
       <c r="H58" t="str">
-        <v>Mei Semones</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:08</v>
+        <v>4:12</v>
       </c>
       <c r="H59" t="str">
-        <v>The Lemon Twigs</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:57</v>
+        <v>3:57</v>
       </c>
       <c r="H60" t="str">
-        <v>Natalie Jane</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:13</v>
+        <v>3:34</v>
       </c>
       <c r="H61" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:12</v>
+        <v>3:48</v>
       </c>
       <c r="H62" t="str">
-        <v>David Gilmour</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:57</v>
+        <v>4:58</v>
       </c>
       <c r="H63" t="str">
-        <v>Far Caspian</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:34</v>
+        <v>2:33</v>
       </c>
       <c r="H64" t="str">
-        <v>Celine Dion</v>
+        <v>Ellise</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:48</v>
+        <v>5:01</v>
       </c>
       <c r="H65" t="str">
-        <v>Harry Styles</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:58</v>
+        <v>4:56</v>
       </c>
       <c r="H66" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:33</v>
+        <v>2:54</v>
       </c>
       <c r="H67" t="str">
-        <v>Ellise</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,21 +2939,21 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:01</v>
+        <v>2:46</v>
       </c>
       <c r="H68" t="str">
-        <v>The Doobie Brothers</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:56</v>
+        <v>2:56</v>
       </c>
       <c r="H69" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>R3HAB</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:54</v>
+        <v>3:21</v>
       </c>
       <c r="H70" t="str">
-        <v>Bebe Rexha</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:46</v>
+        <v>3:16</v>
       </c>
       <c r="H71" t="str">
-        <v>NathanEvanss</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,21 +3091,21 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:56</v>
+        <v>2:41</v>
       </c>
       <c r="H72" t="str">
-        <v>R3HAB</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:21</v>
+        <v>2:29</v>
       </c>
       <c r="H73" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:16</v>
+        <v>2:43</v>
       </c>
       <c r="H74" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:41</v>
+        <v>3:46</v>
       </c>
       <c r="H75" t="str">
-        <v>Johnny Orlando</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:29</v>
+        <v>4:01</v>
       </c>
       <c r="H76" t="str">
-        <v>Russell Dickerson</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:43</v>
+        <v>3:23</v>
       </c>
       <c r="H77" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:46</v>
+        <v>3:39</v>
       </c>
       <c r="H78" t="str">
-        <v>Matt Hansen</v>
+        <v>almost monday</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:01</v>
+        <v>3:04</v>
       </c>
       <c r="H79" t="str">
-        <v>Mike Posner</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,21 +3395,21 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:23</v>
+        <v>3:25</v>
       </c>
       <c r="H80" t="str">
-        <v>Katelyn Tarver</v>
+        <v>vaultboy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:39</v>
+        <v>3:49</v>
       </c>
       <c r="H81" t="str">
-        <v>almost monday</v>
+        <v>The Warning</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:04</v>
+        <v>2:14</v>
       </c>
       <c r="H82" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>aron!</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:25</v>
+        <v>2:43</v>
       </c>
       <c r="H83" t="str">
-        <v>vaultboy</v>
+        <v>Bazzi</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:49</v>
+        <v>4:43</v>
       </c>
       <c r="H84" t="str">
-        <v>The Warning</v>
+        <v>Sting</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:14</v>
+        <v>2:44</v>
       </c>
       <c r="H85" t="str">
-        <v>aron!</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:43</v>
+        <v>4:37</v>
       </c>
       <c r="H86" t="str">
-        <v>Bazzi</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:43</v>
+        <v>4:52</v>
       </c>
       <c r="H87" t="str">
-        <v>Sting</v>
+        <v>Cannons</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:44</v>
+        <v>2:13</v>
       </c>
       <c r="H88" t="str">
-        <v>Dean Lewis</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:37</v>
+        <v>3:19</v>
       </c>
       <c r="H89" t="str">
-        <v>Jessie Ware</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:52</v>
+        <v>2:31</v>
       </c>
       <c r="H90" t="str">
-        <v>Cannons</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,21 +3813,21 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:13</v>
+        <v>2:43</v>
       </c>
       <c r="H91" t="str">
-        <v>Kim Petras</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:19</v>
+        <v>3:10</v>
       </c>
       <c r="H92" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:31</v>
+        <v>3:55</v>
       </c>
       <c r="H93" t="str">
-        <v>Kiana Ledé</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:43</v>
+        <v>3:52</v>
       </c>
       <c r="H94" t="str">
-        <v>Ringo Starr</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:10</v>
+        <v>2:53</v>
       </c>
       <c r="H95" t="str">
-        <v>Maya Hawke</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:55</v>
+        <v>4:30</v>
       </c>
       <c r="H96" t="str">
-        <v>Armin van Buuren</v>
+        <v>Jessie J</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:52</v>
+        <v>5:18</v>
       </c>
       <c r="H97" t="str">
-        <v>Demi Lovato</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:53</v>
+        <v>7:20</v>
       </c>
       <c r="H98" t="str">
-        <v>Peter Gabriel</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:30</v>
+        <v>3:01</v>
       </c>
       <c r="H99" t="str">
-        <v>Jessie J</v>
+        <v>BRITs</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:18</v>
+        <v>3:31</v>
       </c>
       <c r="H100" t="str">
-        <v>Harry Styles</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>7:20</v>
+        <v>3:00</v>
       </c>
       <c r="H101" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,21 +4231,21 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B102" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4254,10 +4254,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:01</v>
+        <v>3:11</v>
       </c>
       <c r="H102" t="str">
-        <v>BRITs</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,21 +4269,21 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B103" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4292,10 +4292,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H103" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Lauv</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,21 +4307,21 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B104" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4330,10 +4330,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:00</v>
+        <v>5:03</v>
       </c>
       <c r="H104" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>RAYE</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,21 +4345,21 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B105" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4368,10 +4368,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:11</v>
+        <v>4:50</v>
       </c>
       <c r="H105" t="str">
-        <v>The Kiffness</v>
+        <v>Armik</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,21 +4383,21 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B106" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4406,10 +4406,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:32</v>
+        <v>4:53</v>
       </c>
       <c r="H106" t="str">
-        <v>Lauv</v>
+        <v>Scorpions</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4421,21 +4421,21 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B107" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4444,10 +4444,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>5:03</v>
+        <v>3:04</v>
       </c>
       <c r="H107" t="str">
-        <v>RAYE</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4459,21 +4459,21 @@
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B108" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4482,10 +4482,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>4:50</v>
+        <v>4:32</v>
       </c>
       <c r="H108" t="str">
-        <v>Armik</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4497,21 +4497,21 @@
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B109" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4520,10 +4520,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>4:53</v>
+        <v>3:47</v>
       </c>
       <c r="H109" t="str">
-        <v>Scorpions</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4535,21 +4535,21 @@
         <v/>
       </c>
       <c r="L109" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B110" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4558,10 +4558,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:04</v>
+        <v>3:40</v>
       </c>
       <c r="H110" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4573,4040 +4573,3926 @@
         <v/>
       </c>
       <c r="L110" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>SWIM</v>
       </c>
       <c r="B111" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>3 weeks ago</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G111" t="str">
-        <v>4:32</v>
+        <v>2:39</v>
       </c>
       <c r="H111" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>BTS</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L111" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B112" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>3 weeks ago</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G112" t="str">
-        <v>3:47</v>
+        <v>5:01</v>
       </c>
       <c r="H112" t="str">
-        <v>Girl Tones</v>
+        <v>RAYE</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L112" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B113" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>3 weeks ago</v>
+        <v>Dandelion</v>
       </c>
       <c r="G113" t="str">
-        <v>3:40</v>
+        <v>3:46</v>
       </c>
       <c r="H113" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L113" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SWIM</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ARIRANG</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G114" t="str">
-        <v>2:39</v>
+        <v>2:45</v>
       </c>
       <c r="H114" t="str">
-        <v>BTS</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L114" t="str">
-        <v>SWIM - BTS</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G115" t="str">
-        <v>5:01</v>
+        <v>2:42</v>
       </c>
       <c r="H115" t="str">
-        <v>RAYE</v>
+        <v>Feid</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L115" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Loving Life Again</v>
+        <v>Leak It</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Dandelion</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:46</v>
+        <v>3:03</v>
       </c>
       <c r="H116" t="str">
-        <v>Ella Langley</v>
+        <v>FLO</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L116" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Rethink Some Things</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Way I Am</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:45</v>
+        <v>2:40</v>
       </c>
       <c r="H117" t="str">
-        <v>Luke Combs</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L117" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>TRANKAITO</v>
+        <v>D33P3R</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>R3SET</v>
       </c>
       <c r="G118" t="str">
-        <v>2:42</v>
+        <v>3:25</v>
       </c>
       <c r="H118" t="str">
-        <v>Feid</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L118" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Leak It</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Leak It - Single</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:03</v>
+        <v>3:01</v>
       </c>
       <c r="H119" t="str">
-        <v>FLO</v>
+        <v>Yeat</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L119" t="str">
-        <v>Leak It - FLO</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>LUVAGIRL</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:40</v>
+        <v>3:09</v>
       </c>
       <c r="H120" t="str">
-        <v>Coco Jones</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L120" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>D33P3R</v>
+        <v>Pongo</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>R3SET</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:25</v>
+        <v>3:09</v>
       </c>
       <c r="H121" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Rvssian</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L121" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>BOTERO</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:01</v>
+        <v>4:14</v>
       </c>
       <c r="H122" t="str">
-        <v>Yeat</v>
+        <v>Maluma</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L122" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Don't Hate Me</v>
+        <v>Distance</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:09</v>
+        <v>3:14</v>
       </c>
       <c r="H123" t="str">
-        <v>Miles Caton</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L123" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Pongo</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Pongo - Single</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:09</v>
+        <v>3:44</v>
       </c>
       <c r="H124" t="str">
-        <v>Rvssian</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L124" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>BOTERO</v>
+        <v>Riptides</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>BOTERO - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G125" t="str">
-        <v>4:14</v>
+        <v>3:17</v>
       </c>
       <c r="H125" t="str">
-        <v>Maluma</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L125" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Distance</v>
+        <v>2.0</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Distance - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G126" t="str">
-        <v>3:14</v>
+        <v>2:49</v>
       </c>
       <c r="H126" t="str">
-        <v>Finn Askew</v>
+        <v>BTS</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L126" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Ocean In The Desert</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>6WA</v>
       </c>
       <c r="G127" t="str">
-        <v>3:44</v>
+        <v>3:08</v>
       </c>
       <c r="H127" t="str">
-        <v>Dionne Warwick</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L127" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Riptides</v>
+        <v>Highest</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>I Built You a Tower</v>
+        <v>Detour</v>
       </c>
       <c r="G128" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H128" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L128" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2.0</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>ARIRANG</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:49</v>
+        <v>2:40</v>
       </c>
       <c r="H129" t="str">
-        <v>BTS</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L129" t="str">
-        <v>2.0 - BTS</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>6IXER PARTY</v>
+        <v>So What</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>6WA</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G130" t="str">
-        <v>3:08</v>
+        <v>4:31</v>
       </c>
       <c r="H130" t="str">
-        <v>BigXthaPlug</v>
+        <v>MUNA</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L130" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Highest</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Detour</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G131" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H131" t="str">
-        <v>Samara Cyn</v>
+        <v>Eli</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L131" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G132" t="str">
-        <v>2:40</v>
+        <v>4:06</v>
       </c>
       <c r="H132" t="str">
-        <v>Coi Leray</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L132" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>So What</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:31</v>
+        <v>2:14</v>
       </c>
       <c r="H133" t="str">
-        <v>MUNA</v>
+        <v>Anitta</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L133" t="str">
-        <v>So What - MUNA</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Big Mama</v>
       </c>
       <c r="G134" t="str">
-        <v>3:12</v>
+        <v>4:20</v>
       </c>
       <c r="H134" t="str">
-        <v>Eli</v>
+        <v>Latto</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L134" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Running To Pain</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>So Help Me God</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G135" t="str">
-        <v>4:06</v>
+        <v>2:58</v>
       </c>
       <c r="H135" t="str">
-        <v>Kelsey Lu</v>
+        <v>6LACK</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L135" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Lighter</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:14</v>
+        <v>2:59</v>
       </c>
       <c r="H136" t="str">
-        <v>Anitta</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L136" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Big Mama</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>4:20</v>
+        <v>4:16</v>
       </c>
       <c r="H137" t="str">
-        <v>Latto</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L137" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bird Flu</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:58</v>
+        <v>3:25</v>
       </c>
       <c r="H138" t="str">
-        <v>6LACK</v>
+        <v>Lizzo</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L138" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Lighter</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G139" t="str">
-        <v>2:59</v>
+        <v>2:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Jelly Roll</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L139" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Wide Awake</v>
+        <v>NORMAL</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Wide Awake - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G140" t="str">
-        <v>4:16</v>
+        <v>3:01</v>
       </c>
       <c r="H140" t="str">
-        <v>Chris Stussy</v>
+        <v>BTS</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L140" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Die Living</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H141" t="str">
-        <v>Lizzo</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L141" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Dinner Party</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Dinner Party</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:34</v>
+        <v>2:59</v>
       </c>
       <c r="H142" t="str">
-        <v>Niall Horan</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L142" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>NORMAL</v>
+        <v>an apple a day</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>ARIRANG</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:01</v>
+        <v>5:16</v>
       </c>
       <c r="H143" t="str">
-        <v>BTS</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L143" t="str">
-        <v>NORMAL - BTS</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Die Living</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Die Living - Single</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>2:09</v>
       </c>
       <c r="H144" t="str">
-        <v>ILLENIUM</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L144" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Heaven On Earth</v>
+        <v>Be With You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G145" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H145" t="str">
-        <v>Pentatonix</v>
+        <v>Muse</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L145" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>an apple a day</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>an apple a day - Single</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G146" t="str">
-        <v>5:16</v>
+        <v>8:27</v>
       </c>
       <c r="H146" t="str">
-        <v>horsegiirL</v>
+        <v>Neurosis</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L146" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>OUT LATE.</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G147" t="str">
-        <v>2:09</v>
+        <v>4:02</v>
       </c>
       <c r="H147" t="str">
-        <v>Loud Luxury</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L147" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Be With You</v>
+        <v>Little by Little</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>The Wow! Signal</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:35</v>
+        <v>2:34</v>
       </c>
       <c r="H148" t="str">
-        <v>Muse</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L148" t="str">
-        <v>Be With You - Muse</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>First Red Rays</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G149" t="str">
-        <v>8:27</v>
+        <v>3:28</v>
       </c>
       <c r="H149" t="str">
-        <v>Neurosis</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L149" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Caught In The Echo</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:02</v>
+        <v>2:46</v>
       </c>
       <c r="H150" t="str">
-        <v>Foo Fighters</v>
+        <v>Alok</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L150" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Little by Little</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Little by Little - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G151" t="str">
-        <v>2:34</v>
+        <v>2:40</v>
       </c>
       <c r="H151" t="str">
-        <v>Mon Rovîa</v>
+        <v>Artemas</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L151" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Montgomery County</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:28</v>
+        <v>2:43</v>
       </c>
       <c r="H152" t="str">
-        <v>Parker McCollum</v>
+        <v>Asake</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L152" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Dive Into Me</v>
+        <v>Honest</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:46</v>
+        <v>3:22</v>
       </c>
       <c r="H153" t="str">
-        <v>Alok</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L153" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>more than just a little bit</v>
+        <v>6ft Under</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>getting up to no good</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:40</v>
+        <v>3:30</v>
       </c>
       <c r="H154" t="str">
-        <v>Artemas</v>
+        <v>KELS</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L154" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>WORSHIP</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>WORSHIP - Single</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G155" t="str">
-        <v>2:43</v>
+        <v>3:29</v>
       </c>
       <c r="H155" t="str">
-        <v>Asake</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L155" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Honest</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Honest - Single</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G156" t="str">
-        <v>3:22</v>
+        <v>3:01</v>
       </c>
       <c r="H156" t="str">
-        <v>Ebony Riley</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L156" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>6ft Under</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>6ft Under - Single</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G157" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H157" t="str">
-        <v>KELS</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L157" t="str">
-        <v>6ft Under - KELS</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Maybe Again</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>When The City Sleeps</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G158" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H158" t="str">
-        <v>Alex Isley</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L158" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Trigger Happy</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Attachment Theory</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:01</v>
+        <v>2:27</v>
       </c>
       <c r="H159" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L159" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>LINAJE</v>
       </c>
       <c r="G160" t="str">
-        <v>3:01</v>
+        <v>5:36</v>
       </c>
       <c r="H160" t="str">
-        <v>Kid Cudi</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L160" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G161" t="str">
-        <v>3:30</v>
+        <v>3:23</v>
       </c>
       <c r="H161" t="str">
-        <v>Swae Lee</v>
+        <v>marquitos</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L161" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Runnin' On E</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G162" t="str">
-        <v>2:27</v>
+        <v>2:35</v>
       </c>
       <c r="H162" t="str">
-        <v>Wyatt Flores</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L162" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>FREESTYLE</v>
+        <v>Honest</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>LINAJE</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G163" t="str">
-        <v>5:36</v>
+        <v>3:39</v>
       </c>
       <c r="H163" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L163" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Orcasitas</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Alma De Cántaro</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G164" t="str">
-        <v>3:23</v>
+        <v>3:01</v>
       </c>
       <c r="H164" t="str">
-        <v>marquitos</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L164" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Vida Loca</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Peaches!</v>
       </c>
       <c r="G165" t="str">
-        <v>2:35</v>
+        <v>5:00</v>
       </c>
       <c r="H165" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L165" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Honest</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G166" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H166" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Cannons</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L166" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Loving One</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H167" t="str">
-        <v>Kenia Os</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L167" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Peaches!</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>5:00</v>
+        <v>3:05</v>
       </c>
       <c r="H168" t="str">
-        <v>The Black Keys</v>
+        <v>Trousdale</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L168" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Light as a Feather</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Everything Glows</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G169" t="str">
-        <v>3:36</v>
+        <v>4:27</v>
       </c>
       <c r="H169" t="str">
-        <v>Cannons</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L169" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Loving One</v>
+        <v>brb</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Loving One - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:39</v>
+        <v>2:36</v>
       </c>
       <c r="H170" t="str">
-        <v>People I’ve Met</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L170" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Both Can Be True</v>
+        <v>Euphoria</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:05</v>
+        <v>3:32</v>
       </c>
       <c r="H171" t="str">
-        <v>Trousdale</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L171" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Buffalo 66</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>4:27</v>
+        <v>2:57</v>
       </c>
       <c r="H172" t="str">
-        <v>Nessa Barrett</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L172" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>brb</v>
+        <v>Gracie</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>brb - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G173" t="str">
-        <v>2:36</v>
+        <v>2:54</v>
       </c>
       <c r="H173" t="str">
-        <v>The Two Lips</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L173" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Euphoria</v>
+        <v>down under</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Euphoria - Single</v>
+        <v>down under - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:32</v>
+        <v>3:24</v>
       </c>
       <c r="H174" t="str">
-        <v>Talia Rae</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L174" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>if i'm lucky</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:57</v>
+        <v>3:15</v>
       </c>
       <c r="H175" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L175" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Gracie</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>F.I.G</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G176" t="str">
-        <v>2:54</v>
+        <v>3:02</v>
       </c>
       <c r="H176" t="str">
-        <v>Naomi Scott</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L176" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>down under</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>down under - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G177" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H177" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L177" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Send Me A Sign</v>
+        <v>Trouble</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G178" t="str">
-        <v>3:15</v>
+        <v>3:17</v>
       </c>
       <c r="H178" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L178" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Something's Not Right Here</v>
+        <v>judas</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>judas - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H179" t="str">
-        <v>OneRepublic</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L179" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Dream Chaser</v>
+        <v>JINX</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Dream Chaser</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:14</v>
+        <v>2:54</v>
       </c>
       <c r="H180" t="str">
-        <v>Willie Nelson</v>
+        <v>Zacari</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L180" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Trouble</v>
+        <v>se fue</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Girlfriend</v>
+        <v>Náufrago</v>
       </c>
       <c r="G181" t="str">
-        <v>3:17</v>
+        <v>2:51</v>
       </c>
       <c r="H181" t="str">
-        <v>Grace Ives</v>
+        <v>Eddy</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L181" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>judas</v>
+        <v>The Blade</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>judas - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:31</v>
+        <v>3:15</v>
       </c>
       <c r="H182" t="str">
-        <v>Josiah Queen</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L182" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>JINX</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>JINX - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G183" t="str">
-        <v>2:54</v>
+        <v>3:13</v>
       </c>
       <c r="H183" t="str">
-        <v>Zacari</v>
+        <v>SPINALL</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L183" t="str">
-        <v>JINX - Zacari</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>se fue</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Náufrago</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:51</v>
+        <v>2:15</v>
       </c>
       <c r="H184" t="str">
-        <v>Eddy</v>
+        <v>ZEP</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L184" t="str">
-        <v>se fue - Eddy</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>The Blade</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>The Blade - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:15</v>
+        <v>3:23</v>
       </c>
       <c r="H185" t="str">
-        <v>Kingfishr</v>
+        <v>Hutch</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L185" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Metric Rules</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:13</v>
+        <v>5:15</v>
       </c>
       <c r="H186" t="str">
-        <v>SPINALL</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L186" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Cyclone</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G187" t="str">
-        <v>2:15</v>
+        <v>5:33</v>
       </c>
       <c r="H187" t="str">
-        <v>ZEP</v>
+        <v>Gaerea</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L187" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>Checkmate</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:23</v>
+        <v>4:23</v>
       </c>
       <c r="H188" t="str">
-        <v>Hutch</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L188" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>DAVE</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>5:15</v>
+        <v>2:01</v>
       </c>
       <c r="H189" t="str">
-        <v>MJ Cole</v>
+        <v>Hulvey</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L189" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Cyclone</v>
+        <v>Change</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Loss</v>
+        <v>Change - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H190" t="str">
-        <v>Gaerea</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L190" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Checkmate</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Checkmate - Single</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:23</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Blue Medusa</v>
+        <v>Maisak</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L191" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>DAVE</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>DAVE - Single</v>
+        <v>V</v>
       </c>
       <c r="G192" t="str">
         <v>2:01</v>
       </c>
       <c r="H192" t="str">
-        <v>Hulvey</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L192" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Change</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Change - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G193" t="str">
-        <v>2:38</v>
+        <v>3:53</v>
       </c>
       <c r="H193" t="str">
-        <v>Stephen Stanley</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L193" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Te Entiendo</v>
+        <v>punchbowl</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:05</v>
+        <v>2:34</v>
       </c>
       <c r="H194" t="str">
-        <v>Maisak</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L194" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>V</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:01</v>
+        <v>3:41</v>
       </c>
       <c r="H195" t="str">
-        <v>Rey Quinto</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L195" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Tirabalas</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:53</v>
+        <v>2:03</v>
       </c>
       <c r="H196" t="str">
-        <v>Hans el Oso</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L196" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>punchbowl</v>
+        <v>Free Nick</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>punchbowl - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:34</v>
+        <v>2:05</v>
       </c>
       <c r="H197" t="str">
-        <v>Julio Caesar</v>
+        <v>Raq baby</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L197" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Wild Ride</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Wild Ride - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:41</v>
+        <v>3:06</v>
       </c>
       <c r="H198" t="str">
-        <v>Durand Bernarr</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L198" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Lamb Chop</v>
+        <v>Define You</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:03</v>
+        <v>3:34</v>
       </c>
       <c r="H199" t="str">
-        <v>Chuckyy</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L199" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Free Nick</v>
+        <v>If You Change</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Free Nick - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G200" t="str">
-        <v>2:05</v>
+        <v>4:41</v>
       </c>
       <c r="H200" t="str">
-        <v>Raq baby</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L200" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Make Me Brand New</v>
+        <v>What I See</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:06</v>
+        <v>2:32</v>
       </c>
       <c r="H201" t="str">
-        <v>Dante’ Pride</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L201" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Define You</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Define You - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G202" t="str">
-        <v>3:34</v>
+        <v>3:47</v>
       </c>
       <c r="H202" t="str">
-        <v>Luca Fogale</v>
+        <v>Witch Post</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L202" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>If You Change</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Roses</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>4:41</v>
+        <v>3:07</v>
       </c>
       <c r="H203" t="str">
-        <v>Widowspeak</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L203" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>What I See</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E204" t="str">
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>2:32</v>
+        <v>2:52</v>
       </c>
       <c r="H204" t="str">
-        <v>See You Next Year</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L204" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Witching Hour</v>
+        <v>Rewind It</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E205" t="str">
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Butterfly</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:47</v>
+        <v>1:34</v>
       </c>
       <c r="H205" t="str">
-        <v>Witch Post</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L205" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Actin' Tough</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E206" t="str">
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:07</v>
+        <v>2:33</v>
       </c>
       <c r="H206" t="str">
-        <v>Dean Turnley</v>
+        <v>slayr</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L206" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Down</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E207" t="str">
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>2:52</v>
+        <v>2:08</v>
       </c>
       <c r="H207" t="str">
-        <v>Anais Cardot</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L207" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Rewind It</v>
+        <v>Make It Out</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D208" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E208" t="str">
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>Rewind It - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G208" t="str">
-        <v>1:34</v>
+        <v>2:17</v>
       </c>
       <c r="H208" t="str">
-        <v>Nino Paid</v>
+        <v>Trueblood</v>
       </c>
       <c r="I208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L208" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Turn It Up</v>
+        <v>better than boston</v>
       </c>
       <c r="B209" t="str">
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D209" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E209" t="str">
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>Turn It Up - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G209" t="str">
-        <v>2:33</v>
+        <v>3:02</v>
       </c>
       <c r="H209" t="str">
-        <v>slayr</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I209" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L209" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Down</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B210" t="str">
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D210" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E210" t="str">
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>Down - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G210" t="str">
-        <v>2:08</v>
+        <v>2:34</v>
       </c>
       <c r="H210" t="str">
-        <v>MexikoDro</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I210" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L210" t="str">
-        <v>Down - MexikoDro</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Make It Out</v>
+        <v>All I Need</v>
       </c>
       <c r="B211" t="str">
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D211" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E211" t="str">
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>Make It Out - Single</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G211" t="str">
-        <v>2:17</v>
+        <v>3:06</v>
       </c>
       <c r="H211" t="str">
-        <v>Trueblood</v>
+        <v>GRiZ</v>
       </c>
       <c r="I211" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L211" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>better than boston</v>
+        <v>Weeping Tones</v>
       </c>
       <c r="B212" t="str">
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D212" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E212" t="str">
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>better than boston - Single</v>
+        <v>Peace In Place</v>
       </c>
       <c r="G212" t="str">
-        <v>3:02</v>
+        <v>2:59</v>
       </c>
       <c r="H212" t="str">
-        <v>Tom Siletto</v>
+        <v>Poison the Well</v>
       </c>
       <c r="I212" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
       </c>
       <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
       </c>
       <c r="L212" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Weeping Tones - Poison the Well</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>Promise You This</v>
       </c>
       <c r="B213" t="str">
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D213" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E213" t="str">
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G213" t="str">
-        <v>2:34</v>
+        <v>5:19</v>
       </c>
       <c r="H213" t="str">
-        <v>Lost Frequencies</v>
+        <v>Exodus</v>
       </c>
       <c r="I213" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
       <c r="L213" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>All I Need</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>All I Need - Single</v>
-      </c>
-      <c r="G214" t="str">
-        <v>3:06</v>
-      </c>
-      <c r="H214" t="str">
-        <v>GRiZ</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
-      </c>
-      <c r="L214" t="str">
-        <v>All I Need - GRiZ</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Weeping Tones</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Peace In Place</v>
-      </c>
-      <c r="G215" t="str">
-        <v>2:59</v>
-      </c>
-      <c r="H215" t="str">
-        <v>Poison the Well</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
-      </c>
-      <c r="L215" t="str">
-        <v>Weeping Tones - Poison the Well</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Promise You This</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>Goliath</v>
-      </c>
-      <c r="G216" t="str">
-        <v>5:19</v>
-      </c>
-      <c r="H216" t="str">
-        <v>Exodus</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
-      </c>
-      <c r="L216" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L216"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L213"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קורין מלאכי - ברוקלין</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-22</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410131&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קורין מלאכי - ברוקלין</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מנחם שוקרון - תפילות</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-22</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410130&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>3:31</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Nick Carter</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מנחם שוקרון - תפילות</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יניב יעקובי - שירת הים</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-22</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410129&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>3:38</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Carly Pearce</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יניב יעקובי - שירת הים</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יוסף יצחק פרקש - אל תירא</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-22</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410128&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-23</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>4:11</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>OneRepublic</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יוסף יצחק פרקש - אל תירא</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-22</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410127&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-23</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>2:57</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>טל עזאני - מלכת הלבבות</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-22</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410126&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-23</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>3:47</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>טל עזאני - מלכת הלבבות</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אליעד לוי - געגוע אלייך</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-22</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410125&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-23</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>7:10</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>David Gilmour</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אליעד לוי - געגוע אלייך</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבי חן - לחזור לבית</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-22</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410124&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-23</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Grace Enger</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אבי חן - לחזור לבית</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>שר שלום מהצרי - והיא שעמדה</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-22</v>
+        <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410123&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-23</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>3:05</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>שר שלום מהצרי - והיא שעמדה</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:17</v>
+        <v>3:12</v>
       </c>
       <c r="H11" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:31</v>
+        <v>9:11</v>
       </c>
       <c r="H12" t="str">
-        <v>Nick Carter</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:38</v>
+        <v>3:49</v>
       </c>
       <c r="H13" t="str">
-        <v>Carly Pearce</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:11</v>
+        <v>3:28</v>
       </c>
       <c r="H14" t="str">
-        <v>OneRepublic</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H15" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:47</v>
+        <v>3:11</v>
       </c>
       <c r="H16" t="str">
-        <v>Armin van Buuren</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>7:10</v>
+        <v>2:27</v>
       </c>
       <c r="H17" t="str">
-        <v>David Gilmour</v>
+        <v>HAUSER</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-23</v>
@@ -1062,10 +1062,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:06</v>
+        <v>3:34</v>
       </c>
       <c r="H18" t="str">
-        <v>Grace Enger</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-23</v>
@@ -1100,10 +1100,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:05</v>
+        <v>2:50</v>
       </c>
       <c r="H19" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-23</v>
@@ -1138,10 +1138,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:12</v>
+        <v>3:51</v>
       </c>
       <c r="H20" t="str">
-        <v>Freya Ridings</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-23</v>
@@ -1176,10 +1176,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>9:11</v>
+        <v>2:39</v>
       </c>
       <c r="H21" t="str">
-        <v>David Gilmour</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-23</v>
@@ -1214,10 +1214,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:49</v>
+        <v>5:08</v>
       </c>
       <c r="H22" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jessie J</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-23</v>
@@ -1252,10 +1252,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:28</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H24" t="str">
-        <v>Martin Garrix</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:11</v>
+        <v>2:31</v>
       </c>
       <c r="H25" t="str">
-        <v>Baby Queen</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H26" t="str">
-        <v>HAUSER</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:34</v>
+        <v>3:22</v>
       </c>
       <c r="H27" t="str">
-        <v>Holly Humberstone</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:50</v>
+        <v>3:43</v>
       </c>
       <c r="H28" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>We Three</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:51</v>
+        <v>2:54</v>
       </c>
       <c r="H29" t="str">
-        <v>Rick Astley</v>
+        <v>paris jackson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:39</v>
+        <v>2:46</v>
       </c>
       <c r="H30" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:08</v>
+        <v>3:37</v>
       </c>
       <c r="H31" t="str">
-        <v>Jessie J</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:46</v>
+        <v>2:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Bishop Briggs</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:42</v>
+        <v>3:38</v>
       </c>
       <c r="H33" t="str">
-        <v>Dean Lewis</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:31</v>
+        <v>4:29</v>
       </c>
       <c r="H34" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Kungs</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:14</v>
+        <v>4:28</v>
       </c>
       <c r="H35" t="str">
-        <v>Luke Combs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:22</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>Allison Russell</v>
+        <v>aron!</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:43</v>
+        <v>3:51</v>
       </c>
       <c r="H37" t="str">
-        <v>We Three</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H38" t="str">
-        <v>paris jackson</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:46</v>
+        <v>4:16</v>
       </c>
       <c r="H39" t="str">
-        <v>Kane Brown</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:37</v>
+        <v>4:16</v>
       </c>
       <c r="H40" t="str">
-        <v>Lainey Wilson</v>
+        <v>LANY</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:57</v>
+        <v>3:25</v>
       </c>
       <c r="H41" t="str">
-        <v>Malcolm Todd</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:38</v>
+        <v>2:50</v>
       </c>
       <c r="H42" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:29</v>
+        <v>3:57</v>
       </c>
       <c r="H43" t="str">
-        <v>Kungs</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:28</v>
+        <v>3:58</v>
       </c>
       <c r="H44" t="str">
-        <v>Sunday (1994)</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:26</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>aron!</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:51</v>
+        <v>4:09</v>
       </c>
       <c r="H46" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:49</v>
+        <v>2:08</v>
       </c>
       <c r="H47" t="str">
-        <v>Sunday (1994)</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:16</v>
+        <v>2:57</v>
       </c>
       <c r="H48" t="str">
-        <v>Owen Riegling</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:16</v>
+        <v>3:13</v>
       </c>
       <c r="H49" t="str">
-        <v>LANY</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:25</v>
+        <v>4:12</v>
       </c>
       <c r="H50" t="str">
-        <v>Maverick Sabre</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:50</v>
+        <v>3:57</v>
       </c>
       <c r="H51" t="str">
-        <v>Amanda Jordan</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H52" t="str">
-        <v>Beabadoobee</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:58</v>
+        <v>3:48</v>
       </c>
       <c r="H53" t="str">
-        <v>Spacey Jane</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:25</v>
+        <v>4:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:09</v>
+        <v>2:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Mei Semones</v>
+        <v>Ellise</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B56" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:08</v>
+        <v>5:01</v>
       </c>
       <c r="H56" t="str">
-        <v>The Lemon Twigs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B57" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:57</v>
+        <v>4:56</v>
       </c>
       <c r="H57" t="str">
-        <v>Natalie Jane</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:13</v>
+        <v>2:54</v>
       </c>
       <c r="H58" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:12</v>
+        <v>2:46</v>
       </c>
       <c r="H59" t="str">
-        <v>David Gilmour</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:57</v>
+        <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>Far Caspian</v>
+        <v>R3HAB</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:34</v>
+        <v>3:21</v>
       </c>
       <c r="H61" t="str">
-        <v>Celine Dion</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-23</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:48</v>
+        <v>3:16</v>
       </c>
       <c r="H62" t="str">
-        <v>Harry Styles</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-23</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:58</v>
+        <v>2:41</v>
       </c>
       <c r="H63" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-23</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:33</v>
+        <v>2:29</v>
       </c>
       <c r="H64" t="str">
-        <v>Ellise</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-23</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:01</v>
+        <v>2:43</v>
       </c>
       <c r="H65" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-23</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:56</v>
+        <v>3:46</v>
       </c>
       <c r="H66" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H67" t="str">
-        <v>Bebe Rexha</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:46</v>
+        <v>3:23</v>
       </c>
       <c r="H68" t="str">
-        <v>NathanEvanss</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:56</v>
+        <v>3:39</v>
       </c>
       <c r="H69" t="str">
-        <v>R3HAB</v>
+        <v>almost monday</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:21</v>
+        <v>3:04</v>
       </c>
       <c r="H70" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:16</v>
+        <v>3:25</v>
       </c>
       <c r="H71" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>vaultboy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-23</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:41</v>
+        <v>3:49</v>
       </c>
       <c r="H72" t="str">
-        <v>Johnny Orlando</v>
+        <v>The Warning</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-23</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:29</v>
+        <v>2:14</v>
       </c>
       <c r="H73" t="str">
-        <v>Russell Dickerson</v>
+        <v>aron!</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-23</v>
@@ -3193,7 +3193,7 @@
         <v>2:43</v>
       </c>
       <c r="H74" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bazzi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-23</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:46</v>
+        <v>4:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Matt Hansen</v>
+        <v>Sting</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-23</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:01</v>
+        <v>2:44</v>
       </c>
       <c r="H76" t="str">
-        <v>Mike Posner</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-23</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:23</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-23</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:39</v>
+        <v>4:52</v>
       </c>
       <c r="H78" t="str">
-        <v>almost monday</v>
+        <v>Cannons</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-23</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:04</v>
+        <v>2:13</v>
       </c>
       <c r="H79" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-23</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:25</v>
+        <v>3:19</v>
       </c>
       <c r="H80" t="str">
-        <v>vaultboy</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-23</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:49</v>
+        <v>2:31</v>
       </c>
       <c r="H81" t="str">
-        <v>The Warning</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-23</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>aron!</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-23</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Bazzi</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-23</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:43</v>
+        <v>3:55</v>
       </c>
       <c r="H84" t="str">
-        <v>Sting</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-23</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:44</v>
+        <v>3:52</v>
       </c>
       <c r="H85" t="str">
-        <v>Dean Lewis</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-23</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:37</v>
+        <v>2:53</v>
       </c>
       <c r="H86" t="str">
-        <v>Jessie Ware</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:52</v>
+        <v>4:30</v>
       </c>
       <c r="H87" t="str">
-        <v>Cannons</v>
+        <v>Jessie J</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:13</v>
+        <v>5:18</v>
       </c>
       <c r="H88" t="str">
-        <v>Kim Petras</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:19</v>
+        <v>7:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:31</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>Kiana Ledé</v>
+        <v>BRITs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-23</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H91" t="str">
-        <v>Ringo Starr</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-23</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:10</v>
+        <v>3:00</v>
       </c>
       <c r="H92" t="str">
-        <v>Maya Hawke</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:55</v>
+        <v>3:11</v>
       </c>
       <c r="H93" t="str">
-        <v>Armin van Buuren</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:52</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Demi Lovato</v>
+        <v>Lauv</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:53</v>
+        <v>5:03</v>
       </c>
       <c r="H95" t="str">
-        <v>Peter Gabriel</v>
+        <v>RAYE</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-23</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:30</v>
+        <v>4:50</v>
       </c>
       <c r="H96" t="str">
-        <v>Jessie J</v>
+        <v>Armik</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-23</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>5:18</v>
+        <v>4:53</v>
       </c>
       <c r="H97" t="str">
-        <v>Harry Styles</v>
+        <v>Scorpions</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-23</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>7:20</v>
+        <v>3:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-23</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:01</v>
+        <v>4:32</v>
       </c>
       <c r="H99" t="str">
-        <v>BRITs</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-23</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H100" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-23</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:00</v>
+        <v>3:40</v>
       </c>
       <c r="H101" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>SWIM</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G102" t="str">
-        <v>3:11</v>
+        <v>2:39</v>
       </c>
       <c r="H102" t="str">
-        <v>The Kiffness</v>
+        <v>BTS</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L102" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B103" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>3 weeks ago</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G103" t="str">
-        <v>3:32</v>
+        <v>5:01</v>
       </c>
       <c r="H103" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L103" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B104" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>3 weeks ago</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>5:03</v>
+        <v>3:46</v>
       </c>
       <c r="H104" t="str">
-        <v>RAYE</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B105" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>3 weeks ago</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G105" t="str">
-        <v>4:50</v>
+        <v>2:45</v>
       </c>
       <c r="H105" t="str">
-        <v>Armik</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L105" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B106" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>3 weeks ago</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G106" t="str">
-        <v>4:53</v>
+        <v>2:42</v>
       </c>
       <c r="H106" t="str">
-        <v>Scorpions</v>
+        <v>Feid</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L106" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Leak It</v>
       </c>
       <c r="B107" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>3 weeks ago</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H107" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>FLO</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L107" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B108" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>3 weeks ago</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>4:32</v>
+        <v>2:40</v>
       </c>
       <c r="H108" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L108" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>D33P3R</v>
       </c>
       <c r="B109" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>3 weeks ago</v>
+        <v>R3SET</v>
       </c>
       <c r="G109" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H109" t="str">
-        <v>Girl Tones</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L109" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B110" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>3 weeks ago</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:40</v>
+        <v>3:01</v>
       </c>
       <c r="H110" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Yeat</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L110" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SWIM</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ARIRANG</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>3:09</v>
       </c>
       <c r="H111" t="str">
-        <v>BTS</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L111" t="str">
-        <v>SWIM - BTS</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>Pongo</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>5:01</v>
+        <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>RAYE</v>
+        <v>Rvssian</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L112" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Loving Life Again</v>
+        <v>BOTERO</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Dandelion</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:46</v>
+        <v>4:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Ella Langley</v>
+        <v>Maluma</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L113" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Rethink Some Things</v>
+        <v>Distance</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Way I Am</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:45</v>
+        <v>3:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Luke Combs</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L114" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>TRANKAITO</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:42</v>
+        <v>3:44</v>
       </c>
       <c r="H115" t="str">
-        <v>Feid</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L115" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Leak It</v>
+        <v>Riptides</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Leak It - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G116" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>FLO</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L116" t="str">
-        <v>Leak It - FLO</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>LUVAGIRL</v>
+        <v>2.0</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G117" t="str">
-        <v>2:40</v>
+        <v>2:49</v>
       </c>
       <c r="H117" t="str">
-        <v>Coco Jones</v>
+        <v>BTS</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L117" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>D33P3R</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>R3SET</v>
+        <v>6WA</v>
       </c>
       <c r="G118" t="str">
-        <v>3:25</v>
+        <v>3:08</v>
       </c>
       <c r="H118" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L118" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>Highest</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>Detour</v>
       </c>
       <c r="G119" t="str">
-        <v>3:01</v>
+        <v>2:56</v>
       </c>
       <c r="H119" t="str">
-        <v>Yeat</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L119" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Don't Hate Me</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:09</v>
+        <v>2:40</v>
       </c>
       <c r="H120" t="str">
-        <v>Miles Caton</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L120" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Pongo</v>
+        <v>So What</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Pongo - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G121" t="str">
-        <v>3:09</v>
+        <v>4:31</v>
       </c>
       <c r="H121" t="str">
-        <v>Rvssian</v>
+        <v>MUNA</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L121" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>BOTERO</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BOTERO - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G122" t="str">
-        <v>4:14</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>Maluma</v>
+        <v>Eli</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L122" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Distance</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Distance - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G123" t="str">
-        <v>3:14</v>
+        <v>4:06</v>
       </c>
       <c r="H123" t="str">
-        <v>Finn Askew</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L123" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:44</v>
+        <v>2:14</v>
       </c>
       <c r="H124" t="str">
-        <v>Dionne Warwick</v>
+        <v>Anitta</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L124" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Riptides</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>I Built You a Tower</v>
+        <v>Big Mama</v>
       </c>
       <c r="G125" t="str">
-        <v>3:17</v>
+        <v>4:20</v>
       </c>
       <c r="H125" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Latto</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L125" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>2.0</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ARIRANG</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G126" t="str">
-        <v>2:49</v>
+        <v>2:58</v>
       </c>
       <c r="H126" t="str">
-        <v>BTS</v>
+        <v>6LACK</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L126" t="str">
-        <v>2.0 - BTS</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>6IXER PARTY</v>
+        <v>Lighter</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>6WA</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:08</v>
+        <v>2:59</v>
       </c>
       <c r="H127" t="str">
-        <v>BigXthaPlug</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L127" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Highest</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Detour</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:56</v>
+        <v>4:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Samara Cyn</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L128" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:40</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>Coi Leray</v>
+        <v>Lizzo</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L129" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>So What</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G130" t="str">
-        <v>4:31</v>
+        <v>2:34</v>
       </c>
       <c r="H130" t="str">
-        <v>MUNA</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L130" t="str">
-        <v>So What - MUNA</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>NORMAL</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G131" t="str">
-        <v>3:12</v>
+        <v>3:01</v>
       </c>
       <c r="H131" t="str">
-        <v>Eli</v>
+        <v>BTS</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L131" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Running To Pain</v>
+        <v>Die Living</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>So Help Me God</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:06</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Kelsey Lu</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L132" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:14</v>
+        <v>2:59</v>
       </c>
       <c r="H133" t="str">
-        <v>Anitta</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L133" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>an apple a day</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Big Mama</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>4:20</v>
+        <v>5:16</v>
       </c>
       <c r="H134" t="str">
-        <v>Latto</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L134" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Bird Flu</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:58</v>
+        <v>2:09</v>
       </c>
       <c r="H135" t="str">
-        <v>6LACK</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L135" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Lighter</v>
+        <v>Be With You</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G136" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H136" t="str">
-        <v>Jelly Roll</v>
+        <v>Muse</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L136" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Wide Awake</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Wide Awake - Single</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G137" t="str">
-        <v>4:16</v>
+        <v>8:27</v>
       </c>
       <c r="H137" t="str">
-        <v>Chris Stussy</v>
+        <v>Neurosis</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L137" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G138" t="str">
-        <v>3:25</v>
+        <v>4:02</v>
       </c>
       <c r="H138" t="str">
-        <v>Lizzo</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L138" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Dinner Party</v>
+        <v>Little by Little</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Dinner Party</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G139" t="str">
         <v>2:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Niall Horan</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L139" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>NORMAL</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>ARIRANG</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G140" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H140" t="str">
-        <v>BTS</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L140" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Die Living</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Die Living - Single</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:50</v>
+        <v>2:46</v>
       </c>
       <c r="H141" t="str">
-        <v>ILLENIUM</v>
+        <v>Alok</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L141" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Heaven On Earth</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G142" t="str">
-        <v>2:59</v>
+        <v>2:40</v>
       </c>
       <c r="H142" t="str">
-        <v>Pentatonix</v>
+        <v>Artemas</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L142" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>an apple a day</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>an apple a day - Single</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>5:16</v>
+        <v>2:43</v>
       </c>
       <c r="H143" t="str">
-        <v>horsegiirL</v>
+        <v>Asake</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L143" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>OUT LATE.</v>
+        <v>Honest</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:09</v>
+        <v>3:22</v>
       </c>
       <c r="H144" t="str">
-        <v>Loud Luxury</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L144" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Be With You</v>
+        <v>6ft Under</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Wow! Signal</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:35</v>
+        <v>3:30</v>
       </c>
       <c r="H145" t="str">
-        <v>Muse</v>
+        <v>KELS</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L145" t="str">
-        <v>Be With You - Muse</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>First Red Rays</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G146" t="str">
-        <v>8:27</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>Neurosis</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L146" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Caught In The Echo</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G147" t="str">
-        <v>4:02</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>Foo Fighters</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L147" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Little by Little</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Little by Little - Single</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:34</v>
+        <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Mon Rovîa</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L148" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Montgomery County</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G149" t="str">
-        <v>3:28</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Parker McCollum</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L149" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Dive Into Me</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:46</v>
+        <v>2:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Alok</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L150" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>more than just a little bit</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>getting up to no good</v>
+        <v>LINAJE</v>
       </c>
       <c r="G151" t="str">
-        <v>2:40</v>
+        <v>5:36</v>
       </c>
       <c r="H151" t="str">
-        <v>Artemas</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L151" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>WORSHIP</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>WORSHIP - Single</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G152" t="str">
-        <v>2:43</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>Asake</v>
+        <v>marquitos</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L152" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Honest - Single</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G153" t="str">
-        <v>3:22</v>
+        <v>2:35</v>
       </c>
       <c r="H153" t="str">
-        <v>Ebony Riley</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L153" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>6ft Under</v>
+        <v>Honest</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>6ft Under - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G154" t="str">
-        <v>3:30</v>
+        <v>3:39</v>
       </c>
       <c r="H154" t="str">
-        <v>KELS</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L154" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Maybe Again</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>When The City Sleeps</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:29</v>
+        <v>3:01</v>
       </c>
       <c r="H155" t="str">
-        <v>Alex Isley</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L155" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Trigger Happy</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Attachment Theory</v>
+        <v>Peaches!</v>
       </c>
       <c r="G156" t="str">
-        <v>3:01</v>
+        <v>5:00</v>
       </c>
       <c r="H156" t="str">
-        <v>Aubrie Sellers</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L156" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G157" t="str">
-        <v>3:01</v>
+        <v>3:36</v>
       </c>
       <c r="H157" t="str">
-        <v>Kid Cudi</v>
+        <v>Cannons</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L157" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>Loving One</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:30</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Swae Lee</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L158" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Runnin' On E</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H159" t="str">
-        <v>Wyatt Flores</v>
+        <v>Trousdale</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L159" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>FREESTYLE</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>LINAJE</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G160" t="str">
-        <v>5:36</v>
+        <v>4:27</v>
       </c>
       <c r="H160" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L160" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Orcasitas</v>
+        <v>brb</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Alma De Cántaro</v>
+        <v>brb - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:23</v>
+        <v>2:36</v>
       </c>
       <c r="H161" t="str">
-        <v>marquitos</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L161" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Vida Loca</v>
+        <v>Euphoria</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:35</v>
+        <v>3:32</v>
       </c>
       <c r="H162" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L162" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Honest</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>The Weight of the Woods</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>3:39</v>
+        <v>2:57</v>
       </c>
       <c r="H163" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L163" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Gracie</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>F.I.G</v>
       </c>
       <c r="G164" t="str">
-        <v>3:01</v>
+        <v>2:54</v>
       </c>
       <c r="H164" t="str">
-        <v>Kenia Os</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L164" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>down under</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Peaches!</v>
+        <v>down under - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>5:00</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>The Black Keys</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L165" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Light as a Feather</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Everything Glows</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:36</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Cannons</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L166" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Loving One</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Loving One - Single</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G167" t="str">
-        <v>3:39</v>
+        <v>3:02</v>
       </c>
       <c r="H167" t="str">
-        <v>People I’ve Met</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L167" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Both Can Be True</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G168" t="str">
-        <v>3:05</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>Trousdale</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L168" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Buffalo 66</v>
+        <v>Trouble</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G169" t="str">
-        <v>4:27</v>
+        <v>3:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Nessa Barrett</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L169" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>brb</v>
+        <v>judas</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>brb - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:36</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>The Two Lips</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L170" t="str">
-        <v>brb - The Two Lips</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Euphoria</v>
+        <v>JINX</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Euphoria - Single</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:32</v>
+        <v>2:54</v>
       </c>
       <c r="H171" t="str">
-        <v>Talia Rae</v>
+        <v>Zacari</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L171" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>if i'm lucky</v>
+        <v>se fue</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Náufrago</v>
       </c>
       <c r="G172" t="str">
-        <v>2:57</v>
+        <v>2:51</v>
       </c>
       <c r="H172" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Eddy</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L172" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Gracie</v>
+        <v>The Blade</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>F.I.G</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:54</v>
+        <v>3:15</v>
       </c>
       <c r="H173" t="str">
-        <v>Naomi Scott</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L173" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>down under</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>down under - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:24</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>Kevian Kraemer</v>
+        <v>SPINALL</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L174" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Send Me A Sign</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:15</v>
+        <v>2:15</v>
       </c>
       <c r="H175" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>ZEP</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L175" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:02</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>OneRepublic</v>
+        <v>Hutch</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L176" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Dream Chaser</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Dream Chaser</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:14</v>
+        <v>5:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Willie Nelson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L177" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Trouble</v>
+        <v>Cyclone</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Girlfriend</v>
+        <v>Loss</v>
       </c>
       <c r="G178" t="str">
-        <v>3:17</v>
+        <v>5:33</v>
       </c>
       <c r="H178" t="str">
-        <v>Grace Ives</v>
+        <v>Gaerea</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L178" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>judas</v>
+        <v>Checkmate</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>judas - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:31</v>
+        <v>4:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Josiah Queen</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L179" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>JINX</v>
+        <v>DAVE</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>JINX - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:54</v>
+        <v>2:01</v>
       </c>
       <c r="H180" t="str">
-        <v>Zacari</v>
+        <v>Hulvey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L180" t="str">
-        <v>JINX - Zacari</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>se fue</v>
+        <v>Change</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Náufrago</v>
+        <v>Change - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H181" t="str">
-        <v>Eddy</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L181" t="str">
-        <v>se fue - Eddy</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The Blade</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>The Blade - Single</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:15</v>
+        <v>3:05</v>
       </c>
       <c r="H182" t="str">
-        <v>Kingfishr</v>
+        <v>Maisak</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L182" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Metric Rules</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>V</v>
       </c>
       <c r="G183" t="str">
-        <v>3:13</v>
+        <v>2:01</v>
       </c>
       <c r="H183" t="str">
-        <v>SPINALL</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L183" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G184" t="str">
-        <v>2:15</v>
+        <v>3:53</v>
       </c>
       <c r="H184" t="str">
-        <v>ZEP</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L184" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>punchbowl</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:23</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>Hutch</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L185" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>5:15</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>MJ Cole</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L186" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Cyclone</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Loss</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>5:33</v>
+        <v>2:03</v>
       </c>
       <c r="H187" t="str">
-        <v>Gaerea</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L187" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Checkmate</v>
+        <v>Free Nick</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Checkmate - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:23</v>
+        <v>2:05</v>
       </c>
       <c r="H188" t="str">
-        <v>Blue Medusa</v>
+        <v>Raq baby</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L188" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DAVE</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>DAVE - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:01</v>
+        <v>3:06</v>
       </c>
       <c r="H189" t="str">
-        <v>Hulvey</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L189" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Change</v>
+        <v>Define You</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Change - Single</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:38</v>
+        <v>3:34</v>
       </c>
       <c r="H190" t="str">
-        <v>Stephen Stanley</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L190" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Te Entiendo</v>
+        <v>If You Change</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G191" t="str">
-        <v>3:05</v>
+        <v>4:41</v>
       </c>
       <c r="H191" t="str">
-        <v>Maisak</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L191" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>CHEVROLET 90</v>
+        <v>What I See</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>V</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:01</v>
+        <v>2:32</v>
       </c>
       <c r="H192" t="str">
-        <v>Rey Quinto</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L192" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Tirabalas</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>Butterfly</v>
       </c>
       <c r="G193" t="str">
-        <v>3:53</v>
+        <v>3:47</v>
       </c>
       <c r="H193" t="str">
-        <v>Hans el Oso</v>
+        <v>Witch Post</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L193" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>punchbowl</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>punchbowl - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:34</v>
+        <v>3:07</v>
       </c>
       <c r="H194" t="str">
-        <v>Julio Caesar</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L194" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Wild Ride</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Wild Ride - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:41</v>
+        <v>2:52</v>
       </c>
       <c r="H195" t="str">
-        <v>Durand Bernarr</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L195" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Lamb Chop</v>
+        <v>Rewind It</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:03</v>
+        <v>1:34</v>
       </c>
       <c r="H196" t="str">
-        <v>Chuckyy</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L196" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Free Nick</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Free Nick - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:05</v>
+        <v>2:33</v>
       </c>
       <c r="H197" t="str">
-        <v>Raq baby</v>
+        <v>slayr</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L197" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Make Me Brand New</v>
+        <v>Down</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:06</v>
+        <v>2:08</v>
       </c>
       <c r="H198" t="str">
-        <v>Dante’ Pride</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L198" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Define You</v>
+        <v>Make It Out</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-23</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Define You - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:34</v>
+        <v>2:17</v>
       </c>
       <c r="H199" t="str">
-        <v>Luca Fogale</v>
+        <v>Trueblood</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L199" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>If You Change</v>
+        <v>better than boston</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-23</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Roses</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:41</v>
+        <v>3:02</v>
       </c>
       <c r="H200" t="str">
-        <v>Widowspeak</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L200" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>What I See</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-23</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:32</v>
+        <v>2:34</v>
       </c>
       <c r="H201" t="str">
-        <v>See You Next Year</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L201" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Witching Hour</v>
+        <v>All I Need</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-23</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Butterfly</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:47</v>
+        <v>3:06</v>
       </c>
       <c r="H202" t="str">
-        <v>Witch Post</v>
+        <v>GRiZ</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L202" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Actin' Tough</v>
+        <v>Weeping Tones</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-23</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Peace In Place</v>
       </c>
       <c r="G203" t="str">
-        <v>3:07</v>
+        <v>2:59</v>
       </c>
       <c r="H203" t="str">
-        <v>Dean Turnley</v>
+        <v>Poison the Well</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
       </c>
       <c r="L203" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Weeping Tones - Poison the Well</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Promise You This</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D204" t="str">
         <v>2026-03-23</v>
@@ -8127,372 +8127,30 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G204" t="str">
-        <v>2:52</v>
+        <v>5:19</v>
       </c>
       <c r="H204" t="str">
-        <v>Anais Cardot</v>
+        <v>Exodus</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
       <c r="L204" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Rewind It</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Rewind It - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>1:34</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Nino Paid</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Rewind It - Nino Paid</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Turn It Up</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Turn It Up - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>2:33</v>
-      </c>
-      <c r="H206" t="str">
-        <v>slayr</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Turn It Up - slayr</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Down</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Down - Single</v>
-      </c>
-      <c r="G207" t="str">
-        <v>2:08</v>
-      </c>
-      <c r="H207" t="str">
-        <v>MexikoDro</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Down - MexikoDro</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Make It Out</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Make It Out - Single</v>
-      </c>
-      <c r="G208" t="str">
-        <v>2:17</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Trueblood</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Make It Out - Trueblood</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>better than boston</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>better than boston - Single</v>
-      </c>
-      <c r="G209" t="str">
-        <v>3:02</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Tom Siletto</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
-      </c>
-      <c r="L209" t="str">
-        <v>better than boston - Tom Siletto</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>So Much Beauty (Around Us)</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
-      </c>
-      <c r="G210" t="str">
-        <v>2:34</v>
-      </c>
-      <c r="H210" t="str">
-        <v>Lost Frequencies</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
-      </c>
-      <c r="L210" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>All I Need</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>All I Need - Single</v>
-      </c>
-      <c r="G211" t="str">
-        <v>3:06</v>
-      </c>
-      <c r="H211" t="str">
-        <v>GRiZ</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
-      </c>
-      <c r="L211" t="str">
-        <v>All I Need - GRiZ</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Weeping Tones</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Peace In Place</v>
-      </c>
-      <c r="G212" t="str">
-        <v>2:59</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Poison the Well</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
-      </c>
-      <c r="L212" t="str">
-        <v>Weeping Tones - Poison the Well</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Promise You This</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>Goliath</v>
-      </c>
-      <c r="G213" t="str">
-        <v>5:19</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Exodus</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
-      </c>
-      <c r="L213" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:31</v>
@@ -1237,7 +1237,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:46</v>

--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>רועי שילה – הפרחים גבוהים עליסה</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a2%d7%99-%d7%a9%d7%99%d7%9c%d7%94-%d7%94%d7%a4%d7%a8%d7%97%d7%99%d7%9d-%d7%92%d7%91%d7%95%d7%94%d7%99%d7%9d-%d7%a2%d7%9c%d7%99%d7%a1%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>רועי שילה שר שיר קצר עדין, כמעט חלומי אבל עמוס במשמעות, שנע בין אהבה, התמסרות ואובדן גבולות זהות. “הפרחים גבוהים עליסה” – משפט  פשוט — אבל הוא טעון מאוד, שאומר: אנחנו נמצאים במרחב לא לגמרי מציאותי, אולי תודעתי או רגשי.</v>
       </c>
       <c r="G2" t="str">
-        <v>3:17</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>רועי שילה – הפרחים גבוהים עליסה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H3" t="str">
-        <v>Nick Carter</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B4" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-23</v>
@@ -530,10 +530,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H4" t="str">
-        <v>Carly Pearce</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-23</v>
@@ -568,10 +568,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:11</v>
+        <v>3:38</v>
       </c>
       <c r="H5" t="str">
-        <v>OneRepublic</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-23</v>
@@ -606,10 +606,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:57</v>
+        <v>4:11</v>
       </c>
       <c r="H6" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B7" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-23</v>
@@ -644,10 +644,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:47</v>
+        <v>2:57</v>
       </c>
       <c r="H7" t="str">
-        <v>Armin van Buuren</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>7:10</v>
+        <v>3:47</v>
       </c>
       <c r="H8" t="str">
-        <v>David Gilmour</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:06</v>
+        <v>7:10</v>
       </c>
       <c r="H9" t="str">
-        <v>Grace Enger</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B10" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-23</v>
@@ -758,10 +758,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:05</v>
+        <v>3:06</v>
       </c>
       <c r="H10" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-23</v>
@@ -796,10 +796,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:12</v>
+        <v>3:05</v>
       </c>
       <c r="H11" t="str">
-        <v>Freya Ridings</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B12" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-23</v>
@@ -834,10 +834,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>9:11</v>
+        <v>3:12</v>
       </c>
       <c r="H12" t="str">
-        <v>David Gilmour</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B13" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-23</v>
@@ -872,10 +872,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:49</v>
+        <v>9:11</v>
       </c>
       <c r="H13" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B14" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-23</v>
@@ -910,10 +910,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:28</v>
+        <v>3:49</v>
       </c>
       <c r="H14" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B15" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-23</v>
@@ -948,10 +948,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:31</v>
+        <v>3:28</v>
       </c>
       <c r="H15" t="str">
-        <v>Martin Garrix</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-23</v>
@@ -986,10 +986,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:11</v>
+        <v>3:31</v>
       </c>
       <c r="H16" t="str">
-        <v>Baby Queen</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-23</v>
@@ -1024,10 +1024,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:27</v>
+        <v>3:11</v>
       </c>
       <c r="H17" t="str">
-        <v>HAUSER</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B18" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-23</v>
@@ -1062,10 +1062,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H18" t="str">
-        <v>Holly Humberstone</v>
+        <v>HAUSER</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B19" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-23</v>
@@ -1100,10 +1100,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:50</v>
+        <v>3:34</v>
       </c>
       <c r="H19" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-23</v>
@@ -1138,10 +1138,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:51</v>
+        <v>2:50</v>
       </c>
       <c r="H20" t="str">
-        <v>Rick Astley</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:39</v>
+        <v>3:51</v>
       </c>
       <c r="H21" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:08</v>
+        <v>2:39</v>
       </c>
       <c r="H22" t="str">
-        <v>Jessie J</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B23" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-23</v>
@@ -1252,10 +1252,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:46</v>
+        <v>5:08</v>
       </c>
       <c r="H23" t="str">
-        <v>Bishop Briggs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B24" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-23</v>
@@ -1290,10 +1290,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:42</v>
+        <v>3:46</v>
       </c>
       <c r="H24" t="str">
-        <v>Dean Lewis</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-23</v>
@@ -1328,10 +1328,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:31</v>
+        <v>2:42</v>
       </c>
       <c r="H25" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-23</v>
@@ -1366,10 +1366,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:14</v>
+        <v>2:31</v>
       </c>
       <c r="H26" t="str">
-        <v>Luke Combs</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B27" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-23</v>
@@ -1404,10 +1404,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H27" t="str">
-        <v>Allison Russell</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-23</v>
@@ -1442,10 +1442,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:43</v>
+        <v>3:22</v>
       </c>
       <c r="H28" t="str">
-        <v>We Three</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B29" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-23</v>
@@ -1480,10 +1480,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:54</v>
+        <v>3:43</v>
       </c>
       <c r="H29" t="str">
-        <v>paris jackson</v>
+        <v>We Three</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B30" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-23</v>
@@ -1518,10 +1518,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H30" t="str">
-        <v>Kane Brown</v>
+        <v>paris jackson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-23</v>
@@ -1556,10 +1556,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:37</v>
+        <v>2:46</v>
       </c>
       <c r="H31" t="str">
-        <v>Lainey Wilson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-23</v>
@@ -1594,10 +1594,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:57</v>
+        <v>3:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Malcolm Todd</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-23</v>
@@ -1632,10 +1632,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:38</v>
+        <v>2:57</v>
       </c>
       <c r="H33" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-23</v>
@@ -1670,10 +1670,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:29</v>
+        <v>3:38</v>
       </c>
       <c r="H34" t="str">
-        <v>Kungs</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B35" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-23</v>
@@ -1708,10 +1708,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:28</v>
+        <v>4:29</v>
       </c>
       <c r="H35" t="str">
-        <v>Sunday (1994)</v>
+        <v>Kungs</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B36" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-23</v>
@@ -1746,10 +1746,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:26</v>
+        <v>4:28</v>
       </c>
       <c r="H36" t="str">
-        <v>aron!</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B37" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-23</v>
@@ -1784,10 +1784,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:51</v>
+        <v>3:26</v>
       </c>
       <c r="H37" t="str">
-        <v>Colinstoughmusic</v>
+        <v>aron!</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B38" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-23</v>
@@ -1822,10 +1822,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:49</v>
+        <v>3:51</v>
       </c>
       <c r="H38" t="str">
-        <v>Sunday (1994)</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B39" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-23</v>
@@ -1860,10 +1860,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:16</v>
+        <v>2:49</v>
       </c>
       <c r="H39" t="str">
-        <v>Owen Riegling</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-23</v>
@@ -1901,7 +1901,7 @@
         <v>4:16</v>
       </c>
       <c r="H40" t="str">
-        <v>LANY</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B41" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-23</v>
@@ -1936,10 +1936,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H41" t="str">
-        <v>Maverick Sabre</v>
+        <v>LANY</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B42" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-23</v>
@@ -1974,10 +1974,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:50</v>
+        <v>3:25</v>
       </c>
       <c r="H42" t="str">
-        <v>Amanda Jordan</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B43" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-23</v>
@@ -2012,10 +2012,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:57</v>
+        <v>2:50</v>
       </c>
       <c r="H43" t="str">
-        <v>Beabadoobee</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B44" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-23</v>
@@ -2050,10 +2050,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:58</v>
+        <v>3:57</v>
       </c>
       <c r="H44" t="str">
-        <v>Spacey Jane</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-23</v>
@@ -2088,10 +2088,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:25</v>
+        <v>3:58</v>
       </c>
       <c r="H45" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:09</v>
+        <v>3:25</v>
       </c>
       <c r="H46" t="str">
-        <v>Mei Semones</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B47" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-23</v>
@@ -2164,10 +2164,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:08</v>
+        <v>4:09</v>
       </c>
       <c r="H47" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:57</v>
+        <v>2:08</v>
       </c>
       <c r="H48" t="str">
-        <v>Natalie Jane</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-23</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:13</v>
+        <v>2:57</v>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-23</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H50" t="str">
-        <v>David Gilmour</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-23</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:57</v>
+        <v>4:12</v>
       </c>
       <c r="H51" t="str">
-        <v>Far Caspian</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:34</v>
+        <v>3:57</v>
       </c>
       <c r="H52" t="str">
-        <v>Celine Dion</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:48</v>
+        <v>3:34</v>
       </c>
       <c r="H53" t="str">
-        <v>Harry Styles</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-23</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:58</v>
+        <v>3:48</v>
       </c>
       <c r="H54" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-23</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:33</v>
+        <v>4:58</v>
       </c>
       <c r="H55" t="str">
-        <v>Ellise</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-23</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:01</v>
+        <v>2:33</v>
       </c>
       <c r="H56" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Ellise</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-23</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:56</v>
+        <v>5:01</v>
       </c>
       <c r="H57" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-23</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:54</v>
+        <v>4:56</v>
       </c>
       <c r="H58" t="str">
-        <v>Bebe Rexha</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-23</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H59" t="str">
-        <v>NathanEvanss</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-23</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H60" t="str">
-        <v>R3HAB</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-23</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>R3HAB</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-23</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:16</v>
+        <v>3:21</v>
       </c>
       <c r="H62" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-23</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H63" t="str">
-        <v>Johnny Orlando</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-23</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:29</v>
+        <v>2:41</v>
       </c>
       <c r="H64" t="str">
-        <v>Russell Dickerson</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-23</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H65" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-23</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:46</v>
+        <v>2:43</v>
       </c>
       <c r="H66" t="str">
-        <v>Matt Hansen</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:01</v>
+        <v>3:46</v>
       </c>
       <c r="H67" t="str">
-        <v>Mike Posner</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:23</v>
+        <v>4:01</v>
       </c>
       <c r="H68" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H69" t="str">
-        <v>almost monday</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H70" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>almost monday</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H71" t="str">
-        <v>vaultboy</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-23</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H72" t="str">
-        <v>The Warning</v>
+        <v>vaultboy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-23</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="H73" t="str">
-        <v>aron!</v>
+        <v>The Warning</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-23</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:43</v>
+        <v>2:14</v>
       </c>
       <c r="H74" t="str">
-        <v>Bazzi</v>
+        <v>aron!</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-23</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Sting</v>
+        <v>Bazzi</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-23</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:44</v>
+        <v>4:43</v>
       </c>
       <c r="H76" t="str">
-        <v>Dean Lewis</v>
+        <v>Sting</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-23</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>2:44</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-23</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:52</v>
+        <v>4:37</v>
       </c>
       <c r="H78" t="str">
-        <v>Cannons</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-23</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:13</v>
+        <v>4:52</v>
       </c>
       <c r="H79" t="str">
-        <v>Kim Petras</v>
+        <v>Cannons</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-23</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:19</v>
+        <v>2:13</v>
       </c>
       <c r="H80" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-23</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:31</v>
+        <v>3:19</v>
       </c>
       <c r="H81" t="str">
-        <v>Kiana Ledé</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-23</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:43</v>
+        <v>2:31</v>
       </c>
       <c r="H82" t="str">
-        <v>Ringo Starr</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-23</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>2:43</v>
       </c>
       <c r="H83" t="str">
-        <v>Maya Hawke</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-23</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:55</v>
+        <v>3:10</v>
       </c>
       <c r="H84" t="str">
-        <v>Armin van Buuren</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-23</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:52</v>
+        <v>3:55</v>
       </c>
       <c r="H85" t="str">
-        <v>Demi Lovato</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-23</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:53</v>
+        <v>3:52</v>
       </c>
       <c r="H86" t="str">
-        <v>Peter Gabriel</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:30</v>
+        <v>2:53</v>
       </c>
       <c r="H87" t="str">
-        <v>Jessie J</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-23</v>
@@ -3722,10 +3722,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:18</v>
+        <v>4:30</v>
       </c>
       <c r="H88" t="str">
-        <v>Harry Styles</v>
+        <v>Jessie J</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-23</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H89" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-23</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H90" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-23</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H91" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-23</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H92" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-23</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H93" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-23</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H94" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-23</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H95" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-23</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H96" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-23</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H97" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-23</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H98" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-23</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H99" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-23</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H100" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-23</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H101" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SWIM</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>ARIRANG</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:39</v>
+        <v>3:40</v>
       </c>
       <c r="H102" t="str">
-        <v>BTS</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>SWIM - BTS</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>SWIM</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G103" t="str">
-        <v>5:01</v>
+        <v>2:39</v>
       </c>
       <c r="H103" t="str">
-        <v>RAYE</v>
+        <v>BTS</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L103" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Loving Life Again</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G104" t="str">
-        <v>3:46</v>
+        <v>5:01</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>RAYE</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L104" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Rethink Some Things</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Way I Am</v>
+        <v>Dandelion</v>
       </c>
       <c r="G105" t="str">
-        <v>2:45</v>
+        <v>3:46</v>
       </c>
       <c r="H105" t="str">
-        <v>Luke Combs</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L105" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TRANKAITO</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G106" t="str">
-        <v>2:42</v>
+        <v>2:45</v>
       </c>
       <c r="H106" t="str">
-        <v>Feid</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L106" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Leak It</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Leak It - Single</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G107" t="str">
-        <v>3:03</v>
+        <v>2:42</v>
       </c>
       <c r="H107" t="str">
-        <v>FLO</v>
+        <v>Feid</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L107" t="str">
-        <v>Leak It - FLO</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>LUVAGIRL</v>
+        <v>Leak It</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:40</v>
+        <v>3:03</v>
       </c>
       <c r="H108" t="str">
-        <v>Coco Jones</v>
+        <v>FLO</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L108" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>D33P3R</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>R3SET</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:25</v>
+        <v>2:40</v>
       </c>
       <c r="H109" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L109" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>D33P3R</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>R3SET</v>
       </c>
       <c r="G110" t="str">
-        <v>3:01</v>
+        <v>3:25</v>
       </c>
       <c r="H110" t="str">
-        <v>Yeat</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L110" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Don't Hate Me</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:09</v>
+        <v>3:01</v>
       </c>
       <c r="H111" t="str">
-        <v>Miles Caton</v>
+        <v>Yeat</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L111" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Pongo</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Pongo - Single</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G112" t="str">
         <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Rvssian</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L112" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>BOTERO</v>
+        <v>Pongo</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>BOTERO - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:14</v>
+        <v>3:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Maluma</v>
+        <v>Rvssian</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L113" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Distance</v>
+        <v>BOTERO</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Distance - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Finn Askew</v>
+        <v>Maluma</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L114" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Distance</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H115" t="str">
-        <v>Dionne Warwick</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L115" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H116" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L116" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2.0</v>
+        <v>Riptides</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>ARIRANG</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G117" t="str">
-        <v>2:49</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>BTS</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L117" t="str">
-        <v>2.0 - BTS</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>6IXER PARTY</v>
+        <v>2.0</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>6WA</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G118" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H118" t="str">
-        <v>BigXthaPlug</v>
+        <v>BTS</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L118" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Highest</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Detour</v>
+        <v>6WA</v>
       </c>
       <c r="G119" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H119" t="str">
-        <v>Samara Cyn</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L119" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>Highest</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Detour</v>
       </c>
       <c r="G120" t="str">
-        <v>2:40</v>
+        <v>2:56</v>
       </c>
       <c r="H120" t="str">
-        <v>Coi Leray</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L120" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>So What</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:31</v>
+        <v>2:40</v>
       </c>
       <c r="H121" t="str">
-        <v>MUNA</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L121" t="str">
-        <v>So What - MUNA</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>So What</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G122" t="str">
-        <v>3:12</v>
+        <v>4:31</v>
       </c>
       <c r="H122" t="str">
-        <v>Eli</v>
+        <v>MUNA</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L122" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Running To Pain</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>So Help Me God</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G123" t="str">
-        <v>4:06</v>
+        <v>3:12</v>
       </c>
       <c r="H123" t="str">
-        <v>Kelsey Lu</v>
+        <v>Eli</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L123" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G124" t="str">
-        <v>2:14</v>
+        <v>4:06</v>
       </c>
       <c r="H124" t="str">
-        <v>Anitta</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L124" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Big Mama</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:20</v>
+        <v>2:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Latto</v>
+        <v>Anitta</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L125" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Bird Flu</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Big Mama</v>
       </c>
       <c r="G126" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H126" t="str">
-        <v>6LACK</v>
+        <v>Latto</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L126" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Lighter</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G127" t="str">
-        <v>2:59</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>Jelly Roll</v>
+        <v>6LACK</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L127" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Wide Awake</v>
+        <v>Lighter</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:16</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>Chris Stussy</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L128" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:25</v>
+        <v>4:16</v>
       </c>
       <c r="H129" t="str">
-        <v>Lizzo</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L129" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Dinner Party</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:34</v>
+        <v>3:25</v>
       </c>
       <c r="H130" t="str">
-        <v>Niall Horan</v>
+        <v>Lizzo</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L130" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>NORMAL</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>ARIRANG</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G131" t="str">
-        <v>3:01</v>
+        <v>2:34</v>
       </c>
       <c r="H131" t="str">
-        <v>BTS</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L131" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Die Living</v>
+        <v>NORMAL</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Die Living - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>3:01</v>
       </c>
       <c r="H132" t="str">
-        <v>ILLENIUM</v>
+        <v>BTS</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L132" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Heaven On Earth</v>
+        <v>Die Living</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:59</v>
+        <v>2:50</v>
       </c>
       <c r="H133" t="str">
-        <v>Pentatonix</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L133" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>an apple a day</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>an apple a day - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>5:16</v>
+        <v>2:59</v>
       </c>
       <c r="H134" t="str">
-        <v>horsegiirL</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L134" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>OUT LATE.</v>
+        <v>an apple a day</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:09</v>
+        <v>5:16</v>
       </c>
       <c r="H135" t="str">
-        <v>Loud Luxury</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L135" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Be With You</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>The Wow! Signal</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:35</v>
+        <v>2:09</v>
       </c>
       <c r="H136" t="str">
-        <v>Muse</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L136" t="str">
-        <v>Be With You - Muse</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>First Red Rays</v>
+        <v>Be With You</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G137" t="str">
-        <v>8:27</v>
+        <v>3:35</v>
       </c>
       <c r="H137" t="str">
-        <v>Neurosis</v>
+        <v>Muse</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L137" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Caught In The Echo</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Your Favorite Toy</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G138" t="str">
-        <v>4:02</v>
+        <v>8:27</v>
       </c>
       <c r="H138" t="str">
-        <v>Foo Fighters</v>
+        <v>Neurosis</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L138" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Little by Little</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Little by Little - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G139" t="str">
-        <v>2:34</v>
+        <v>4:02</v>
       </c>
       <c r="H139" t="str">
-        <v>Mon Rovîa</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L139" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Montgomery County</v>
+        <v>Little by Little</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:28</v>
+        <v>2:34</v>
       </c>
       <c r="H140" t="str">
-        <v>Parker McCollum</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L140" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dive Into Me</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G141" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H141" t="str">
-        <v>Alok</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L141" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>more than just a little bit</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>getting up to no good</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H142" t="str">
-        <v>Artemas</v>
+        <v>Alok</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L142" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>WORSHIP</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>WORSHIP - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G143" t="str">
-        <v>2:43</v>
+        <v>2:40</v>
       </c>
       <c r="H143" t="str">
-        <v>Asake</v>
+        <v>Artemas</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L143" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Honest</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Honest - Single</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:22</v>
+        <v>2:43</v>
       </c>
       <c r="H144" t="str">
-        <v>Ebony Riley</v>
+        <v>Asake</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L144" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>6ft Under</v>
+        <v>Honest</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>6ft Under - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H145" t="str">
-        <v>KELS</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L145" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Maybe Again</v>
+        <v>6ft Under</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>When The City Sleeps</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H146" t="str">
-        <v>Alex Isley</v>
+        <v>KELS</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L146" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Trigger Happy</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Attachment Theory</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>3:29</v>
       </c>
       <c r="H147" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L147" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G148" t="str">
         <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Kid Cudi</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L148" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H149" t="str">
-        <v>Swae Lee</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L149" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Runnin' On E</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G150" t="str">
-        <v>2:27</v>
+        <v>3:30</v>
       </c>
       <c r="H150" t="str">
-        <v>Wyatt Flores</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L150" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>FREESTYLE</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LINAJE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:36</v>
+        <v>2:27</v>
       </c>
       <c r="H151" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L151" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Orcasitas</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Alma De Cántaro</v>
+        <v>LINAJE</v>
       </c>
       <c r="G152" t="str">
-        <v>3:23</v>
+        <v>5:36</v>
       </c>
       <c r="H152" t="str">
-        <v>marquitos</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L152" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Vida Loca</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G153" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H153" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>marquitos</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L153" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>The Weight of the Woods</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G154" t="str">
-        <v>3:39</v>
+        <v>2:35</v>
       </c>
       <c r="H154" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L154" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Honest</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G155" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H155" t="str">
-        <v>Kenia Os</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L155" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Peaches!</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G156" t="str">
-        <v>5:00</v>
+        <v>3:01</v>
       </c>
       <c r="H156" t="str">
-        <v>The Black Keys</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L156" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Light as a Feather</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Everything Glows</v>
+        <v>Peaches!</v>
       </c>
       <c r="G157" t="str">
-        <v>3:36</v>
+        <v>5:00</v>
       </c>
       <c r="H157" t="str">
-        <v>Cannons</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L157" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Loving One</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Loving One - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H158" t="str">
-        <v>People I’ve Met</v>
+        <v>Cannons</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L158" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Both Can Be True</v>
+        <v>Loving One</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H159" t="str">
-        <v>Trousdale</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L159" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Buffalo 66</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>4:27</v>
+        <v>3:05</v>
       </c>
       <c r="H160" t="str">
-        <v>Nessa Barrett</v>
+        <v>Trousdale</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L160" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>brb</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>brb - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G161" t="str">
-        <v>2:36</v>
+        <v>4:27</v>
       </c>
       <c r="H161" t="str">
-        <v>The Two Lips</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L161" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Euphoria</v>
+        <v>brb</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Euphoria - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H162" t="str">
-        <v>Talia Rae</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L162" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>if i'm lucky</v>
+        <v>Euphoria</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H163" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L163" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Gracie</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>F.I.G</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H164" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L164" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>down under</v>
+        <v>Gracie</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>down under - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>2:54</v>
       </c>
       <c r="H165" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L165" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Send Me A Sign</v>
+        <v>down under</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>down under - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H166" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L166" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:02</v>
+        <v>3:15</v>
       </c>
       <c r="H167" t="str">
-        <v>OneRepublic</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L167" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Dream Chaser</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dream Chaser</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G168" t="str">
-        <v>3:14</v>
+        <v>3:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Willie Nelson</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L168" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Trouble</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Girlfriend</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G169" t="str">
-        <v>3:17</v>
+        <v>3:14</v>
       </c>
       <c r="H169" t="str">
-        <v>Grace Ives</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L169" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>judas</v>
+        <v>Trouble</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>judas - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G170" t="str">
-        <v>3:31</v>
+        <v>3:17</v>
       </c>
       <c r="H170" t="str">
-        <v>Josiah Queen</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L170" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>JINX</v>
+        <v>judas</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>JINX - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:54</v>
+        <v>3:31</v>
       </c>
       <c r="H171" t="str">
-        <v>Zacari</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L171" t="str">
-        <v>JINX - Zacari</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>se fue</v>
+        <v>JINX</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Náufrago</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H172" t="str">
-        <v>Eddy</v>
+        <v>Zacari</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L172" t="str">
-        <v>se fue - Eddy</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>The Blade</v>
+        <v>se fue</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>The Blade - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G173" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H173" t="str">
-        <v>Kingfishr</v>
+        <v>Eddy</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L173" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Metric Rules</v>
+        <v>The Blade</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H174" t="str">
-        <v>SPINALL</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L174" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>2:15</v>
+        <v>3:13</v>
       </c>
       <c r="H175" t="str">
-        <v>ZEP</v>
+        <v>SPINALL</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L175" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:23</v>
+        <v>2:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Hutch</v>
+        <v>ZEP</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L176" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>5:15</v>
+        <v>3:23</v>
       </c>
       <c r="H177" t="str">
-        <v>MJ Cole</v>
+        <v>Hutch</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L177" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cyclone</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Loss</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:33</v>
+        <v>5:15</v>
       </c>
       <c r="H178" t="str">
-        <v>Gaerea</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L178" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Checkmate</v>
+        <v>Cyclone</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Checkmate - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G179" t="str">
-        <v>4:23</v>
+        <v>5:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Blue Medusa</v>
+        <v>Gaerea</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L179" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>DAVE</v>
+        <v>Checkmate</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>DAVE - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:01</v>
+        <v>4:23</v>
       </c>
       <c r="H180" t="str">
-        <v>Hulvey</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L180" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Change</v>
+        <v>DAVE</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Change - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:38</v>
+        <v>2:01</v>
       </c>
       <c r="H181" t="str">
-        <v>Stephen Stanley</v>
+        <v>Hulvey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L181" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Te Entiendo</v>
+        <v>Change</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:05</v>
+        <v>2:38</v>
       </c>
       <c r="H182" t="str">
-        <v>Maisak</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L182" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>V</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:01</v>
+        <v>3:05</v>
       </c>
       <c r="H183" t="str">
-        <v>Rey Quinto</v>
+        <v>Maisak</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L183" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Tirabalas</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>V</v>
       </c>
       <c r="G184" t="str">
-        <v>3:53</v>
+        <v>2:01</v>
       </c>
       <c r="H184" t="str">
-        <v>Hans el Oso</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L184" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>punchbowl</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>punchbowl - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G185" t="str">
-        <v>2:34</v>
+        <v>3:53</v>
       </c>
       <c r="H185" t="str">
-        <v>Julio Caesar</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L185" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Wild Ride</v>
+        <v>punchbowl</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Wild Ride - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>2:34</v>
       </c>
       <c r="H186" t="str">
-        <v>Durand Bernarr</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L186" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Lamb Chop</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:03</v>
+        <v>3:41</v>
       </c>
       <c r="H187" t="str">
-        <v>Chuckyy</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L187" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Free Nick</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Free Nick - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:05</v>
+        <v>2:03</v>
       </c>
       <c r="H188" t="str">
-        <v>Raq baby</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L188" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Make Me Brand New</v>
+        <v>Free Nick</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:06</v>
+        <v>2:05</v>
       </c>
       <c r="H189" t="str">
-        <v>Dante’ Pride</v>
+        <v>Raq baby</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L189" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Define You</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Define You - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:34</v>
+        <v>3:06</v>
       </c>
       <c r="H190" t="str">
-        <v>Luca Fogale</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L190" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>If You Change</v>
+        <v>Define You</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Roses</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:41</v>
+        <v>3:34</v>
       </c>
       <c r="H191" t="str">
-        <v>Widowspeak</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L191" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>What I See</v>
+        <v>If You Change</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G192" t="str">
-        <v>2:32</v>
+        <v>4:41</v>
       </c>
       <c r="H192" t="str">
-        <v>See You Next Year</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L192" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Witching Hour</v>
+        <v>What I See</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Butterfly</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:47</v>
+        <v>2:32</v>
       </c>
       <c r="H193" t="str">
-        <v>Witch Post</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L193" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Actin' Tough</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G194" t="str">
-        <v>3:07</v>
+        <v>3:47</v>
       </c>
       <c r="H194" t="str">
-        <v>Dean Turnley</v>
+        <v>Witch Post</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L194" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H195" t="str">
-        <v>Anais Cardot</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L195" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Rewind It</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Rewind It - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>1:34</v>
+        <v>2:52</v>
       </c>
       <c r="H196" t="str">
-        <v>Nino Paid</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L196" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Turn It Up</v>
+        <v>Rewind It</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-23</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:33</v>
+        <v>1:34</v>
       </c>
       <c r="H197" t="str">
-        <v>slayr</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L197" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Down</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-23</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Down - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:08</v>
+        <v>2:33</v>
       </c>
       <c r="H198" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L198" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Make It Out</v>
+        <v>Down</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-23</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Make It Out - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:17</v>
+        <v>2:08</v>
       </c>
       <c r="H199" t="str">
-        <v>Trueblood</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L199" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>better than boston</v>
+        <v>Make It Out</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-23</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>better than boston - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:02</v>
+        <v>2:17</v>
       </c>
       <c r="H200" t="str">
-        <v>Tom Siletto</v>
+        <v>Trueblood</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L200" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>better than boston</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-23</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H201" t="str">
-        <v>Lost Frequencies</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L201" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>All I Need</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D202" t="str">
         <v>2026-03-23</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>All I Need - Single</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:06</v>
+        <v>2:34</v>
       </c>
       <c r="H202" t="str">
-        <v>GRiZ</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L202" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Weeping Tones</v>
+        <v>All I Need</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D203" t="str">
         <v>2026-03-23</v>
@@ -8089,68 +8089,106 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Peace In Place</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H203" t="str">
-        <v>Poison the Well</v>
+        <v>GRiZ</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L203" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D204" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
+      <c r="D205" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G204" t="str">
+      <c r="G205" t="str">
         <v>5:19</v>
       </c>
-      <c r="H204" t="str">
+      <c r="H205" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K204" t="str">
+      <c r="K205" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L204" t="str">
+      <c r="L205" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רועי שילה – הפרחים גבוהים עליסה</v>
+        <v>שירה זלוף – הפסקה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a2%d7%99-%d7%a9%d7%99%d7%9c%d7%94-%d7%94%d7%a4%d7%a8%d7%97%d7%99%d7%9d-%d7%92%d7%91%d7%95%d7%94%d7%99%d7%9d-%d7%a2%d7%9c%d7%99%d7%a1%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%94%d7%a4%d7%a1%d7%a7%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>רועי שילה שר שיר קצר עדין, כמעט חלומי אבל עמוס במשמעות, שנע בין אהבה, התמסרות ואובדן גבולות זהות. “הפרחים גבוהים עליסה” – משפט  פשוט — אבל הוא טעון מאוד, שאומר: אנחנו נמצאים במרחב לא לגמרי מציאותי, אולי תודעתי או רגשי.</v>
+        <v>שירה זלוף שרה בלדה אישית, כואבת וחשופה, שיר זיכרון שהופך לווידוי ומווידוי להאשמה. זה שיר על איך חוויות בית ספר מהעבר ממשיכות לחיות בתוך הגוף והנפש שנים קדימה. העבר לא נשאר בעבר – הוא פולש להווה, מפריע לשינה, מעורר תגובות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רועי שילה – הפרחים גבוהים עליסה</v>
+        <v>שירה זלוף – הפסקה</v>
       </c>
     </row>
     <row r="3">

--- a/data/global/2026-03-week04/titles.xlsx
+++ b/data/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירה זלוף – הפסקה</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-23</v>
+        <v>6 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%94%d7%a4%d7%a1%d7%a7%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שירה זלוף שרה בלדה אישית, כואבת וחשופה, שיר זיכרון שהופך לווידוי ומווידוי להאשמה. זה שיר על איך חוויות בית ספר מהעבר ממשיכות לחיות בתוך הגוף והנפש שנים קדימה. העבר לא נשאר בעבר – הוא פולש להווה, מפריע לשינה, מעורר תגובות</v>
+        <v>6 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירה זלוף – הפסקה</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H3" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-23</v>
@@ -530,10 +530,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H4" t="str">
-        <v>Nick Carter</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B5" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-23</v>
@@ -568,10 +568,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:38</v>
+        <v>4:11</v>
       </c>
       <c r="H5" t="str">
-        <v>Carly Pearce</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B6" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-23</v>
@@ -606,10 +606,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:11</v>
+        <v>2:57</v>
       </c>
       <c r="H6" t="str">
-        <v>OneRepublic</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B7" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-23</v>
@@ -644,10 +644,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:57</v>
+        <v>3:47</v>
       </c>
       <c r="H7" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:47</v>
+        <v>7:10</v>
       </c>
       <c r="H8" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:10</v>
+        <v>3:06</v>
       </c>
       <c r="H9" t="str">
-        <v>David Gilmour</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-23</v>
@@ -758,10 +758,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:06</v>
+        <v>3:05</v>
       </c>
       <c r="H10" t="str">
-        <v>Grace Enger</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B11" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-23</v>
@@ -796,10 +796,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H11" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B12" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-23</v>
@@ -834,10 +834,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:12</v>
+        <v>9:11</v>
       </c>
       <c r="H12" t="str">
-        <v>Freya Ridings</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B13" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-23</v>
@@ -872,10 +872,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>9:11</v>
+        <v>3:49</v>
       </c>
       <c r="H13" t="str">
-        <v>David Gilmour</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B14" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-23</v>
@@ -910,10 +910,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:49</v>
+        <v>3:28</v>
       </c>
       <c r="H14" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jonas Brothers and Demi Lovato</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-23</v>
@@ -948,10 +948,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H15" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-23</v>
@@ -986,10 +986,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:31</v>
+        <v>3:11</v>
       </c>
       <c r="H16" t="str">
-        <v>Martin Garrix</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B17" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-23</v>
@@ -1024,10 +1024,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:11</v>
+        <v>2:27</v>
       </c>
       <c r="H17" t="str">
-        <v>Baby Queen</v>
+        <v>HAUSER</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>Holly Humberstone - Cruel World</v>
       </c>
       <c r="B18" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-23</v>
@@ -1062,10 +1062,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Holly Humberstone - Cruel World</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:34</v>
+        <v>2:50</v>
       </c>
       <c r="H19" t="str">
-        <v>Holly Humberstone</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Holly Humberstone - Cruel World - Holly Humberstone</v>
+        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H20" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-23</v>
@@ -1176,10 +1176,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:51</v>
+        <v>2:39</v>
       </c>
       <c r="H21" t="str">
-        <v>Rick Astley</v>
+        <v>Alan Walker and Emyrson Flora</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B22" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-23</v>
@@ -1214,10 +1214,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:39</v>
+        <v>5:08</v>
       </c>
       <c r="H22" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>Jessie J</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B23" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-23</v>
@@ -1252,10 +1252,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:08</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Jessie J</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-23</v>
@@ -1290,10 +1290,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:46</v>
+        <v>2:42</v>
       </c>
       <c r="H24" t="str">
-        <v>Bishop Briggs</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-23</v>
@@ -1328,10 +1328,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:42</v>
+        <v>2:31</v>
       </c>
       <c r="H25" t="str">
-        <v>Dean Lewis</v>
+        <v>Chris Janson and Official David Lee Murphy</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B26" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-23</v>
@@ -1366,10 +1366,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:31</v>
+        <v>3:14</v>
       </c>
       <c r="H26" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-23</v>
@@ -1404,10 +1404,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H27" t="str">
-        <v>Luke Combs</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B28" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-23</v>
@@ -1442,10 +1442,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:22</v>
+        <v>3:43</v>
       </c>
       <c r="H28" t="str">
-        <v>Allison Russell</v>
+        <v>We Three</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>paris jackson - zombies in love</v>
       </c>
       <c r="B29" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-23</v>
@@ -1480,10 +1480,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:43</v>
+        <v>2:54</v>
       </c>
       <c r="H29" t="str">
-        <v>We Three</v>
+        <v>paris jackson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>paris jackson - zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-23</v>
@@ -1518,10 +1518,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H30" t="str">
-        <v>paris jackson</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-23</v>
@@ -1556,10 +1556,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:46</v>
+        <v>3:37</v>
       </c>
       <c r="H31" t="str">
-        <v>Kane Brown</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-23</v>
@@ -1594,10 +1594,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:37</v>
+        <v>2:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Lainey Wilson</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-23</v>
@@ -1632,10 +1632,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H33" t="str">
-        <v>Malcolm Todd</v>
+        <v>Carly Pearce and Riley Green</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B34" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-23</v>
@@ -1670,10 +1670,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:38</v>
+        <v>4:29</v>
       </c>
       <c r="H34" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Kungs</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B35" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-23</v>
@@ -1708,10 +1708,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:29</v>
+        <v>4:28</v>
       </c>
       <c r="H35" t="str">
-        <v>Kungs</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B36" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-23</v>
@@ -1746,10 +1746,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:28</v>
+        <v>3:26</v>
       </c>
       <c r="H36" t="str">
-        <v>Sunday (1994)</v>
+        <v>aron!</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>aron! - Wonderful Thing (Piano) - aron!</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-23</v>
@@ -1784,10 +1784,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H37" t="str">
-        <v>aron!</v>
+        <v>Colinstoughmusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B38" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-23</v>
@@ -1822,10 +1822,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:51</v>
+        <v>2:49</v>
       </c>
       <c r="H38" t="str">
-        <v>Colinstoughmusic</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B39" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-23</v>
@@ -1860,10 +1860,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:49</v>
+        <v>4:16</v>
       </c>
       <c r="H39" t="str">
-        <v>Sunday (1994)</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B40" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-23</v>
@@ -1901,7 +1901,7 @@
         <v>4:16</v>
       </c>
       <c r="H40" t="str">
-        <v>Owen Riegling</v>
+        <v>LANY</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B41" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-23</v>
@@ -1936,10 +1936,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H41" t="str">
-        <v>LANY</v>
+        <v>Maverick Sabre</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B42" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-23</v>
@@ -1974,10 +1974,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H42" t="str">
-        <v>Maverick Sabre</v>
+        <v>Amanda Jordan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B43" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-23</v>
@@ -2012,10 +2012,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:50</v>
+        <v>3:57</v>
       </c>
       <c r="H43" t="str">
-        <v>Amanda Jordan</v>
+        <v>Beabadoobee</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:57</v>
+        <v>3:58</v>
       </c>
       <c r="H44" t="str">
-        <v>Beabadoobee</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:58</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>Spacey Jane</v>
+        <v>Spotify and Zara Larsson</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H46" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=1hh1WhFpib8</v>
+        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:09</v>
+        <v>2:08</v>
       </c>
       <c r="H47" t="str">
-        <v>Mei Semones</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mei Semones - Tooth Fairy ft. John Roseboro - Mei Semones</v>
+        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video)</v>
+        <v>Natalie Jane - sabotage (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TqCUlPDcPoE</v>
+        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:08</v>
+        <v>2:57</v>
       </c>
       <c r="H48" t="str">
-        <v>The Lemon Twigs</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Lemon Twigs - I Just Can't Get Over Losing You (Official Video) - The Lemon Twigs</v>
+        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video)</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=gTn_9WxrtuQ</v>
+        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-23</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:57</v>
+        <v>3:13</v>
       </c>
       <c r="H49" t="str">
-        <v>Natalie Jane</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Natalie Jane - sabotage (Lyric Video) - Natalie Jane</v>
+        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=lOiWuol3t3o</v>
+        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-23</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H50" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Vanilla Ninja - Too Epic To Be True | Estonia 🇪🇪 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006)</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Dv6ReB1nHGg</v>
+        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-23</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H51" t="str">
-        <v>David Gilmour</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>David Gilmour - Smile (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum)</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=JYe-XBcBquw</v>
+        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:57</v>
+        <v>3:34</v>
       </c>
       <c r="H52" t="str">
-        <v>Far Caspian</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>A Drawing Of The Sun (Live At Leeds Museum) - Far Caspian</v>
+        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=jRERD9mDWg4</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:34</v>
+        <v>3:48</v>
       </c>
       <c r="H53" t="str">
-        <v>Celine Dion</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Céline Dion - All By Myself (Live on Noel's House Party - BBC, 1996) - Celine Dion</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Harry Styles - American Girls (Official Video)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-23</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:48</v>
+        <v>4:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Harry Styles</v>
+        <v>Warner Records and Morrissey</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-23</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:58</v>
+        <v>2:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Warner Records and Morrissey</v>
+        <v>Ellise</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records and Morrissey</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ellise - Littlepill (Official Music Video)</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-23</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:33</v>
+        <v>5:01</v>
       </c>
       <c r="H56" t="str">
-        <v>Ellise</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-23</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:01</v>
+        <v>4:56</v>
       </c>
       <c r="H57" t="str">
-        <v>The Doobie Brothers</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-23</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:56</v>
+        <v>2:54</v>
       </c>
       <c r="H58" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-23</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:54</v>
+        <v>2:46</v>
       </c>
       <c r="H59" t="str">
-        <v>Bebe Rexha</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-23</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>NathanEvanss</v>
+        <v>R3HAB</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-23</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H61" t="str">
-        <v>R3HAB</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-23</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:21</v>
+        <v>3:16</v>
       </c>
       <c r="H62" t="str">
-        <v>War Child UK and Depeche Mode</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-23</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H63" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-23</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:41</v>
+        <v>2:29</v>
       </c>
       <c r="H64" t="str">
-        <v>Johnny Orlando</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-23</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:29</v>
+        <v>2:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Russell Dickerson</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-23</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H66" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H67" t="str">
-        <v>Matt Hansen</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:01</v>
+        <v>3:23</v>
       </c>
       <c r="H68" t="str">
-        <v>Mike Posner</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Katelyn Tarver</v>
+        <v>almost monday</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>almost monday - leaving is easy (official video)</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>almost monday - leaving is easy (official video) - almost monday</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H71" t="str">
-        <v>Anne Wilson and Cole Swindell</v>
+        <v>vaultboy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-23</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:25</v>
+        <v>3:49</v>
       </c>
       <c r="H72" t="str">
-        <v>vaultboy</v>
+        <v>The Warning</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Warning - Kerosene (Official Video)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-23</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:49</v>
+        <v>2:14</v>
       </c>
       <c r="H73" t="str">
-        <v>The Warning</v>
+        <v>aron!</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Warning - Kerosene (Official Video) - The Warning</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>aron! - Wonderful Thing (City View Video)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-23</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:14</v>
+        <v>2:43</v>
       </c>
       <c r="H74" t="str">
-        <v>aron!</v>
+        <v>Bazzi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bazzi - moment (Official Music Video)</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-23</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Bazzi</v>
+        <v>Sting</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-23</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:43</v>
+        <v>2:44</v>
       </c>
       <c r="H76" t="str">
-        <v>Sting</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-23</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:44</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-23</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:37</v>
+        <v>4:52</v>
       </c>
       <c r="H78" t="str">
-        <v>Jessie Ware</v>
+        <v>Cannons</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-23</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:52</v>
+        <v>2:13</v>
       </c>
       <c r="H79" t="str">
-        <v>Cannons</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-23</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H80" t="str">
-        <v>Kim Petras</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-23</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:19</v>
+        <v>2:31</v>
       </c>
       <c r="H81" t="str">
-        <v>Vanessa Carlton</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-23</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:31</v>
+        <v>2:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Kiana Ledé</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-23</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:43</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Ringo Starr</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-23</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:10</v>
+        <v>3:55</v>
       </c>
       <c r="H84" t="str">
-        <v>Maya Hawke</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-23</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:55</v>
+        <v>3:52</v>
       </c>
       <c r="H85" t="str">
-        <v>Armin van Buuren</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-23</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:52</v>
+        <v>2:53</v>
       </c>
       <c r="H86" t="str">
-        <v>Demi Lovato</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:53</v>
+        <v>4:30</v>
       </c>
       <c r="H87" t="str">
-        <v>Peter Gabriel</v>
+        <v>Jessie J</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B88" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-23</v>
@@ -3722,10 +3722,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:30</v>
+        <v>5:18</v>
       </c>
       <c r="H88" t="str">
-        <v>Jessie J</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-23</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-23</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-23</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H91" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-23</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H92" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-23</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H93" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-23</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-23</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H95" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-23</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H96" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-23</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H97" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-23</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-23</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H99" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-23</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H100" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-23</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H101" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>SWIM</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G102" t="str">
-        <v>3:40</v>
+        <v>2:39</v>
       </c>
       <c r="H102" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>BTS</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L102" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SWIM</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/swim/1868862384</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ARIRANG</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G103" t="str">
-        <v>2:39</v>
+        <v>5:01</v>
       </c>
       <c r="H103" t="str">
-        <v>BTS</v>
+        <v>RAYE</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/swim/1868862375</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L103" t="str">
-        <v>SWIM - BTS</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>5:01</v>
+        <v>3:46</v>
       </c>
       <c r="H104" t="str">
-        <v>RAYE</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Loving Life Again</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dandelion</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G105" t="str">
-        <v>3:46</v>
+        <v>2:45</v>
       </c>
       <c r="H105" t="str">
-        <v>Ella Langley</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L105" t="str">
-        <v>Loving Life Again - Ella Langley</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Rethink Some Things</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>The Way I Am</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G106" t="str">
-        <v>2:45</v>
+        <v>2:42</v>
       </c>
       <c r="H106" t="str">
-        <v>Luke Combs</v>
+        <v>Feid</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L106" t="str">
-        <v>Rethink Some Things - Luke Combs</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>TRANKAITO</v>
+        <v>Leak It</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:42</v>
+        <v>3:03</v>
       </c>
       <c r="H107" t="str">
-        <v>Feid</v>
+        <v>FLO</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/feid/194502100</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L107" t="str">
-        <v>TRANKAITO - Feid</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Leak It</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Leak It - Single</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:03</v>
+        <v>2:40</v>
       </c>
       <c r="H108" t="str">
-        <v>FLO</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L108" t="str">
-        <v>Leak It - FLO</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>LUVAGIRL</v>
+        <v>D33P3R</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>LUVAGIRL - Single</v>
+        <v>R3SET</v>
       </c>
       <c r="G109" t="str">
-        <v>2:40</v>
+        <v>3:25</v>
       </c>
       <c r="H109" t="str">
-        <v>Coco Jones</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L109" t="str">
-        <v>LUVAGIRL - Coco Jones</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>D33P3R</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>R3SET</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:25</v>
+        <v>3:01</v>
       </c>
       <c r="H110" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Yeat</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L110" t="str">
-        <v>D33P3R - Mike WiLL Made-It</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Let King Tonka Talk</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Let King Tonka Talk - Single</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:01</v>
+        <v>3:09</v>
       </c>
       <c r="H111" t="str">
-        <v>Yeat</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L111" t="str">
-        <v>Let King Tonka Talk - Yeat</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Don't Hate Me</v>
+        <v>PONGO</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Don't Hate Me - Single</v>
+        <v>PONGO - Single</v>
       </c>
       <c r="G112" t="str">
         <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Miles Caton</v>
+        <v>Rvssian</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L112" t="str">
-        <v>Don't Hate Me - Miles Caton</v>
+        <v>PONGO - Rvssian</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Pongo</v>
+        <v>BOTERO</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Pongo - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:09</v>
+        <v>4:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Rvssian</v>
+        <v>Maluma</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L113" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>BOTERO</v>
+        <v>Distance</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/botero/1884672859</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>BOTERO - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:14</v>
+        <v>3:14</v>
       </c>
       <c r="H114" t="str">
-        <v>Maluma</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/botero/1884672851</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L114" t="str">
-        <v>BOTERO - Maluma</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Distance</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Distance - Single</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:14</v>
+        <v>3:44</v>
       </c>
       <c r="H115" t="str">
-        <v>Finn Askew</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L115" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Riptides</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G116" t="str">
-        <v>3:44</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>Dionne Warwick</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L116" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Riptides</v>
+        <v>2.0</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>I Built You a Tower</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>2:49</v>
       </c>
       <c r="H117" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>BTS</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L117" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2.0</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/2-0/1868862380</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ARIRANG</v>
+        <v>6WA</v>
       </c>
       <c r="G118" t="str">
-        <v>2:49</v>
+        <v>3:08</v>
       </c>
       <c r="H118" t="str">
-        <v>BTS</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/2-0/1868862375</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L118" t="str">
-        <v>2.0 - BTS</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>6IXER PARTY</v>
+        <v>Highest</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>6WA</v>
+        <v>Detour</v>
       </c>
       <c r="G119" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H119" t="str">
-        <v>BigXthaPlug</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L119" t="str">
-        <v>6IXER PARTY - BigXthaPlug</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Highest</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/highest/1882162060</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Detour</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:56</v>
+        <v>2:40</v>
       </c>
       <c r="H120" t="str">
-        <v>Samara Cyn</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/highest/1882161774</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L120" t="str">
-        <v>Highest - Samara Cyn</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
+        <v>So What</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G121" t="str">
-        <v>2:40</v>
+        <v>4:31</v>
       </c>
       <c r="H121" t="str">
-        <v>Coi Leray</v>
+        <v>MUNA</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L121" t="str">
-        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>So What</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/so-what/1870703328</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G122" t="str">
-        <v>4:31</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>MUNA</v>
+        <v>Eli</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/so-what/1870702692</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L122" t="str">
-        <v>So What - MUNA</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G123" t="str">
-        <v>3:12</v>
+        <v>4:06</v>
       </c>
       <c r="H123" t="str">
-        <v>Eli</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L123" t="str">
-        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Running To Pain</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>So Help Me God</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:06</v>
+        <v>2:14</v>
       </c>
       <c r="H124" t="str">
-        <v>Kelsey Lu</v>
+        <v>Anitta</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L124" t="str">
-        <v>Running To Pain - Kelsey Lu</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Pinterest (Spanish)</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Pinterest (Spanish) - Single</v>
+        <v>Big Mama</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>4:20</v>
       </c>
       <c r="H125" t="str">
-        <v>Anitta</v>
+        <v>Latto</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L125" t="str">
-        <v>Pinterest (Spanish) - Anitta</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Business &amp; Personal (Intro)</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Big Mama</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G126" t="str">
-        <v>4:20</v>
+        <v>2:58</v>
       </c>
       <c r="H126" t="str">
-        <v>Latto</v>
+        <v>6LACK</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L126" t="str">
-        <v>Business &amp; Personal (Intro) - Latto</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Bird Flu</v>
+        <v>Lighter</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:59</v>
       </c>
       <c r="H127" t="str">
-        <v>6LACK</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L127" t="str">
-        <v>Bird Flu - 6LACK</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Lighter</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/lighter/1884704638</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Lighter (FIFA World Cup 2026™) - Single</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>4:16</v>
       </c>
       <c r="H128" t="str">
-        <v>Jelly Roll</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/lighter/1884704631</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L128" t="str">
-        <v>Lighter - Jelly Roll</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Wide Awake</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Wide Awake - Single</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:16</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>Chris Stussy</v>
+        <v>Lizzo</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L129" t="str">
-        <v>Wide Awake - Chris Stussy</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Don’t Make Me Love U</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Don’t Make Me Love U - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G130" t="str">
-        <v>3:25</v>
+        <v>2:34</v>
       </c>
       <c r="H130" t="str">
-        <v>Lizzo</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L130" t="str">
-        <v>Don’t Make Me Love U - Lizzo</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Dinner Party</v>
+        <v>NORMAL</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Dinner Party</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G131" t="str">
-        <v>2:34</v>
+        <v>3:01</v>
       </c>
       <c r="H131" t="str">
-        <v>Niall Horan</v>
+        <v>BTS</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L131" t="str">
-        <v>Dinner Party - Niall Horan</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>NORMAL</v>
+        <v>Die Living</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/normal/1868862387</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ARIRANG</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>BTS</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/bts/883131348</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/normal/1868862375</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L132" t="str">
-        <v>NORMAL - BTS</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Die Living</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/die-living/1884752889</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Die Living - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:50</v>
+        <v>2:59</v>
       </c>
       <c r="H133" t="str">
-        <v>ILLENIUM</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/die-living/1884752887</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L133" t="str">
-        <v>Die Living - ILLENIUM</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Heaven On Earth</v>
+        <v>an apple a day</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Heaven On Earth - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:59</v>
+        <v>5:16</v>
       </c>
       <c r="H134" t="str">
-        <v>Pentatonix</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L134" t="str">
-        <v>Heaven On Earth - Pentatonix</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>an apple a day</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>an apple a day - Single</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>5:16</v>
+        <v>2:09</v>
       </c>
       <c r="H135" t="str">
-        <v>horsegiirL</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L135" t="str">
-        <v>an apple a day - horsegiirL</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>OUT LATE.</v>
+        <v>Be With You</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/out-late/1884478039</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>OUT LATE. - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G136" t="str">
-        <v>2:09</v>
+        <v>3:35</v>
       </c>
       <c r="H136" t="str">
-        <v>Loud Luxury</v>
+        <v>Muse</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/out-late/1884478038</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L136" t="str">
-        <v>OUT LATE. - Loud Luxury</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Be With You</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Wow! Signal</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G137" t="str">
-        <v>3:35</v>
+        <v>8:27</v>
       </c>
       <c r="H137" t="str">
-        <v>Muse</v>
+        <v>Neurosis</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L137" t="str">
-        <v>Be With You - Muse</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>First Red Rays</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>An Undying Love for a Burning World</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G138" t="str">
-        <v>8:27</v>
+        <v>4:02</v>
       </c>
       <c r="H138" t="str">
-        <v>Neurosis</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L138" t="str">
-        <v>First Red Rays - Neurosis</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Caught In The Echo</v>
+        <v>Little by Little</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>4:02</v>
+        <v>2:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Foo Fighters</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L139" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Little by Little</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Little by Little - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:34</v>
+        <v>3:28</v>
       </c>
       <c r="H140" t="str">
-        <v>Mon Rovîa</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L140" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Montgomery County</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:28</v>
+        <v>2:46</v>
       </c>
       <c r="H141" t="str">
-        <v>Parker McCollum</v>
+        <v>Alok</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L141" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Dive Into Me</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G142" t="str">
-        <v>2:46</v>
+        <v>2:40</v>
       </c>
       <c r="H142" t="str">
-        <v>Alok</v>
+        <v>Artemas</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L142" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>more than just a little bit</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>getting up to no good</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:40</v>
+        <v>2:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Artemas</v>
+        <v>Asake</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L143" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>WORSHIP</v>
+        <v>Honest</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>WORSHIP - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:43</v>
+        <v>3:22</v>
       </c>
       <c r="H144" t="str">
-        <v>Asake</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L144" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Honest</v>
+        <v>6ft Under</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Honest - Single</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:22</v>
+        <v>3:30</v>
       </c>
       <c r="H145" t="str">
-        <v>Ebony Riley</v>
+        <v>KELS</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L145" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>6ft Under</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>6ft Under - Single</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G146" t="str">
-        <v>3:30</v>
+        <v>3:29</v>
       </c>
       <c r="H146" t="str">
-        <v>KELS</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L146" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Maybe Again</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>When The City Sleeps</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G147" t="str">
-        <v>3:29</v>
+        <v>3:01</v>
       </c>
       <c r="H147" t="str">
-        <v>Alex Isley</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L147" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Trigger Happy</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Attachment Theory</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G148" t="str">
         <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L148" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G149" t="str">
-        <v>3:01</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Kid Cudi</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L149" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:30</v>
+        <v>2:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Swae Lee</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L150" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Runnin' On E</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>LINAJE</v>
       </c>
       <c r="G151" t="str">
-        <v>2:27</v>
+        <v>5:36</v>
       </c>
       <c r="H151" t="str">
-        <v>Wyatt Flores</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L151" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>FREESTYLE</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>LINAJE</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G152" t="str">
-        <v>5:36</v>
+        <v>3:23</v>
       </c>
       <c r="H152" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>marquitos</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L152" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Orcasitas</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Alma De Cántaro</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G153" t="str">
-        <v>3:23</v>
+        <v>2:35</v>
       </c>
       <c r="H153" t="str">
-        <v>marquitos</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L153" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Vida Loca</v>
+        <v>Honest</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>FREE SPIRITS</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G154" t="str">
-        <v>2:35</v>
+        <v>3:39</v>
       </c>
       <c r="H154" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L154" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Honest</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>The Weight of the Woods</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:39</v>
+        <v>3:01</v>
       </c>
       <c r="H155" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L155" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Peaches!</v>
       </c>
       <c r="G156" t="str">
-        <v>3:01</v>
+        <v>5:00</v>
       </c>
       <c r="H156" t="str">
-        <v>Kenia Os</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L156" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Peaches!</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G157" t="str">
-        <v>5:00</v>
+        <v>3:36</v>
       </c>
       <c r="H157" t="str">
-        <v>The Black Keys</v>
+        <v>Cannons</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L157" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Light as a Feather</v>
+        <v>Loving One</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Everything Glows</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Cannons</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L158" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Loving One</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Loving One - Single</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:39</v>
+        <v>3:05</v>
       </c>
       <c r="H159" t="str">
-        <v>People I’ve Met</v>
+        <v>Trousdale</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L159" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Both Can Be True</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G160" t="str">
-        <v>3:05</v>
+        <v>4:27</v>
       </c>
       <c r="H160" t="str">
-        <v>Trousdale</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L160" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Buffalo 66</v>
+        <v>brb</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>brb - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:27</v>
+        <v>2:36</v>
       </c>
       <c r="H161" t="str">
-        <v>Nessa Barrett</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L161" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>brb</v>
+        <v>Euphoria</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>brb - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:36</v>
+        <v>3:32</v>
       </c>
       <c r="H162" t="str">
-        <v>The Two Lips</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L162" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Euphoria</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Euphoria - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>3:32</v>
+        <v>2:57</v>
       </c>
       <c r="H163" t="str">
-        <v>Talia Rae</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L163" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>if i'm lucky</v>
+        <v>Gracie</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>better late than not at all - EP</v>
+        <v>F.I.G</v>
       </c>
       <c r="G164" t="str">
-        <v>2:57</v>
+        <v>2:54</v>
       </c>
       <c r="H164" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L164" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Gracie</v>
+        <v>down under</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>F.I.G</v>
+        <v>down under - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:54</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>Naomi Scott</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L165" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>down under</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/down-under/1883127406</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>down under - Single</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/down-under/1883127402</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L166" t="str">
-        <v>down under - Kevian Kraemer</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Send Me A Sign</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Send Me A Sign - Single</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>3:02</v>
       </c>
       <c r="H167" t="str">
-        <v>Girlfriend, Wife</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L167" t="str">
-        <v>Send Me A Sign - Girlfriend, Wife</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G168" t="str">
-        <v>3:02</v>
+        <v>3:14</v>
       </c>
       <c r="H168" t="str">
-        <v>OneRepublic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L168" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Dream Chaser</v>
+        <v>Trouble</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Dream Chaser</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G169" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H169" t="str">
-        <v>Willie Nelson</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L169" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Trouble</v>
+        <v>judas</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Girlfriend</v>
+        <v>judas - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:17</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Grace Ives</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L170" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>judas</v>
+        <v>JINX</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>judas - Single</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:31</v>
+        <v>2:54</v>
       </c>
       <c r="H171" t="str">
-        <v>Josiah Queen</v>
+        <v>Zacari</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L171" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>JINX</v>
+        <v>se fue</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>JINX - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G172" t="str">
-        <v>2:54</v>
+        <v>2:51</v>
       </c>
       <c r="H172" t="str">
-        <v>Zacari</v>
+        <v>Eddy</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L172" t="str">
-        <v>JINX - Zacari</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>se fue</v>
+        <v>The Blade</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Náufrago</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:51</v>
+        <v>3:15</v>
       </c>
       <c r="H173" t="str">
-        <v>Eddy</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L173" t="str">
-        <v>se fue - Eddy</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Blade</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Blade - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:15</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>Kingfishr</v>
+        <v>SPINALL</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L174" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Metric Rules</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:13</v>
+        <v>2:15</v>
       </c>
       <c r="H175" t="str">
-        <v>SPINALL</v>
+        <v>ZEP</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L175" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:15</v>
+        <v>3:23</v>
       </c>
       <c r="H176" t="str">
-        <v>ZEP</v>
+        <v>Hutch</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L176" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:23</v>
+        <v>5:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Hutch</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L177" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Cyclone</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G178" t="str">
-        <v>5:15</v>
+        <v>5:33</v>
       </c>
       <c r="H178" t="str">
-        <v>MJ Cole</v>
+        <v>Gaerea</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L178" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Cyclone</v>
+        <v>Checkmate</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Loss</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>5:33</v>
+        <v>4:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Gaerea</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L179" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checkmate</v>
+        <v>DAVE</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Checkmate - Single</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:23</v>
+        <v>2:01</v>
       </c>
       <c r="H180" t="str">
-        <v>Blue Medusa</v>
+        <v>Hulvey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L180" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>DAVE</v>
+        <v>Change</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>DAVE - Single</v>
+        <v>Change - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:01</v>
+        <v>2:38</v>
       </c>
       <c r="H181" t="str">
-        <v>Hulvey</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L181" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Change</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Change - Single</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:38</v>
+        <v>3:05</v>
       </c>
       <c r="H182" t="str">
-        <v>Stephen Stanley</v>
+        <v>Maisak</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L182" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Te Entiendo</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>V</v>
       </c>
       <c r="G183" t="str">
-        <v>3:05</v>
+        <v>2:01</v>
       </c>
       <c r="H183" t="str">
-        <v>Maisak</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L183" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>CHEVROLET 90</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>V</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G184" t="str">
-        <v>2:01</v>
+        <v>3:53</v>
       </c>
       <c r="H184" t="str">
-        <v>Rey Quinto</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L184" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Tirabalas</v>
+        <v>punchbowl</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:53</v>
+        <v>2:34</v>
       </c>
       <c r="H185" t="str">
-        <v>Hans el Oso</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L185" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>punchbowl</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>punchbowl - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:34</v>
+        <v>3:41</v>
       </c>
       <c r="H186" t="str">
-        <v>Julio Caesar</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L186" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Wild Ride</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Wild Ride - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:41</v>
+        <v>2:03</v>
       </c>
       <c r="H187" t="str">
-        <v>Durand Bernarr</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L187" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Lamb Chop</v>
+        <v>Free Nick</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:03</v>
+        <v>2:05</v>
       </c>
       <c r="H188" t="str">
-        <v>Chuckyy</v>
+        <v>Raq baby</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L188" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t=